--- a/docs/assets/GaGu DB.xlsx
+++ b/docs/assets/GaGu DB.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9547" uniqueCount="2364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9574" uniqueCount="2374">
   <si>
     <t>CODE</t>
   </si>
@@ -5366,6 +5366,36 @@
   </si>
   <si>
     <t>TEXT</t>
+  </si>
+  <si>
+    <t>GAME</t>
+  </si>
+  <si>
+    <t>b_Abundance_b img_assets/images/hsr/icons/HSR_Abundance.png_img : Heals allies and restores HP to the team</t>
+  </si>
+  <si>
+    <t>b_Destruction_b img_assets/images/hsr/icons/HSR_Destruction.png_img : Deals outstanding amounts of damage and possesses great survivability. Suitable for various combat scenarios</t>
+  </si>
+  <si>
+    <t>b_Erudition_b img_assets/images/hsr/icons/HSR_Erudition.png_img : Deals remarkable amounts of multi-target damage. The main damage dealer against groups of enemies</t>
+  </si>
+  <si>
+    <t>b_Harmony_b img_assets/images/hsr/icons/HSR_Harmony.png_img : Applies buffs to allies to improve the team's combat capacities</t>
+  </si>
+  <si>
+    <t>b_Hunt_b img_assets/images/hsr/icons/HSR_Hunt.png_img : Deals extraordinary amounts of single-target damage. The main damage dealer against Elite Enemies</t>
+  </si>
+  <si>
+    <t>b_Nihility_b img_assets/images/hsr/icons/HSR_Nihility.png_img : Applies debuffs to enemies to reduce their combat capacities</t>
+  </si>
+  <si>
+    <t>b_Preservation_b img_assets/images/hsr/icons/HSR_Preservation.png_img : Possesses powerful defensive abilities to protect allies in various ways</t>
+  </si>
+  <si>
+    <t>b_Remembrance_b img_assets/images/hsr/icons/HSR_Remembrance.png_img : Possesses the ability to summon a memosprite with special abilities to fight alongside the team in battle</t>
+  </si>
+  <si>
+    <t>b_Elation_b img_assets/images/hsr/icons/HSR_Elation.png_img : Devise different kinds of punchlines to entice Aha to join in the revelry.</t>
   </si>
   <si>
     <t>TEAM</t>
@@ -7536,7 +7566,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="120">
+  <cellXfs count="122">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -7861,6 +7891,12 @@
     <xf borderId="22" fillId="4" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="3" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -8177,7 +8213,7 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:D39" displayName="NOTES" name="NOTES" id="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:D48" displayName="NOTES" name="NOTES" id="12">
   <tableColumns count="4">
     <tableColumn name="GAME_CODE" id="1"/>
     <tableColumn name="OWNER_CODE" id="2"/>
@@ -14060,27 +14096,23 @@
       </c>
     </row>
     <row r="2" ht="22.5" customHeight="1">
-      <c r="A2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="C2" s="3" t="s">
+      <c r="A2" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="108"/>
+      <c r="C2" s="23" t="s">
         <v>1765</v>
       </c>
-      <c r="D2" s="108" t="s">
+      <c r="D2" s="109" t="s">
         <v>1766</v>
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="10">
-        <v>2.0</v>
-      </c>
-      <c r="C3" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="108"/>
+      <c r="C3" s="23" t="s">
         <v>1765</v>
       </c>
       <c r="D3" s="109" t="s">
@@ -14088,27 +14120,23 @@
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="4">
-        <v>3.0</v>
-      </c>
-      <c r="C4" s="3" t="s">
+      <c r="A4" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="108"/>
+      <c r="C4" s="23" t="s">
         <v>1765</v>
       </c>
-      <c r="D4" s="108" t="s">
+      <c r="D4" s="109" t="s">
         <v>1768</v>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="10">
-        <v>4.0</v>
-      </c>
-      <c r="C5" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="108"/>
+      <c r="C5" s="23" t="s">
         <v>1765</v>
       </c>
       <c r="D5" s="109" t="s">
@@ -14116,27 +14144,23 @@
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="C6" s="3" t="s">
+      <c r="A6" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="108"/>
+      <c r="C6" s="23" t="s">
         <v>1765</v>
       </c>
-      <c r="D6" s="108" t="s">
+      <c r="D6" s="109" t="s">
         <v>1770</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="10">
-        <v>5.0</v>
-      </c>
-      <c r="C7" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="108"/>
+      <c r="C7" s="23" t="s">
         <v>1765</v>
       </c>
       <c r="D7" s="109" t="s">
@@ -14144,27 +14168,23 @@
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
-      <c r="A8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="C8" s="3" t="s">
+      <c r="A8" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="108"/>
+      <c r="C8" s="23" t="s">
         <v>1765</v>
       </c>
-      <c r="D8" s="108" t="s">
+      <c r="D8" s="109" t="s">
         <v>1772</v>
       </c>
     </row>
     <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="10">
-        <v>6.0</v>
-      </c>
-      <c r="C9" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="108"/>
+      <c r="C9" s="23" t="s">
         <v>1765</v>
       </c>
       <c r="D9" s="109" t="s">
@@ -14172,185 +14192,183 @@
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
-      <c r="A10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="4">
+      <c r="A10" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="108"/>
+      <c r="C10" s="23" t="s">
+        <v>1765</v>
+      </c>
+      <c r="D10" s="109" t="s">
+        <v>1774</v>
+      </c>
+    </row>
+    <row r="11" ht="22.5" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>1775</v>
+      </c>
+      <c r="D11" s="110" t="s">
+        <v>1776</v>
+      </c>
+    </row>
+    <row r="12" ht="22.5" customHeight="1">
+      <c r="A12" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="10">
+        <v>2.0</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>1775</v>
+      </c>
+      <c r="D12" s="111" t="s">
+        <v>1777</v>
+      </c>
+    </row>
+    <row r="13" ht="22.5" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>1775</v>
+      </c>
+      <c r="D13" s="110" t="s">
+        <v>1778</v>
+      </c>
+    </row>
+    <row r="14" ht="22.5" customHeight="1">
+      <c r="A14" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" s="10">
+        <v>4.0</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>1775</v>
+      </c>
+      <c r="D14" s="111" t="s">
+        <v>1779</v>
+      </c>
+    </row>
+    <row r="15" ht="22.5" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>1775</v>
+      </c>
+      <c r="D15" s="110" t="s">
+        <v>1780</v>
+      </c>
+    </row>
+    <row r="16" ht="22.5" customHeight="1">
+      <c r="A16" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16" s="10">
+        <v>5.0</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>1775</v>
+      </c>
+      <c r="D16" s="111" t="s">
+        <v>1781</v>
+      </c>
+    </row>
+    <row r="17" ht="22.5" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B17" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>1775</v>
+      </c>
+      <c r="D17" s="110" t="s">
+        <v>1782</v>
+      </c>
+    </row>
+    <row r="18" ht="22.5" customHeight="1">
+      <c r="A18" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B18" s="10">
         <v>6.0</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>1765</v>
-      </c>
-      <c r="D10" s="108" t="s">
-        <v>1774</v>
-      </c>
-    </row>
-    <row r="11" ht="22.5" customHeight="1">
-      <c r="A11" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="10">
+      <c r="C18" s="9" t="s">
+        <v>1775</v>
+      </c>
+      <c r="D18" s="111" t="s">
+        <v>1783</v>
+      </c>
+    </row>
+    <row r="19" ht="22.5" customHeight="1">
+      <c r="A19" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B19" s="4">
         <v>6.0</v>
       </c>
-      <c r="C11" s="9" t="s">
-        <v>1765</v>
-      </c>
-      <c r="D11" s="109" t="s">
+      <c r="C19" s="3" t="s">
         <v>1775</v>
       </c>
-    </row>
-    <row r="12" ht="22.5" customHeight="1">
-      <c r="A12" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" s="4">
+      <c r="D19" s="110" t="s">
+        <v>1784</v>
+      </c>
+    </row>
+    <row r="20" ht="22.5" customHeight="1">
+      <c r="A20" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B20" s="10">
+        <v>6.0</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>1775</v>
+      </c>
+      <c r="D20" s="111" t="s">
+        <v>1785</v>
+      </c>
+    </row>
+    <row r="21" ht="22.5" customHeight="1">
+      <c r="A21" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B21" s="4">
         <v>7.0</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>1765</v>
-      </c>
-      <c r="D12" s="108" t="s">
-        <v>1776</v>
-      </c>
-    </row>
-    <row r="13" ht="22.5" customHeight="1">
-      <c r="A13" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B13" s="10">
+      <c r="C21" s="3" t="s">
+        <v>1775</v>
+      </c>
+      <c r="D21" s="110" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="22" ht="22.5" customHeight="1">
+      <c r="A22" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B22" s="10">
         <v>8.0</v>
       </c>
-      <c r="C13" s="9" t="s">
-        <v>1765</v>
-      </c>
-      <c r="D13" s="109" t="s">
-        <v>1777</v>
-      </c>
-    </row>
-    <row r="14" ht="22.5" customHeight="1">
-      <c r="A14" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14" s="4">
-        <v>9.0</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>1765</v>
-      </c>
-      <c r="D14" s="108" t="s">
-        <v>1778</v>
-      </c>
-    </row>
-    <row r="15" ht="22.5" customHeight="1">
-      <c r="A15" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B15" s="10">
-        <v>10.0</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>1765</v>
-      </c>
-      <c r="D15" s="109" t="s">
-        <v>1779</v>
-      </c>
-    </row>
-    <row r="16" ht="22.5" customHeight="1">
-      <c r="A16" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B16" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>1765</v>
-      </c>
-      <c r="D16" s="108" t="s">
-        <v>1780</v>
-      </c>
-    </row>
-    <row r="17" ht="22.5" customHeight="1">
-      <c r="A17" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B17" s="10">
-        <v>12.0</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>1765</v>
-      </c>
-      <c r="D17" s="109" t="s">
-        <v>1781</v>
-      </c>
-    </row>
-    <row r="18" ht="22.5" customHeight="1">
-      <c r="A18" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B18" s="4">
-        <v>14.0</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>1765</v>
-      </c>
-      <c r="D18" s="108" t="s">
-        <v>1782</v>
-      </c>
-    </row>
-    <row r="19" ht="22.5" customHeight="1">
-      <c r="A19" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B19" s="10">
-        <v>16.0</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>1765</v>
-      </c>
-      <c r="D19" s="109" t="s">
-        <v>1783</v>
-      </c>
-    </row>
-    <row r="20" ht="22.5" customHeight="1">
-      <c r="A20" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B20" s="4">
-        <v>18.0</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>1765</v>
-      </c>
-      <c r="D20" s="108" t="s">
-        <v>1784</v>
-      </c>
-    </row>
-    <row r="21" ht="22.5" customHeight="1">
-      <c r="A21" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B21" s="10">
-        <v>19.0</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>1765</v>
-      </c>
-      <c r="D21" s="109" t="s">
-        <v>1785</v>
-      </c>
-    </row>
-    <row r="22" ht="22.5" customHeight="1">
-      <c r="A22" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B22" s="4">
-        <v>20.0</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>1765</v>
-      </c>
-      <c r="D22" s="110" t="s">
-        <v>1786</v>
+      <c r="C22" s="9" t="s">
+        <v>1775</v>
+      </c>
+      <c r="D22" s="111" t="s">
+        <v>1787</v>
       </c>
     </row>
     <row r="23" ht="22.5" customHeight="1">
@@ -14358,237 +14376,363 @@
         <v>10</v>
       </c>
       <c r="B23" s="4">
-        <v>20.0</v>
+        <v>9.0</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>1765</v>
-      </c>
-      <c r="D23" s="111" t="s">
-        <v>1787</v>
+        <v>1775</v>
+      </c>
+      <c r="D23" s="110" t="s">
+        <v>1788</v>
       </c>
     </row>
     <row r="24" ht="22.5" customHeight="1">
       <c r="A24" s="8" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B24" s="10">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>1765</v>
-      </c>
-      <c r="D24" s="109" t="s">
-        <v>1788</v>
+        <v>1775</v>
+      </c>
+      <c r="D24" s="111" t="s">
+        <v>1789</v>
       </c>
     </row>
     <row r="25" ht="22.5" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B25" s="4">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>1765</v>
-      </c>
-      <c r="D25" s="108" t="s">
-        <v>1789</v>
+        <v>1775</v>
+      </c>
+      <c r="D25" s="110" t="s">
+        <v>1790</v>
       </c>
     </row>
     <row r="26" ht="22.5" customHeight="1">
       <c r="A26" s="8" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B26" s="10">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>1765</v>
-      </c>
-      <c r="D26" s="109" t="s">
-        <v>1790</v>
+        <v>1775</v>
+      </c>
+      <c r="D26" s="111" t="s">
+        <v>1791</v>
       </c>
     </row>
     <row r="27" ht="22.5" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="B27" s="4">
-        <v>1.0</v>
+        <v>14.0</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>1765</v>
-      </c>
-      <c r="D27" s="108" t="s">
-        <v>1791</v>
+        <v>1775</v>
+      </c>
+      <c r="D27" s="110" t="s">
+        <v>1792</v>
       </c>
     </row>
     <row r="28" ht="22.5" customHeight="1">
       <c r="A28" s="8" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="B28" s="10">
-        <v>2.0</v>
+        <v>16.0</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>1765</v>
-      </c>
-      <c r="D28" s="112" t="s">
-        <v>1792</v>
+        <v>1775</v>
+      </c>
+      <c r="D28" s="111" t="s">
+        <v>1793</v>
       </c>
     </row>
     <row r="29" ht="22.5" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="B29" s="4">
-        <v>3.0</v>
+        <v>18.0</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>1765</v>
-      </c>
-      <c r="D29" s="108" t="s">
-        <v>1793</v>
+        <v>1775</v>
+      </c>
+      <c r="D29" s="110" t="s">
+        <v>1794</v>
       </c>
     </row>
     <row r="30" ht="22.5" customHeight="1">
       <c r="A30" s="8" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="B30" s="10">
-        <v>4.0</v>
+        <v>19.0</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>1765</v>
-      </c>
-      <c r="D30" s="109" t="s">
-        <v>1794</v>
+        <v>1775</v>
+      </c>
+      <c r="D30" s="111" t="s">
+        <v>1795</v>
       </c>
     </row>
     <row r="31" ht="22.5" customHeight="1">
       <c r="A31" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B31" s="4">
+        <v>20.0</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>1775</v>
+      </c>
+      <c r="D31" s="112" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="32" ht="22.5" customHeight="1">
+      <c r="A32" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B32" s="4">
+        <v>20.0</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>1775</v>
+      </c>
+      <c r="D32" s="113" t="s">
+        <v>1797</v>
+      </c>
+    </row>
+    <row r="33" ht="22.5" customHeight="1">
+      <c r="A33" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B33" s="10">
+        <v>7.0</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>1775</v>
+      </c>
+      <c r="D33" s="111" t="s">
+        <v>1798</v>
+      </c>
+    </row>
+    <row r="34" ht="22.5" customHeight="1">
+      <c r="A34" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B34" s="4">
+        <v>11.0</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>1775</v>
+      </c>
+      <c r="D34" s="110" t="s">
+        <v>1799</v>
+      </c>
+    </row>
+    <row r="35" ht="22.5" customHeight="1">
+      <c r="A35" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B35" s="10">
+        <v>11.0</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>1775</v>
+      </c>
+      <c r="D35" s="111" t="s">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="36" ht="22.5" customHeight="1">
+      <c r="A36" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B31" s="4">
+      <c r="B36" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>1775</v>
+      </c>
+      <c r="D36" s="110" t="s">
+        <v>1801</v>
+      </c>
+    </row>
+    <row r="37" ht="22.5" customHeight="1">
+      <c r="A37" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B37" s="10">
+        <v>2.0</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>1775</v>
+      </c>
+      <c r="D37" s="114" t="s">
+        <v>1802</v>
+      </c>
+    </row>
+    <row r="38" ht="22.5" customHeight="1">
+      <c r="A38" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B38" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>1775</v>
+      </c>
+      <c r="D38" s="110" t="s">
+        <v>1803</v>
+      </c>
+    </row>
+    <row r="39" ht="22.5" customHeight="1">
+      <c r="A39" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B39" s="10">
+        <v>4.0</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>1775</v>
+      </c>
+      <c r="D39" s="111" t="s">
+        <v>1804</v>
+      </c>
+    </row>
+    <row r="40" ht="22.5" customHeight="1">
+      <c r="A40" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B40" s="4">
         <v>5.0</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>1765</v>
-      </c>
-      <c r="D31" s="108" t="s">
-        <v>1795</v>
-      </c>
-    </row>
-    <row r="32" ht="22.5" customHeight="1">
-      <c r="A32" s="8" t="s">
+      <c r="C40" s="3" t="s">
+        <v>1775</v>
+      </c>
+      <c r="D40" s="110" t="s">
+        <v>1805</v>
+      </c>
+    </row>
+    <row r="41" ht="22.5" customHeight="1">
+      <c r="A41" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B32" s="10">
+      <c r="B41" s="10">
         <v>6.0</v>
       </c>
-      <c r="C32" s="9" t="s">
-        <v>1765</v>
-      </c>
-      <c r="D32" s="109" t="s">
-        <v>1796</v>
-      </c>
-    </row>
-    <row r="33" ht="22.5" customHeight="1">
-      <c r="A33" s="2" t="s">
+      <c r="C41" s="9" t="s">
+        <v>1775</v>
+      </c>
+      <c r="D41" s="111" t="s">
+        <v>1806</v>
+      </c>
+    </row>
+    <row r="42" ht="22.5" customHeight="1">
+      <c r="A42" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B33" s="4">
+      <c r="B42" s="4">
         <v>7.0</v>
       </c>
-      <c r="C33" s="3" t="s">
-        <v>1765</v>
-      </c>
-      <c r="D33" s="108" t="s">
-        <v>1797</v>
-      </c>
-    </row>
-    <row r="34" ht="22.5" customHeight="1">
-      <c r="A34" s="8" t="s">
+      <c r="C42" s="3" t="s">
+        <v>1775</v>
+      </c>
+      <c r="D42" s="110" t="s">
+        <v>1807</v>
+      </c>
+    </row>
+    <row r="43" ht="22.5" customHeight="1">
+      <c r="A43" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B34" s="10">
+      <c r="B43" s="10">
         <v>9.0</v>
       </c>
-      <c r="C34" s="9" t="s">
-        <v>1765</v>
-      </c>
-      <c r="D34" s="109" t="s">
-        <v>1798</v>
-      </c>
-    </row>
-    <row r="35" ht="22.5" customHeight="1">
-      <c r="A35" s="2" t="s">
+      <c r="C43" s="9" t="s">
+        <v>1775</v>
+      </c>
+      <c r="D43" s="111" t="s">
+        <v>1808</v>
+      </c>
+    </row>
+    <row r="44" ht="22.5" customHeight="1">
+      <c r="A44" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B35" s="4">
+      <c r="B44" s="4">
         <v>10.0</v>
       </c>
-      <c r="C35" s="3" t="s">
-        <v>1765</v>
-      </c>
-      <c r="D35" s="108" t="s">
-        <v>1799</v>
-      </c>
-    </row>
-    <row r="36" ht="22.5" customHeight="1">
-      <c r="A36" s="8" t="s">
+      <c r="C44" s="3" t="s">
+        <v>1775</v>
+      </c>
+      <c r="D44" s="110" t="s">
+        <v>1809</v>
+      </c>
+    </row>
+    <row r="45" ht="22.5" customHeight="1">
+      <c r="A45" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B36" s="10">
+      <c r="B45" s="10">
         <v>1.0</v>
       </c>
-      <c r="C36" s="9" t="s">
-        <v>1765</v>
-      </c>
-      <c r="D36" s="109" t="s">
-        <v>1800</v>
-      </c>
-    </row>
-    <row r="37" ht="22.5" customHeight="1">
-      <c r="A37" s="2" t="s">
+      <c r="C45" s="9" t="s">
+        <v>1775</v>
+      </c>
+      <c r="D45" s="111" t="s">
+        <v>1810</v>
+      </c>
+    </row>
+    <row r="46" ht="22.5" customHeight="1">
+      <c r="A46" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B37" s="4">
+      <c r="B46" s="4">
         <v>2.0</v>
       </c>
-      <c r="C37" s="3" t="s">
-        <v>1765</v>
-      </c>
-      <c r="D37" s="108" t="s">
-        <v>1801</v>
-      </c>
-    </row>
-    <row r="38" ht="22.5" customHeight="1">
-      <c r="A38" s="8" t="s">
+      <c r="C46" s="3" t="s">
+        <v>1775</v>
+      </c>
+      <c r="D46" s="110" t="s">
+        <v>1811</v>
+      </c>
+    </row>
+    <row r="47" ht="22.5" customHeight="1">
+      <c r="A47" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B38" s="10">
+      <c r="B47" s="10">
         <v>4.0</v>
       </c>
-      <c r="C38" s="9" t="s">
-        <v>1765</v>
-      </c>
-      <c r="D38" s="109" t="s">
-        <v>1802</v>
-      </c>
-    </row>
-    <row r="39" ht="22.5" customHeight="1">
-      <c r="A39" s="33" t="s">
+      <c r="C47" s="9" t="s">
+        <v>1775</v>
+      </c>
+      <c r="D47" s="111" t="s">
+        <v>1812</v>
+      </c>
+    </row>
+    <row r="48" ht="22.5" customHeight="1">
+      <c r="A48" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="B39" s="36">
+      <c r="B48" s="36">
         <v>5.0</v>
       </c>
-      <c r="C39" s="34" t="s">
-        <v>1765</v>
-      </c>
-      <c r="D39" s="113" t="s">
-        <v>1803</v>
+      <c r="C48" s="34" t="s">
+        <v>1775</v>
+      </c>
+      <c r="D48" s="115" t="s">
+        <v>1813</v>
       </c>
     </row>
   </sheetData>
@@ -14630,1654 +14774,1654 @@
         <v>261</v>
       </c>
       <c r="F1" s="39" t="s">
-        <v>1804</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="2" ht="22.5" customHeight="1">
-      <c r="A2" s="114"/>
-      <c r="B2" s="114" t="s">
+      <c r="A2" s="116"/>
+      <c r="B2" s="116" t="s">
         <v>1661</v>
       </c>
-      <c r="C2" s="114" t="s">
+      <c r="C2" s="116" t="s">
         <v>1661</v>
       </c>
       <c r="D2" s="40" t="s">
-        <v>1805</v>
-      </c>
-      <c r="E2" s="114" t="s">
-        <v>1806</v>
-      </c>
-      <c r="F2" s="115"/>
+        <v>1815</v>
+      </c>
+      <c r="E2" s="116" t="s">
+        <v>1816</v>
+      </c>
+      <c r="F2" s="117"/>
     </row>
     <row r="3" ht="22.5" customHeight="1">
-      <c r="A3" s="114"/>
-      <c r="B3" s="114" t="s">
+      <c r="A3" s="116"/>
+      <c r="B3" s="116" t="s">
         <v>1669</v>
       </c>
-      <c r="C3" s="114" t="s">
+      <c r="C3" s="116" t="s">
         <v>1669</v>
       </c>
       <c r="D3" s="40" t="s">
-        <v>1805</v>
-      </c>
-      <c r="E3" s="114" t="s">
-        <v>1807</v>
-      </c>
-      <c r="F3" s="115"/>
+        <v>1815</v>
+      </c>
+      <c r="E3" s="116" t="s">
+        <v>1817</v>
+      </c>
+      <c r="F3" s="117"/>
     </row>
     <row r="4" ht="22.5" customHeight="1">
-      <c r="A4" s="114"/>
-      <c r="B4" s="114" t="s">
+      <c r="A4" s="116"/>
+      <c r="B4" s="116" t="s">
         <v>206</v>
       </c>
-      <c r="C4" s="114" t="s">
+      <c r="C4" s="116" t="s">
         <v>206</v>
       </c>
       <c r="D4" s="40" t="s">
-        <v>1805</v>
-      </c>
-      <c r="E4" s="114" t="s">
-        <v>1808</v>
-      </c>
-      <c r="F4" s="115"/>
+        <v>1815</v>
+      </c>
+      <c r="E4" s="116" t="s">
+        <v>1818</v>
+      </c>
+      <c r="F4" s="117"/>
     </row>
     <row r="5" ht="22.5" customHeight="1">
-      <c r="A5" s="114"/>
-      <c r="B5" s="114" t="s">
+      <c r="A5" s="116"/>
+      <c r="B5" s="116" t="s">
         <v>1285</v>
       </c>
-      <c r="C5" s="114" t="s">
+      <c r="C5" s="116" t="s">
         <v>1285</v>
       </c>
       <c r="D5" s="40" t="s">
-        <v>1805</v>
-      </c>
-      <c r="E5" s="114" t="s">
-        <v>1809</v>
-      </c>
-      <c r="F5" s="115"/>
+        <v>1815</v>
+      </c>
+      <c r="E5" s="116" t="s">
+        <v>1819</v>
+      </c>
+      <c r="F5" s="117"/>
     </row>
     <row r="6" ht="22.5" customHeight="1">
-      <c r="A6" s="114"/>
-      <c r="B6" s="114" t="s">
+      <c r="A6" s="116"/>
+      <c r="B6" s="116" t="s">
         <v>1713</v>
       </c>
-      <c r="C6" s="114" t="s">
+      <c r="C6" s="116" t="s">
         <v>1713</v>
       </c>
       <c r="D6" s="40" t="s">
-        <v>1805</v>
-      </c>
-      <c r="E6" s="114" t="s">
-        <v>1810</v>
-      </c>
-      <c r="F6" s="115"/>
+        <v>1815</v>
+      </c>
+      <c r="E6" s="116" t="s">
+        <v>1820</v>
+      </c>
+      <c r="F6" s="117"/>
     </row>
     <row r="7" ht="22.5" customHeight="1">
-      <c r="A7" s="114" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="114" t="s">
+      <c r="A7" s="116" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="116" t="s">
         <v>69</v>
       </c>
-      <c r="C7" s="114" t="s">
+      <c r="C7" s="116" t="s">
         <v>69</v>
       </c>
-      <c r="D7" s="116" t="s">
+      <c r="D7" s="118" t="s">
         <v>53</v>
       </c>
-      <c r="E7" s="114" t="s">
-        <v>1811</v>
-      </c>
-      <c r="F7" s="115"/>
+      <c r="E7" s="116" t="s">
+        <v>1821</v>
+      </c>
+      <c r="F7" s="117"/>
     </row>
     <row r="8" ht="22.5" customHeight="1">
-      <c r="A8" s="114" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="114" t="s">
+      <c r="A8" s="116" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="116" t="s">
         <v>75</v>
       </c>
-      <c r="C8" s="114" t="s">
+      <c r="C8" s="116" t="s">
         <v>75</v>
       </c>
-      <c r="D8" s="116" t="s">
+      <c r="D8" s="118" t="s">
         <v>53</v>
       </c>
-      <c r="E8" s="114" t="s">
-        <v>1812</v>
-      </c>
-      <c r="F8" s="115"/>
+      <c r="E8" s="116" t="s">
+        <v>1822</v>
+      </c>
+      <c r="F8" s="117"/>
     </row>
     <row r="9" ht="22.5" customHeight="1">
-      <c r="A9" s="114" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="114" t="s">
+      <c r="A9" s="116" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="116" t="s">
         <v>59</v>
       </c>
-      <c r="C9" s="114" t="s">
+      <c r="C9" s="116" t="s">
         <v>59</v>
       </c>
-      <c r="D9" s="116" t="s">
+      <c r="D9" s="118" t="s">
         <v>53</v>
       </c>
-      <c r="E9" s="114" t="s">
-        <v>1813</v>
-      </c>
-      <c r="F9" s="115"/>
+      <c r="E9" s="116" t="s">
+        <v>1823</v>
+      </c>
+      <c r="F9" s="117"/>
     </row>
     <row r="10" ht="22.5" customHeight="1">
-      <c r="A10" s="114" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="114" t="s">
+      <c r="A10" s="116" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="116" t="s">
         <v>63</v>
       </c>
-      <c r="C10" s="114" t="s">
+      <c r="C10" s="116" t="s">
         <v>63</v>
       </c>
-      <c r="D10" s="116" t="s">
+      <c r="D10" s="118" t="s">
         <v>53</v>
       </c>
-      <c r="E10" s="114" t="s">
-        <v>1814</v>
-      </c>
-      <c r="F10" s="115"/>
+      <c r="E10" s="116" t="s">
+        <v>1824</v>
+      </c>
+      <c r="F10" s="117"/>
     </row>
     <row r="11" ht="22.5" customHeight="1">
-      <c r="A11" s="114" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="114" t="s">
+      <c r="A11" s="116" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="116" t="s">
         <v>65</v>
       </c>
-      <c r="C11" s="114" t="s">
+      <c r="C11" s="116" t="s">
         <v>65</v>
       </c>
-      <c r="D11" s="116" t="s">
+      <c r="D11" s="118" t="s">
         <v>53</v>
       </c>
-      <c r="E11" s="114" t="s">
-        <v>1815</v>
-      </c>
-      <c r="F11" s="115"/>
+      <c r="E11" s="116" t="s">
+        <v>1825</v>
+      </c>
+      <c r="F11" s="117"/>
     </row>
     <row r="12" ht="22.5" customHeight="1">
-      <c r="A12" s="114" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="114" t="s">
+      <c r="A12" s="116" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="116" t="s">
         <v>154</v>
       </c>
-      <c r="C12" s="114" t="s">
+      <c r="C12" s="116" t="s">
         <v>154</v>
       </c>
-      <c r="D12" s="116" t="s">
+      <c r="D12" s="118" t="s">
         <v>53</v>
       </c>
-      <c r="E12" s="114" t="s">
-        <v>1816</v>
-      </c>
-      <c r="F12" s="115"/>
+      <c r="E12" s="116" t="s">
+        <v>1826</v>
+      </c>
+      <c r="F12" s="117"/>
     </row>
     <row r="13" ht="22.5" customHeight="1">
-      <c r="A13" s="114" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" s="114" t="s">
+      <c r="A13" s="116" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="116" t="s">
         <v>134</v>
       </c>
-      <c r="C13" s="114" t="s">
+      <c r="C13" s="116" t="s">
         <v>134</v>
       </c>
-      <c r="D13" s="116" t="s">
+      <c r="D13" s="118" t="s">
         <v>53</v>
       </c>
-      <c r="E13" s="114" t="s">
-        <v>1817</v>
-      </c>
-      <c r="F13" s="115"/>
+      <c r="E13" s="116" t="s">
+        <v>1827</v>
+      </c>
+      <c r="F13" s="117"/>
     </row>
     <row r="14" ht="22.5" customHeight="1">
-      <c r="A14" s="114" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" s="114" t="s">
+      <c r="A14" s="116" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="116" t="s">
         <v>156</v>
       </c>
-      <c r="C14" s="114" t="s">
+      <c r="C14" s="116" t="s">
         <v>156</v>
       </c>
-      <c r="D14" s="116" t="s">
+      <c r="D14" s="118" t="s">
         <v>53</v>
       </c>
-      <c r="E14" s="114" t="s">
-        <v>1818</v>
-      </c>
-      <c r="F14" s="115"/>
+      <c r="E14" s="116" t="s">
+        <v>1828</v>
+      </c>
+      <c r="F14" s="117"/>
     </row>
     <row r="15" ht="22.5" customHeight="1">
-      <c r="A15" s="114" t="s">
-        <v>17</v>
-      </c>
-      <c r="B15" s="114" t="s">
+      <c r="A15" s="116" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="116" t="s">
         <v>136</v>
       </c>
-      <c r="C15" s="114" t="s">
+      <c r="C15" s="116" t="s">
         <v>136</v>
       </c>
-      <c r="D15" s="116" t="s">
+      <c r="D15" s="118" t="s">
         <v>53</v>
       </c>
-      <c r="E15" s="114" t="s">
-        <v>1819</v>
-      </c>
-      <c r="F15" s="115"/>
+      <c r="E15" s="116" t="s">
+        <v>1829</v>
+      </c>
+      <c r="F15" s="117"/>
     </row>
     <row r="16" ht="22.5" customHeight="1">
-      <c r="A16" s="114" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="114" t="s">
+      <c r="A16" s="116" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="116" t="s">
         <v>127</v>
       </c>
-      <c r="C16" s="114" t="s">
+      <c r="C16" s="116" t="s">
         <v>127</v>
       </c>
-      <c r="D16" s="116" t="s">
+      <c r="D16" s="118" t="s">
         <v>53</v>
       </c>
-      <c r="E16" s="114" t="s">
-        <v>1820</v>
-      </c>
-      <c r="F16" s="115"/>
+      <c r="E16" s="116" t="s">
+        <v>1830</v>
+      </c>
+      <c r="F16" s="117"/>
     </row>
     <row r="17" ht="22.5" customHeight="1">
-      <c r="A17" s="114" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17" s="114" t="s">
+      <c r="A17" s="116" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" s="116" t="s">
         <v>124</v>
       </c>
-      <c r="C17" s="114" t="s">
+      <c r="C17" s="116" t="s">
         <v>124</v>
       </c>
-      <c r="D17" s="116" t="s">
+      <c r="D17" s="118" t="s">
         <v>53</v>
       </c>
-      <c r="E17" s="114" t="s">
-        <v>1821</v>
-      </c>
-      <c r="F17" s="115"/>
+      <c r="E17" s="116" t="s">
+        <v>1831</v>
+      </c>
+      <c r="F17" s="117"/>
     </row>
     <row r="18" ht="22.5" customHeight="1">
-      <c r="A18" s="114" t="s">
-        <v>17</v>
-      </c>
-      <c r="B18" s="114" t="s">
+      <c r="A18" s="116" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="116" t="s">
         <v>130</v>
       </c>
-      <c r="C18" s="114" t="s">
+      <c r="C18" s="116" t="s">
         <v>130</v>
       </c>
-      <c r="D18" s="116" t="s">
+      <c r="D18" s="118" t="s">
         <v>53</v>
       </c>
-      <c r="E18" s="114" t="s">
-        <v>1822</v>
-      </c>
-      <c r="F18" s="115"/>
+      <c r="E18" s="116" t="s">
+        <v>1832</v>
+      </c>
+      <c r="F18" s="117"/>
     </row>
     <row r="19" ht="22.5" customHeight="1">
-      <c r="A19" s="114" t="s">
-        <v>17</v>
-      </c>
-      <c r="B19" s="114" t="s">
+      <c r="A19" s="116" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="116" t="s">
         <v>138</v>
       </c>
-      <c r="C19" s="114" t="s">
+      <c r="C19" s="116" t="s">
         <v>138</v>
       </c>
-      <c r="D19" s="116" t="s">
+      <c r="D19" s="118" t="s">
         <v>53</v>
       </c>
-      <c r="E19" s="114" t="s">
-        <v>1823</v>
-      </c>
-      <c r="F19" s="115"/>
+      <c r="E19" s="116" t="s">
+        <v>1833</v>
+      </c>
+      <c r="F19" s="117"/>
     </row>
     <row r="20" ht="22.5" customHeight="1">
-      <c r="A20" s="114" t="s">
-        <v>17</v>
-      </c>
-      <c r="B20" s="114" t="s">
+      <c r="A20" s="116" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="116" t="s">
         <v>146</v>
       </c>
-      <c r="C20" s="114" t="s">
+      <c r="C20" s="116" t="s">
         <v>146</v>
       </c>
-      <c r="D20" s="116" t="s">
+      <c r="D20" s="118" t="s">
         <v>53</v>
       </c>
-      <c r="E20" s="114" t="s">
-        <v>1824</v>
-      </c>
-      <c r="F20" s="115"/>
+      <c r="E20" s="116" t="s">
+        <v>1834</v>
+      </c>
+      <c r="F20" s="117"/>
     </row>
     <row r="21" ht="22.5" customHeight="1">
-      <c r="A21" s="114" t="s">
+      <c r="A21" s="116" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="114" t="s">
+      <c r="B21" s="116" t="s">
         <v>193</v>
       </c>
-      <c r="C21" s="114" t="s">
+      <c r="C21" s="116" t="s">
         <v>193</v>
       </c>
-      <c r="D21" s="116" t="s">
+      <c r="D21" s="118" t="s">
         <v>53</v>
       </c>
-      <c r="E21" s="114" t="s">
-        <v>1825</v>
-      </c>
-      <c r="F21" s="115"/>
+      <c r="E21" s="116" t="s">
+        <v>1835</v>
+      </c>
+      <c r="F21" s="117"/>
     </row>
     <row r="22" ht="22.5" customHeight="1">
-      <c r="A22" s="114" t="s">
+      <c r="A22" s="116" t="s">
         <v>23</v>
       </c>
-      <c r="B22" s="114" t="s">
+      <c r="B22" s="116" t="s">
         <v>199</v>
       </c>
-      <c r="C22" s="114" t="s">
+      <c r="C22" s="116" t="s">
         <v>199</v>
       </c>
-      <c r="D22" s="116" t="s">
+      <c r="D22" s="118" t="s">
         <v>53</v>
       </c>
-      <c r="E22" s="114" t="s">
-        <v>1826</v>
-      </c>
-      <c r="F22" s="115"/>
+      <c r="E22" s="116" t="s">
+        <v>1836</v>
+      </c>
+      <c r="F22" s="117"/>
     </row>
     <row r="23" ht="22.5" customHeight="1">
-      <c r="A23" s="114" t="s">
+      <c r="A23" s="116" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="114" t="s">
+      <c r="B23" s="116" t="s">
         <v>196</v>
       </c>
-      <c r="C23" s="114" t="s">
+      <c r="C23" s="116" t="s">
         <v>196</v>
       </c>
-      <c r="D23" s="116" t="s">
+      <c r="D23" s="118" t="s">
         <v>53</v>
       </c>
-      <c r="E23" s="114" t="s">
-        <v>1827</v>
-      </c>
-      <c r="F23" s="115"/>
+      <c r="E23" s="116" t="s">
+        <v>1837</v>
+      </c>
+      <c r="F23" s="117"/>
     </row>
     <row r="24" ht="22.5" customHeight="1">
-      <c r="A24" s="114" t="s">
+      <c r="A24" s="116" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="114" t="s">
+      <c r="B24" s="116" t="s">
         <v>221</v>
       </c>
-      <c r="C24" s="114" t="s">
+      <c r="C24" s="116" t="s">
         <v>221</v>
       </c>
-      <c r="D24" s="116" t="s">
+      <c r="D24" s="118" t="s">
         <v>53</v>
       </c>
-      <c r="E24" s="114" t="s">
-        <v>1828</v>
-      </c>
-      <c r="F24" s="115"/>
+      <c r="E24" s="116" t="s">
+        <v>1838</v>
+      </c>
+      <c r="F24" s="117"/>
     </row>
     <row r="25" ht="22.5" customHeight="1">
-      <c r="A25" s="114" t="s">
+      <c r="A25" s="116" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="114" t="s">
+      <c r="B25" s="116" t="s">
         <v>190</v>
       </c>
-      <c r="C25" s="114" t="s">
+      <c r="C25" s="116" t="s">
         <v>190</v>
       </c>
-      <c r="D25" s="116" t="s">
+      <c r="D25" s="118" t="s">
         <v>53</v>
       </c>
-      <c r="E25" s="114" t="s">
-        <v>1829</v>
-      </c>
-      <c r="F25" s="115"/>
+      <c r="E25" s="116" t="s">
+        <v>1839</v>
+      </c>
+      <c r="F25" s="117"/>
     </row>
     <row r="26" ht="22.5" customHeight="1">
-      <c r="A26" s="114" t="s">
+      <c r="A26" s="116" t="s">
         <v>23</v>
       </c>
-      <c r="B26" s="114" t="s">
+      <c r="B26" s="116" t="s">
         <v>206</v>
       </c>
-      <c r="C26" s="114" t="s">
+      <c r="C26" s="116" t="s">
         <v>206</v>
       </c>
-      <c r="D26" s="116" t="s">
+      <c r="D26" s="118" t="s">
         <v>53</v>
       </c>
-      <c r="E26" s="114" t="s">
-        <v>1830</v>
-      </c>
-      <c r="F26" s="115"/>
+      <c r="E26" s="116" t="s">
+        <v>1840</v>
+      </c>
+      <c r="F26" s="117"/>
     </row>
     <row r="27" ht="22.5" customHeight="1">
-      <c r="A27" s="114" t="s">
+      <c r="A27" s="116" t="s">
         <v>29</v>
       </c>
-      <c r="B27" s="114" t="s">
+      <c r="B27" s="116" t="s">
         <v>69</v>
       </c>
-      <c r="C27" s="114" t="s">
+      <c r="C27" s="116" t="s">
         <v>69</v>
       </c>
-      <c r="D27" s="116" t="s">
+      <c r="D27" s="118" t="s">
         <v>53</v>
       </c>
-      <c r="E27" s="114" t="s">
-        <v>1831</v>
-      </c>
-      <c r="F27" s="115"/>
+      <c r="E27" s="116" t="s">
+        <v>1841</v>
+      </c>
+      <c r="F27" s="117"/>
     </row>
     <row r="28" ht="22.5" customHeight="1">
-      <c r="A28" s="114" t="s">
+      <c r="A28" s="116" t="s">
         <v>29</v>
       </c>
-      <c r="B28" s="114" t="s">
+      <c r="B28" s="116" t="s">
         <v>237</v>
       </c>
-      <c r="C28" s="114" t="s">
+      <c r="C28" s="116" t="s">
         <v>237</v>
       </c>
-      <c r="D28" s="116" t="s">
+      <c r="D28" s="118" t="s">
         <v>53</v>
       </c>
-      <c r="E28" s="114" t="s">
-        <v>1832</v>
-      </c>
-      <c r="F28" s="115"/>
+      <c r="E28" s="116" t="s">
+        <v>1842</v>
+      </c>
+      <c r="F28" s="117"/>
     </row>
     <row r="29" ht="22.5" customHeight="1">
-      <c r="A29" s="114" t="s">
+      <c r="A29" s="116" t="s">
         <v>29</v>
       </c>
-      <c r="B29" s="114" t="s">
+      <c r="B29" s="116" t="s">
         <v>234</v>
       </c>
-      <c r="C29" s="114" t="s">
+      <c r="C29" s="116" t="s">
         <v>234</v>
       </c>
-      <c r="D29" s="116" t="s">
+      <c r="D29" s="118" t="s">
         <v>53</v>
       </c>
-      <c r="E29" s="114" t="s">
-        <v>1833</v>
-      </c>
-      <c r="F29" s="115"/>
+      <c r="E29" s="116" t="s">
+        <v>1843</v>
+      </c>
+      <c r="F29" s="117"/>
     </row>
     <row r="30" ht="22.5" customHeight="1">
-      <c r="A30" s="114" t="s">
+      <c r="A30" s="116" t="s">
         <v>29</v>
       </c>
-      <c r="B30" s="114" t="s">
+      <c r="B30" s="116" t="s">
         <v>252</v>
       </c>
-      <c r="C30" s="114" t="s">
+      <c r="C30" s="116" t="s">
         <v>252</v>
       </c>
-      <c r="D30" s="116" t="s">
+      <c r="D30" s="118" t="s">
         <v>53</v>
       </c>
-      <c r="E30" s="114" t="s">
-        <v>1834</v>
-      </c>
-      <c r="F30" s="115"/>
+      <c r="E30" s="116" t="s">
+        <v>1844</v>
+      </c>
+      <c r="F30" s="117"/>
     </row>
     <row r="31" ht="22.5" customHeight="1">
-      <c r="A31" s="114" t="s">
+      <c r="A31" s="116" t="s">
         <v>29</v>
       </c>
-      <c r="B31" s="114" t="s">
+      <c r="B31" s="116" t="s">
         <v>256</v>
       </c>
-      <c r="C31" s="114" t="s">
+      <c r="C31" s="116" t="s">
         <v>256</v>
       </c>
-      <c r="D31" s="116" t="s">
+      <c r="D31" s="118" t="s">
         <v>53</v>
       </c>
-      <c r="E31" s="114" t="s">
-        <v>1835</v>
-      </c>
-      <c r="F31" s="115"/>
+      <c r="E31" s="116" t="s">
+        <v>1845</v>
+      </c>
+      <c r="F31" s="117"/>
     </row>
     <row r="32" ht="22.5" customHeight="1">
-      <c r="A32" s="114" t="s">
+      <c r="A32" s="116" t="s">
         <v>29</v>
       </c>
-      <c r="B32" s="114" t="s">
+      <c r="B32" s="116" t="s">
         <v>240</v>
       </c>
-      <c r="C32" s="114" t="s">
+      <c r="C32" s="116" t="s">
         <v>240</v>
       </c>
-      <c r="D32" s="116" t="s">
+      <c r="D32" s="118" t="s">
         <v>53</v>
       </c>
-      <c r="E32" s="114" t="s">
-        <v>1836</v>
-      </c>
-      <c r="F32" s="115"/>
+      <c r="E32" s="116" t="s">
+        <v>1846</v>
+      </c>
+      <c r="F32" s="117"/>
     </row>
     <row r="33" ht="22.5" customHeight="1">
-      <c r="A33" s="114" t="s">
+      <c r="A33" s="116" t="s">
         <v>29</v>
       </c>
-      <c r="B33" s="114" t="s">
+      <c r="B33" s="116" t="s">
         <v>254</v>
       </c>
-      <c r="C33" s="114" t="s">
+      <c r="C33" s="116" t="s">
         <v>254</v>
       </c>
-      <c r="D33" s="116" t="s">
+      <c r="D33" s="118" t="s">
         <v>53</v>
       </c>
-      <c r="E33" s="114" t="s">
-        <v>1837</v>
-      </c>
-      <c r="F33" s="115"/>
+      <c r="E33" s="116" t="s">
+        <v>1847</v>
+      </c>
+      <c r="F33" s="117"/>
     </row>
     <row r="34" ht="22.5" customHeight="1">
-      <c r="A34" s="114" t="s">
+      <c r="A34" s="116" t="s">
         <v>29</v>
       </c>
-      <c r="B34" s="114" t="s">
+      <c r="B34" s="116" t="s">
         <v>242</v>
       </c>
-      <c r="C34" s="114" t="s">
+      <c r="C34" s="116" t="s">
         <v>242</v>
       </c>
-      <c r="D34" s="116" t="s">
+      <c r="D34" s="118" t="s">
         <v>53</v>
       </c>
-      <c r="E34" s="114" t="s">
-        <v>1838</v>
-      </c>
-      <c r="F34" s="115"/>
+      <c r="E34" s="116" t="s">
+        <v>1848</v>
+      </c>
+      <c r="F34" s="117"/>
     </row>
     <row r="35" ht="22.5" customHeight="1">
-      <c r="A35" s="114" t="s">
+      <c r="A35" s="116" t="s">
         <v>29</v>
       </c>
-      <c r="B35" s="114" t="s">
+      <c r="B35" s="116" t="s">
         <v>244</v>
       </c>
-      <c r="C35" s="114" t="s">
+      <c r="C35" s="116" t="s">
         <v>244</v>
       </c>
-      <c r="D35" s="116" t="s">
+      <c r="D35" s="118" t="s">
         <v>53</v>
       </c>
-      <c r="E35" s="114" t="s">
-        <v>1839</v>
-      </c>
-      <c r="F35" s="115"/>
+      <c r="E35" s="116" t="s">
+        <v>1849</v>
+      </c>
+      <c r="F35" s="117"/>
     </row>
     <row r="36" ht="22.5" customHeight="1">
-      <c r="A36" s="114" t="s">
+      <c r="A36" s="116" t="s">
         <v>29</v>
       </c>
-      <c r="B36" s="114" t="s">
+      <c r="B36" s="116" t="s">
         <v>250</v>
       </c>
-      <c r="C36" s="114" t="s">
+      <c r="C36" s="116" t="s">
         <v>250</v>
       </c>
-      <c r="D36" s="116" t="s">
+      <c r="D36" s="118" t="s">
         <v>53</v>
       </c>
-      <c r="E36" s="114" t="s">
-        <v>1840</v>
-      </c>
-      <c r="F36" s="115"/>
+      <c r="E36" s="116" t="s">
+        <v>1850</v>
+      </c>
+      <c r="F36" s="117"/>
     </row>
     <row r="37" ht="22.5" customHeight="1">
-      <c r="A37" s="114" t="s">
-        <v>10</v>
-      </c>
-      <c r="B37" s="114">
+      <c r="A37" s="116" t="s">
+        <v>10</v>
+      </c>
+      <c r="B37" s="116">
         <v>5.0</v>
       </c>
-      <c r="C37" s="114" t="s">
-        <v>1841</v>
-      </c>
-      <c r="D37" s="116" t="s">
+      <c r="C37" s="116" t="s">
+        <v>1851</v>
+      </c>
+      <c r="D37" s="118" t="s">
         <v>54</v>
       </c>
-      <c r="E37" s="114" t="s">
-        <v>1842</v>
-      </c>
-      <c r="F37" s="115"/>
+      <c r="E37" s="116" t="s">
+        <v>1852</v>
+      </c>
+      <c r="F37" s="117"/>
     </row>
     <row r="38" ht="22.5" customHeight="1">
-      <c r="A38" s="114" t="s">
-        <v>10</v>
-      </c>
-      <c r="B38" s="114">
+      <c r="A38" s="116" t="s">
+        <v>10</v>
+      </c>
+      <c r="B38" s="116">
         <v>4.0</v>
       </c>
-      <c r="C38" s="114" t="s">
-        <v>1843</v>
-      </c>
-      <c r="D38" s="116" t="s">
+      <c r="C38" s="116" t="s">
+        <v>1853</v>
+      </c>
+      <c r="D38" s="118" t="s">
         <v>54</v>
       </c>
-      <c r="E38" s="114" t="s">
-        <v>1844</v>
-      </c>
-      <c r="F38" s="115"/>
+      <c r="E38" s="116" t="s">
+        <v>1854</v>
+      </c>
+      <c r="F38" s="117"/>
     </row>
     <row r="39" ht="22.5" customHeight="1">
-      <c r="A39" s="114" t="s">
-        <v>10</v>
-      </c>
-      <c r="B39" s="114">
+      <c r="A39" s="116" t="s">
+        <v>10</v>
+      </c>
+      <c r="B39" s="116">
         <v>3.0</v>
       </c>
-      <c r="C39" s="114" t="s">
-        <v>1845</v>
-      </c>
-      <c r="D39" s="116" t="s">
+      <c r="C39" s="116" t="s">
+        <v>1855</v>
+      </c>
+      <c r="D39" s="118" t="s">
         <v>54</v>
       </c>
-      <c r="E39" s="114" t="s">
-        <v>1846</v>
-      </c>
-      <c r="F39" s="115"/>
+      <c r="E39" s="116" t="s">
+        <v>1856</v>
+      </c>
+      <c r="F39" s="117"/>
     </row>
     <row r="40" ht="22.5" customHeight="1">
-      <c r="A40" s="114" t="s">
-        <v>17</v>
-      </c>
-      <c r="B40" s="114">
+      <c r="A40" s="116" t="s">
+        <v>17</v>
+      </c>
+      <c r="B40" s="116">
         <v>5.0</v>
       </c>
-      <c r="C40" s="114" t="s">
-        <v>1847</v>
-      </c>
-      <c r="D40" s="116" t="s">
+      <c r="C40" s="116" t="s">
+        <v>1857</v>
+      </c>
+      <c r="D40" s="118" t="s">
         <v>54</v>
       </c>
-      <c r="E40" s="114" t="s">
-        <v>1848</v>
-      </c>
-      <c r="F40" s="115"/>
+      <c r="E40" s="116" t="s">
+        <v>1858</v>
+      </c>
+      <c r="F40" s="117"/>
     </row>
     <row r="41" ht="22.5" customHeight="1">
-      <c r="A41" s="114" t="s">
-        <v>17</v>
-      </c>
-      <c r="B41" s="114">
+      <c r="A41" s="116" t="s">
+        <v>17</v>
+      </c>
+      <c r="B41" s="116">
         <v>4.0</v>
       </c>
-      <c r="C41" s="114" t="s">
-        <v>1843</v>
-      </c>
-      <c r="D41" s="116" t="s">
+      <c r="C41" s="116" t="s">
+        <v>1853</v>
+      </c>
+      <c r="D41" s="118" t="s">
         <v>54</v>
       </c>
-      <c r="E41" s="114" t="s">
-        <v>1849</v>
-      </c>
-      <c r="F41" s="115"/>
+      <c r="E41" s="116" t="s">
+        <v>1859</v>
+      </c>
+      <c r="F41" s="117"/>
     </row>
     <row r="42" ht="22.5" customHeight="1">
-      <c r="A42" s="114" t="s">
+      <c r="A42" s="116" t="s">
         <v>23</v>
       </c>
-      <c r="B42" s="114" t="s">
+      <c r="B42" s="116" t="s">
         <v>194</v>
       </c>
-      <c r="C42" s="114" t="s">
-        <v>1850</v>
-      </c>
-      <c r="D42" s="116" t="s">
+      <c r="C42" s="116" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D42" s="118" t="s">
         <v>54</v>
       </c>
-      <c r="E42" s="114" t="s">
-        <v>1851</v>
-      </c>
-      <c r="F42" s="115"/>
+      <c r="E42" s="116" t="s">
+        <v>1861</v>
+      </c>
+      <c r="F42" s="117"/>
     </row>
     <row r="43" ht="22.5" customHeight="1">
-      <c r="A43" s="114" t="s">
+      <c r="A43" s="116" t="s">
         <v>23</v>
       </c>
-      <c r="B43" s="114" t="s">
+      <c r="B43" s="116" t="s">
         <v>191</v>
       </c>
-      <c r="C43" s="114" t="s">
-        <v>1852</v>
-      </c>
-      <c r="D43" s="116" t="s">
+      <c r="C43" s="116" t="s">
+        <v>1862</v>
+      </c>
+      <c r="D43" s="118" t="s">
         <v>54</v>
       </c>
-      <c r="E43" s="114" t="s">
-        <v>1853</v>
-      </c>
-      <c r="F43" s="115"/>
+      <c r="E43" s="116" t="s">
+        <v>1863</v>
+      </c>
+      <c r="F43" s="117"/>
     </row>
     <row r="44" ht="22.5" customHeight="1">
-      <c r="A44" s="114" t="s">
+      <c r="A44" s="116" t="s">
         <v>29</v>
       </c>
-      <c r="B44" s="114" t="s">
+      <c r="B44" s="116" t="s">
         <v>194</v>
       </c>
-      <c r="C44" s="114" t="s">
-        <v>1850</v>
-      </c>
-      <c r="D44" s="116" t="s">
+      <c r="C44" s="116" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D44" s="118" t="s">
         <v>54</v>
       </c>
-      <c r="E44" s="114" t="s">
-        <v>1854</v>
-      </c>
-      <c r="F44" s="115"/>
+      <c r="E44" s="116" t="s">
+        <v>1864</v>
+      </c>
+      <c r="F44" s="117"/>
     </row>
     <row r="45" ht="22.5" customHeight="1">
-      <c r="A45" s="114" t="s">
+      <c r="A45" s="116" t="s">
         <v>29</v>
       </c>
-      <c r="B45" s="114" t="s">
+      <c r="B45" s="116" t="s">
         <v>191</v>
       </c>
-      <c r="C45" s="114" t="s">
-        <v>1852</v>
-      </c>
-      <c r="D45" s="116" t="s">
+      <c r="C45" s="116" t="s">
+        <v>1862</v>
+      </c>
+      <c r="D45" s="118" t="s">
         <v>54</v>
       </c>
-      <c r="E45" s="114" t="s">
-        <v>1855</v>
-      </c>
-      <c r="F45" s="115"/>
+      <c r="E45" s="116" t="s">
+        <v>1865</v>
+      </c>
+      <c r="F45" s="117"/>
     </row>
     <row r="46" ht="22.5" customHeight="1">
-      <c r="A46" s="114" t="s">
+      <c r="A46" s="116" t="s">
         <v>42</v>
       </c>
-      <c r="B46" s="114" t="s">
+      <c r="B46" s="116" t="s">
         <v>1029</v>
       </c>
-      <c r="C46" s="114" t="s">
-        <v>1856</v>
-      </c>
-      <c r="D46" s="116" t="s">
+      <c r="C46" s="116" t="s">
+        <v>1866</v>
+      </c>
+      <c r="D46" s="118" t="s">
         <v>54</v>
       </c>
-      <c r="E46" s="114" t="s">
-        <v>1857</v>
-      </c>
-      <c r="F46" s="115"/>
+      <c r="E46" s="116" t="s">
+        <v>1867</v>
+      </c>
+      <c r="F46" s="117"/>
     </row>
     <row r="47" ht="22.5" customHeight="1">
-      <c r="A47" s="114" t="s">
+      <c r="A47" s="116" t="s">
         <v>42</v>
       </c>
-      <c r="B47" s="114" t="s">
+      <c r="B47" s="116" t="s">
         <v>1283</v>
       </c>
-      <c r="C47" s="114" t="s">
-        <v>1858</v>
-      </c>
-      <c r="D47" s="116" t="s">
+      <c r="C47" s="116" t="s">
+        <v>1868</v>
+      </c>
+      <c r="D47" s="118" t="s">
         <v>54</v>
       </c>
-      <c r="E47" s="114" t="s">
-        <v>1859</v>
-      </c>
-      <c r="F47" s="115"/>
+      <c r="E47" s="116" t="s">
+        <v>1869</v>
+      </c>
+      <c r="F47" s="117"/>
     </row>
     <row r="48" ht="22.5" customHeight="1">
-      <c r="A48" s="114" t="s">
-        <v>10</v>
-      </c>
-      <c r="B48" s="114" t="s">
+      <c r="A48" s="116" t="s">
+        <v>10</v>
+      </c>
+      <c r="B48" s="116" t="s">
         <v>62</v>
       </c>
-      <c r="C48" s="114" t="s">
+      <c r="C48" s="116" t="s">
         <v>62</v>
       </c>
       <c r="D48" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="E48" s="114" t="s">
+      <c r="E48" s="116" t="s">
         <v>1593</v>
       </c>
-      <c r="F48" s="116" t="s">
-        <v>1860</v>
+      <c r="F48" s="118" t="s">
+        <v>1870</v>
       </c>
     </row>
     <row r="49" ht="22.5" customHeight="1">
-      <c r="A49" s="114" t="s">
-        <v>10</v>
-      </c>
-      <c r="B49" s="114" t="s">
+      <c r="A49" s="116" t="s">
+        <v>10</v>
+      </c>
+      <c r="B49" s="116" t="s">
         <v>58</v>
       </c>
-      <c r="C49" s="114" t="s">
+      <c r="C49" s="116" t="s">
         <v>58</v>
       </c>
       <c r="D49" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="E49" s="114" t="s">
+      <c r="E49" s="116" t="s">
         <v>1595</v>
       </c>
-      <c r="F49" s="116" t="s">
-        <v>1860</v>
+      <c r="F49" s="118" t="s">
+        <v>1870</v>
       </c>
     </row>
     <row r="50" ht="22.5" customHeight="1">
-      <c r="A50" s="114" t="s">
-        <v>10</v>
-      </c>
-      <c r="B50" s="114" t="s">
+      <c r="A50" s="116" t="s">
+        <v>10</v>
+      </c>
+      <c r="B50" s="116" t="s">
         <v>91</v>
       </c>
-      <c r="C50" s="114" t="s">
+      <c r="C50" s="116" t="s">
         <v>91</v>
       </c>
       <c r="D50" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="E50" s="114" t="s">
+      <c r="E50" s="116" t="s">
         <v>1597</v>
       </c>
-      <c r="F50" s="116" t="s">
-        <v>1860</v>
+      <c r="F50" s="118" t="s">
+        <v>1870</v>
       </c>
     </row>
     <row r="51" ht="22.5" customHeight="1">
-      <c r="A51" s="114" t="s">
-        <v>10</v>
-      </c>
-      <c r="B51" s="114" t="s">
+      <c r="A51" s="116" t="s">
+        <v>10</v>
+      </c>
+      <c r="B51" s="116" t="s">
         <v>77</v>
       </c>
-      <c r="C51" s="114" t="s">
+      <c r="C51" s="116" t="s">
         <v>77</v>
       </c>
       <c r="D51" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="E51" s="114" t="s">
+      <c r="E51" s="116" t="s">
         <v>1599</v>
       </c>
-      <c r="F51" s="116" t="s">
-        <v>1860</v>
+      <c r="F51" s="118" t="s">
+        <v>1870</v>
       </c>
     </row>
     <row r="52" ht="22.5" customHeight="1">
-      <c r="A52" s="114" t="s">
-        <v>10</v>
-      </c>
-      <c r="B52" s="114" t="s">
+      <c r="A52" s="116" t="s">
+        <v>10</v>
+      </c>
+      <c r="B52" s="116" t="s">
         <v>68</v>
       </c>
-      <c r="C52" s="114" t="s">
+      <c r="C52" s="116" t="s">
         <v>68</v>
       </c>
       <c r="D52" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="E52" s="114" t="s">
+      <c r="E52" s="116" t="s">
         <v>1602</v>
       </c>
-      <c r="F52" s="116" t="s">
-        <v>1860</v>
+      <c r="F52" s="118" t="s">
+        <v>1870</v>
       </c>
     </row>
     <row r="53" ht="22.5" customHeight="1">
-      <c r="A53" s="114" t="s">
-        <v>10</v>
-      </c>
-      <c r="B53" s="114" t="s">
+      <c r="A53" s="116" t="s">
+        <v>10</v>
+      </c>
+      <c r="B53" s="116" t="s">
         <v>74</v>
       </c>
-      <c r="C53" s="114" t="s">
+      <c r="C53" s="116" t="s">
         <v>74</v>
       </c>
       <c r="D53" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="E53" s="114" t="s">
+      <c r="E53" s="116" t="s">
         <v>1604</v>
       </c>
-      <c r="F53" s="116" t="s">
-        <v>1860</v>
+      <c r="F53" s="118" t="s">
+        <v>1870</v>
       </c>
     </row>
     <row r="54" ht="22.5" customHeight="1">
-      <c r="A54" s="114" t="s">
-        <v>10</v>
-      </c>
-      <c r="B54" s="114" t="s">
+      <c r="A54" s="116" t="s">
+        <v>10</v>
+      </c>
+      <c r="B54" s="116" t="s">
         <v>72</v>
       </c>
-      <c r="C54" s="114" t="s">
+      <c r="C54" s="116" t="s">
         <v>72</v>
       </c>
       <c r="D54" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="E54" s="114" t="s">
+      <c r="E54" s="116" t="s">
         <v>1605</v>
       </c>
-      <c r="F54" s="116" t="s">
-        <v>1860</v>
+      <c r="F54" s="118" t="s">
+        <v>1870</v>
       </c>
     </row>
     <row r="55" ht="22.5" customHeight="1">
-      <c r="A55" s="114" t="s">
-        <v>17</v>
-      </c>
-      <c r="B55" s="114" t="s">
+      <c r="A55" s="116" t="s">
+        <v>17</v>
+      </c>
+      <c r="B55" s="116" t="s">
         <v>140</v>
       </c>
-      <c r="C55" s="114" t="s">
+      <c r="C55" s="116" t="s">
         <v>140</v>
       </c>
       <c r="D55" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="E55" s="114" t="s">
+      <c r="E55" s="116" t="s">
         <v>1631</v>
       </c>
-      <c r="F55" s="116" t="s">
-        <v>1860</v>
+      <c r="F55" s="118" t="s">
+        <v>1870</v>
       </c>
     </row>
     <row r="56" ht="22.5" customHeight="1">
-      <c r="A56" s="114" t="s">
-        <v>17</v>
-      </c>
-      <c r="B56" s="114" t="s">
+      <c r="A56" s="116" t="s">
+        <v>17</v>
+      </c>
+      <c r="B56" s="116" t="s">
         <v>150</v>
       </c>
-      <c r="C56" s="114" t="s">
+      <c r="C56" s="116" t="s">
         <v>150</v>
       </c>
       <c r="D56" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="E56" s="114" t="s">
-        <v>1861</v>
-      </c>
-      <c r="F56" s="116" t="s">
-        <v>1860</v>
+      <c r="E56" s="116" t="s">
+        <v>1871</v>
+      </c>
+      <c r="F56" s="118" t="s">
+        <v>1870</v>
       </c>
     </row>
     <row r="57" ht="22.5" customHeight="1">
-      <c r="A57" s="114" t="s">
-        <v>17</v>
-      </c>
-      <c r="B57" s="114" t="s">
+      <c r="A57" s="116" t="s">
+        <v>17</v>
+      </c>
+      <c r="B57" s="116" t="s">
         <v>142</v>
       </c>
-      <c r="C57" s="114" t="s">
+      <c r="C57" s="116" t="s">
         <v>142</v>
       </c>
       <c r="D57" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="E57" s="114" t="s">
+      <c r="E57" s="116" t="s">
         <v>1624</v>
       </c>
-      <c r="F57" s="116" t="s">
-        <v>1860</v>
+      <c r="F57" s="118" t="s">
+        <v>1870</v>
       </c>
     </row>
     <row r="58" ht="22.5" customHeight="1">
-      <c r="A58" s="114" t="s">
-        <v>17</v>
-      </c>
-      <c r="B58" s="114" t="s">
+      <c r="A58" s="116" t="s">
+        <v>17</v>
+      </c>
+      <c r="B58" s="116" t="s">
         <v>123</v>
       </c>
-      <c r="C58" s="114" t="s">
+      <c r="C58" s="116" t="s">
         <v>123</v>
       </c>
       <c r="D58" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="E58" s="114" t="s">
+      <c r="E58" s="116" t="s">
         <v>1629</v>
       </c>
-      <c r="F58" s="116" t="s">
-        <v>1860</v>
+      <c r="F58" s="118" t="s">
+        <v>1870</v>
       </c>
     </row>
     <row r="59" ht="22.5" customHeight="1">
-      <c r="A59" s="114" t="s">
-        <v>17</v>
-      </c>
-      <c r="B59" s="114" t="s">
+      <c r="A59" s="116" t="s">
+        <v>17</v>
+      </c>
+      <c r="B59" s="116" t="s">
         <v>132</v>
       </c>
-      <c r="C59" s="114" t="s">
+      <c r="C59" s="116" t="s">
         <v>132</v>
       </c>
       <c r="D59" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="E59" s="114" t="s">
+      <c r="E59" s="116" t="s">
         <v>1635</v>
       </c>
-      <c r="F59" s="116" t="s">
-        <v>1860</v>
+      <c r="F59" s="118" t="s">
+        <v>1870</v>
       </c>
     </row>
     <row r="60" ht="22.5" customHeight="1">
-      <c r="A60" s="114" t="s">
-        <v>17</v>
-      </c>
-      <c r="B60" s="114" t="s">
+      <c r="A60" s="116" t="s">
+        <v>17</v>
+      </c>
+      <c r="B60" s="116" t="s">
         <v>126</v>
       </c>
-      <c r="C60" s="114" t="s">
+      <c r="C60" s="116" t="s">
         <v>126</v>
       </c>
       <c r="D60" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="E60" s="114" t="s">
+      <c r="E60" s="116" t="s">
         <v>1634</v>
       </c>
-      <c r="F60" s="116" t="s">
-        <v>1860</v>
+      <c r="F60" s="118" t="s">
+        <v>1870</v>
       </c>
     </row>
     <row r="61" ht="22.5" customHeight="1">
-      <c r="A61" s="114" t="s">
-        <v>17</v>
-      </c>
-      <c r="B61" s="114" t="s">
+      <c r="A61" s="116" t="s">
+        <v>17</v>
+      </c>
+      <c r="B61" s="116" t="s">
         <v>129</v>
       </c>
-      <c r="C61" s="114" t="s">
+      <c r="C61" s="116" t="s">
         <v>129</v>
       </c>
       <c r="D61" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="E61" s="114" t="s">
+      <c r="E61" s="116" t="s">
         <v>1625</v>
       </c>
-      <c r="F61" s="116" t="s">
-        <v>1860</v>
+      <c r="F61" s="118" t="s">
+        <v>1870</v>
       </c>
     </row>
     <row r="62" ht="22.5" customHeight="1">
-      <c r="A62" s="114" t="s">
+      <c r="A62" s="116" t="s">
         <v>23</v>
       </c>
-      <c r="B62" s="114" t="s">
+      <c r="B62" s="116" t="s">
         <v>140</v>
       </c>
-      <c r="C62" s="114" t="s">
+      <c r="C62" s="116" t="s">
         <v>140</v>
       </c>
       <c r="D62" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="E62" s="114" t="s">
+      <c r="E62" s="116" t="s">
         <v>1649</v>
       </c>
-      <c r="F62" s="116" t="s">
-        <v>1860</v>
+      <c r="F62" s="118" t="s">
+        <v>1870</v>
       </c>
     </row>
     <row r="63" ht="22.5" customHeight="1">
-      <c r="A63" s="114" t="s">
+      <c r="A63" s="116" t="s">
         <v>23</v>
       </c>
-      <c r="B63" s="114" t="s">
+      <c r="B63" s="116" t="s">
         <v>227</v>
       </c>
-      <c r="C63" s="114" t="s">
+      <c r="C63" s="116" t="s">
         <v>227</v>
       </c>
       <c r="D63" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="E63" s="114" t="s">
-        <v>1862</v>
-      </c>
-      <c r="F63" s="116" t="s">
-        <v>1863</v>
+      <c r="E63" s="116" t="s">
+        <v>1872</v>
+      </c>
+      <c r="F63" s="118" t="s">
+        <v>1873</v>
       </c>
     </row>
     <row r="64" ht="22.5" customHeight="1">
-      <c r="A64" s="114" t="s">
+      <c r="A64" s="116" t="s">
         <v>23</v>
       </c>
-      <c r="B64" s="114" t="s">
+      <c r="B64" s="116" t="s">
         <v>150</v>
       </c>
-      <c r="C64" s="114" t="s">
+      <c r="C64" s="116" t="s">
         <v>150</v>
       </c>
       <c r="D64" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="E64" s="114" t="s">
+      <c r="E64" s="116" t="s">
         <v>1644</v>
       </c>
-      <c r="F64" s="116" t="s">
-        <v>1860</v>
+      <c r="F64" s="118" t="s">
+        <v>1870</v>
       </c>
     </row>
     <row r="65" ht="22.5" customHeight="1">
-      <c r="A65" s="114" t="s">
+      <c r="A65" s="116" t="s">
         <v>23</v>
       </c>
-      <c r="B65" s="114" t="s">
+      <c r="B65" s="116" t="s">
         <v>142</v>
       </c>
-      <c r="C65" s="114" t="s">
+      <c r="C65" s="116" t="s">
         <v>142</v>
       </c>
       <c r="D65" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="E65" s="114" t="s">
+      <c r="E65" s="116" t="s">
         <v>1646</v>
       </c>
-      <c r="F65" s="116" t="s">
-        <v>1860</v>
+      <c r="F65" s="118" t="s">
+        <v>1870</v>
       </c>
     </row>
     <row r="66" ht="22.5" customHeight="1">
-      <c r="A66" s="114" t="s">
+      <c r="A66" s="116" t="s">
         <v>23</v>
       </c>
-      <c r="B66" s="114" t="s">
+      <c r="B66" s="116" t="s">
         <v>210</v>
       </c>
-      <c r="C66" s="114" t="s">
+      <c r="C66" s="116" t="s">
         <v>210</v>
       </c>
       <c r="D66" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="E66" s="114" t="s">
-        <v>1864</v>
-      </c>
-      <c r="F66" s="116" t="s">
-        <v>1863</v>
+      <c r="E66" s="116" t="s">
+        <v>1874</v>
+      </c>
+      <c r="F66" s="118" t="s">
+        <v>1873</v>
       </c>
     </row>
     <row r="67" ht="22.5" customHeight="1">
-      <c r="A67" s="114" t="s">
+      <c r="A67" s="116" t="s">
         <v>23</v>
       </c>
-      <c r="B67" s="114" t="s">
+      <c r="B67" s="116" t="s">
         <v>189</v>
       </c>
-      <c r="C67" s="114" t="s">
+      <c r="C67" s="116" t="s">
         <v>189</v>
       </c>
       <c r="D67" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="E67" s="114" t="s">
+      <c r="E67" s="116" t="s">
         <v>1642</v>
       </c>
-      <c r="F67" s="116" t="s">
-        <v>1860</v>
+      <c r="F67" s="118" t="s">
+        <v>1870</v>
       </c>
     </row>
     <row r="68" ht="22.5" customHeight="1">
-      <c r="A68" s="114" t="s">
+      <c r="A68" s="116" t="s">
         <v>23</v>
       </c>
-      <c r="B68" s="114" t="s">
+      <c r="B68" s="116" t="s">
         <v>205</v>
       </c>
-      <c r="C68" s="114" t="s">
+      <c r="C68" s="116" t="s">
         <v>205</v>
       </c>
       <c r="D68" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="E68" s="114" t="s">
+      <c r="E68" s="116" t="s">
         <v>1643</v>
       </c>
-      <c r="F68" s="116" t="s">
-        <v>1860</v>
+      <c r="F68" s="118" t="s">
+        <v>1870</v>
       </c>
     </row>
     <row r="69" ht="22.5" customHeight="1">
-      <c r="A69" s="114" t="s">
+      <c r="A69" s="116" t="s">
         <v>23</v>
       </c>
-      <c r="B69" s="114" t="s">
+      <c r="B69" s="116" t="s">
         <v>229</v>
       </c>
-      <c r="C69" s="114" t="s">
+      <c r="C69" s="116" t="s">
         <v>229</v>
       </c>
       <c r="D69" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="E69" s="114" t="s">
-        <v>1865</v>
-      </c>
-      <c r="F69" s="116" t="s">
-        <v>1863</v>
+      <c r="E69" s="116" t="s">
+        <v>1875</v>
+      </c>
+      <c r="F69" s="118" t="s">
+        <v>1873</v>
       </c>
     </row>
     <row r="70" ht="22.5" customHeight="1">
-      <c r="A70" s="114" t="s">
+      <c r="A70" s="116" t="s">
         <v>23</v>
       </c>
-      <c r="B70" s="116" t="s">
+      <c r="B70" s="118" t="s">
         <v>132</v>
       </c>
-      <c r="C70" s="116" t="s">
+      <c r="C70" s="118" t="s">
         <v>132</v>
       </c>
       <c r="D70" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="E70" s="116" t="s">
-        <v>1866</v>
-      </c>
-      <c r="F70" s="116" t="s">
-        <v>1860</v>
+      <c r="E70" s="118" t="s">
+        <v>1876</v>
+      </c>
+      <c r="F70" s="118" t="s">
+        <v>1870</v>
       </c>
     </row>
     <row r="71" ht="22.5" customHeight="1">
-      <c r="A71" s="114" t="s">
+      <c r="A71" s="116" t="s">
         <v>29</v>
       </c>
-      <c r="B71" s="114" t="s">
+      <c r="B71" s="116" t="s">
         <v>150</v>
       </c>
-      <c r="C71" s="114" t="s">
+      <c r="C71" s="116" t="s">
         <v>150</v>
       </c>
       <c r="D71" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="E71" s="114" t="s">
+      <c r="E71" s="116" t="s">
         <v>1650</v>
       </c>
-      <c r="F71" s="116" t="s">
-        <v>1860</v>
+      <c r="F71" s="118" t="s">
+        <v>1870</v>
       </c>
     </row>
     <row r="72" ht="22.5" customHeight="1">
-      <c r="A72" s="114" t="s">
+      <c r="A72" s="116" t="s">
         <v>29</v>
       </c>
-      <c r="B72" s="114" t="s">
+      <c r="B72" s="116" t="s">
         <v>123</v>
       </c>
-      <c r="C72" s="114" t="s">
+      <c r="C72" s="116" t="s">
         <v>123</v>
       </c>
       <c r="D72" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="E72" s="114" t="s">
+      <c r="E72" s="116" t="s">
         <v>1653</v>
       </c>
-      <c r="F72" s="116" t="s">
-        <v>1860</v>
+      <c r="F72" s="118" t="s">
+        <v>1870</v>
       </c>
     </row>
     <row r="73" ht="22.5" customHeight="1">
-      <c r="A73" s="114" t="s">
+      <c r="A73" s="116" t="s">
         <v>29</v>
       </c>
-      <c r="B73" s="114" t="s">
+      <c r="B73" s="116" t="s">
         <v>142</v>
       </c>
-      <c r="C73" s="114" t="s">
+      <c r="C73" s="116" t="s">
         <v>142</v>
       </c>
       <c r="D73" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="E73" s="114" t="s">
+      <c r="E73" s="116" t="s">
         <v>1652</v>
       </c>
-      <c r="F73" s="116" t="s">
-        <v>1860</v>
+      <c r="F73" s="118" t="s">
+        <v>1870</v>
       </c>
     </row>
     <row r="74" ht="22.5" customHeight="1">
-      <c r="A74" s="114" t="s">
+      <c r="A74" s="116" t="s">
         <v>29</v>
       </c>
-      <c r="B74" s="114" t="s">
+      <c r="B74" s="116" t="s">
         <v>140</v>
       </c>
-      <c r="C74" s="114" t="s">
+      <c r="C74" s="116" t="s">
         <v>140</v>
       </c>
       <c r="D74" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="E74" s="114" t="s">
+      <c r="E74" s="116" t="s">
         <v>1654</v>
       </c>
-      <c r="F74" s="116" t="s">
-        <v>1860</v>
+      <c r="F74" s="118" t="s">
+        <v>1870</v>
       </c>
     </row>
     <row r="75" ht="22.5" customHeight="1">
-      <c r="A75" s="114" t="s">
+      <c r="A75" s="116" t="s">
         <v>35</v>
       </c>
-      <c r="B75" s="114" t="s">
+      <c r="B75" s="116" t="s">
         <v>191</v>
       </c>
-      <c r="C75" s="114" t="s">
+      <c r="C75" s="116" t="s">
         <v>191</v>
       </c>
       <c r="D75" s="40" t="s">
-        <v>1867</v>
+        <v>1877</v>
       </c>
       <c r="E75" s="41" t="s">
-        <v>1868</v>
-      </c>
-      <c r="F75" s="116"/>
+        <v>1878</v>
+      </c>
+      <c r="F75" s="118"/>
     </row>
     <row r="76" ht="22.5" customHeight="1">
-      <c r="A76" s="114" t="s">
+      <c r="A76" s="116" t="s">
         <v>35</v>
       </c>
-      <c r="B76" s="114" t="s">
-        <v>1869</v>
-      </c>
-      <c r="C76" s="114" t="s">
-        <v>1869</v>
+      <c r="B76" s="116" t="s">
+        <v>1879</v>
+      </c>
+      <c r="C76" s="116" t="s">
+        <v>1879</v>
       </c>
       <c r="D76" s="40" t="s">
-        <v>1867</v>
+        <v>1877</v>
       </c>
       <c r="E76" s="41" t="s">
-        <v>1870</v>
-      </c>
-      <c r="F76" s="116"/>
+        <v>1880</v>
+      </c>
+      <c r="F76" s="118"/>
     </row>
     <row r="77" ht="22.5" customHeight="1">
-      <c r="A77" s="114" t="s">
+      <c r="A77" s="116" t="s">
         <v>35</v>
       </c>
-      <c r="B77" s="114" t="s">
-        <v>1871</v>
-      </c>
-      <c r="C77" s="114" t="s">
-        <v>1871</v>
+      <c r="B77" s="116" t="s">
+        <v>1881</v>
+      </c>
+      <c r="C77" s="116" t="s">
+        <v>1881</v>
       </c>
       <c r="D77" s="40" t="s">
-        <v>1867</v>
+        <v>1877</v>
       </c>
       <c r="E77" s="41" t="s">
-        <v>1872</v>
-      </c>
-      <c r="F77" s="116"/>
+        <v>1882</v>
+      </c>
+      <c r="F77" s="118"/>
     </row>
     <row r="78" ht="22.5" customHeight="1">
-      <c r="A78" s="114" t="s">
+      <c r="A78" s="116" t="s">
         <v>35</v>
       </c>
-      <c r="B78" s="114" t="s">
+      <c r="B78" s="116" t="s">
         <v>1462</v>
       </c>
-      <c r="C78" s="114" t="s">
+      <c r="C78" s="116" t="s">
         <v>1462</v>
       </c>
       <c r="D78" s="40" t="s">
-        <v>1867</v>
+        <v>1877</v>
       </c>
       <c r="E78" s="41" t="s">
-        <v>1873</v>
-      </c>
-      <c r="F78" s="116"/>
+        <v>1883</v>
+      </c>
+      <c r="F78" s="118"/>
     </row>
     <row r="79" ht="22.5" customHeight="1">
-      <c r="A79" s="114" t="s">
+      <c r="A79" s="116" t="s">
         <v>35</v>
       </c>
-      <c r="B79" s="114" t="s">
-        <v>1874</v>
-      </c>
-      <c r="C79" s="114" t="s">
-        <v>1875</v>
+      <c r="B79" s="116" t="s">
+        <v>1884</v>
+      </c>
+      <c r="C79" s="116" t="s">
+        <v>1885</v>
       </c>
       <c r="D79" s="40" t="s">
-        <v>1867</v>
+        <v>1877</v>
       </c>
       <c r="E79" s="41" t="s">
-        <v>1876</v>
-      </c>
-      <c r="F79" s="116"/>
+        <v>1886</v>
+      </c>
+      <c r="F79" s="118"/>
     </row>
     <row r="80" ht="22.5" customHeight="1">
-      <c r="A80" s="114" t="s">
+      <c r="A80" s="116" t="s">
         <v>35</v>
       </c>
-      <c r="B80" s="114" t="s">
+      <c r="B80" s="116" t="s">
+        <v>1887</v>
+      </c>
+      <c r="C80" s="116" t="s">
+        <v>1888</v>
+      </c>
+      <c r="D80" s="40" t="s">
         <v>1877</v>
       </c>
-      <c r="C80" s="114" t="s">
-        <v>1878</v>
-      </c>
-      <c r="D80" s="40" t="s">
-        <v>1867</v>
-      </c>
       <c r="E80" s="41" t="s">
-        <v>1879</v>
-      </c>
-      <c r="F80" s="116"/>
+        <v>1889</v>
+      </c>
+      <c r="F80" s="118"/>
     </row>
     <row r="81" ht="22.5" customHeight="1">
-      <c r="A81" s="114" t="s">
+      <c r="A81" s="116" t="s">
         <v>35</v>
       </c>
-      <c r="B81" s="114" t="s">
-        <v>1880</v>
-      </c>
-      <c r="C81" s="114" t="s">
-        <v>1881</v>
+      <c r="B81" s="116" t="s">
+        <v>1890</v>
+      </c>
+      <c r="C81" s="116" t="s">
+        <v>1891</v>
       </c>
       <c r="D81" s="40" t="s">
-        <v>1867</v>
+        <v>1877</v>
       </c>
       <c r="E81" s="41" t="s">
-        <v>1882</v>
-      </c>
-      <c r="F81" s="116"/>
+        <v>1892</v>
+      </c>
+      <c r="F81" s="118"/>
     </row>
     <row r="82" ht="22.5" customHeight="1">
-      <c r="A82" s="114" t="s">
+      <c r="A82" s="116" t="s">
         <v>35</v>
       </c>
-      <c r="B82" s="114" t="s">
+      <c r="B82" s="116" t="s">
         <v>1029</v>
       </c>
-      <c r="C82" s="114" t="s">
-        <v>1883</v>
+      <c r="C82" s="116" t="s">
+        <v>1893</v>
       </c>
       <c r="D82" s="40" t="s">
-        <v>1867</v>
+        <v>1877</v>
       </c>
       <c r="E82" s="41" t="s">
-        <v>1884</v>
-      </c>
-      <c r="F82" s="116"/>
+        <v>1894</v>
+      </c>
+      <c r="F82" s="118"/>
     </row>
     <row r="83" ht="22.5" customHeight="1">
-      <c r="A83" s="114" t="s">
+      <c r="A83" s="116" t="s">
         <v>35</v>
       </c>
-      <c r="B83" s="114" t="s">
-        <v>1885</v>
-      </c>
-      <c r="C83" s="114" t="s">
-        <v>1886</v>
+      <c r="B83" s="116" t="s">
+        <v>1895</v>
+      </c>
+      <c r="C83" s="116" t="s">
+        <v>1896</v>
       </c>
       <c r="D83" s="40" t="s">
-        <v>1867</v>
+        <v>1877</v>
       </c>
       <c r="E83" s="41" t="s">
-        <v>1887</v>
-      </c>
-      <c r="F83" s="116"/>
+        <v>1897</v>
+      </c>
+      <c r="F83" s="118"/>
     </row>
     <row r="84" ht="22.5" customHeight="1">
-      <c r="A84" s="114" t="s">
+      <c r="A84" s="116" t="s">
         <v>35</v>
       </c>
-      <c r="B84" s="114" t="s">
-        <v>1888</v>
-      </c>
-      <c r="C84" s="114" t="s">
-        <v>1889</v>
+      <c r="B84" s="116" t="s">
+        <v>1898</v>
+      </c>
+      <c r="C84" s="116" t="s">
+        <v>1899</v>
       </c>
       <c r="D84" s="40" t="s">
-        <v>1867</v>
+        <v>1877</v>
       </c>
       <c r="E84" s="41" t="s">
-        <v>1890</v>
-      </c>
-      <c r="F84" s="116"/>
+        <v>1900</v>
+      </c>
+      <c r="F84" s="118"/>
     </row>
     <row r="85" ht="22.5" customHeight="1">
-      <c r="A85" s="114" t="s">
+      <c r="A85" s="116" t="s">
         <v>35</v>
       </c>
-      <c r="B85" s="114" t="s">
-        <v>1891</v>
-      </c>
-      <c r="C85" s="114" t="s">
-        <v>1892</v>
+      <c r="B85" s="116" t="s">
+        <v>1901</v>
+      </c>
+      <c r="C85" s="116" t="s">
+        <v>1902</v>
       </c>
       <c r="D85" s="40" t="s">
-        <v>1867</v>
+        <v>1877</v>
       </c>
       <c r="E85" s="41" t="s">
-        <v>1893</v>
-      </c>
-      <c r="F85" s="116"/>
+        <v>1903</v>
+      </c>
+      <c r="F85" s="118"/>
     </row>
     <row r="86" ht="22.5" customHeight="1">
-      <c r="A86" s="114" t="s">
+      <c r="A86" s="116" t="s">
         <v>35</v>
       </c>
-      <c r="B86" s="114" t="s">
-        <v>1894</v>
-      </c>
-      <c r="C86" s="114" t="s">
-        <v>1895</v>
+      <c r="B86" s="116" t="s">
+        <v>1904</v>
+      </c>
+      <c r="C86" s="116" t="s">
+        <v>1905</v>
       </c>
       <c r="D86" s="40" t="s">
-        <v>1867</v>
+        <v>1877</v>
       </c>
       <c r="E86" s="41" t="s">
-        <v>1896</v>
-      </c>
-      <c r="F86" s="116"/>
+        <v>1906</v>
+      </c>
+      <c r="F86" s="118"/>
     </row>
     <row r="87" ht="22.5" customHeight="1">
-      <c r="A87" s="114" t="s">
+      <c r="A87" s="116" t="s">
         <v>35</v>
       </c>
-      <c r="B87" s="114" t="s">
-        <v>1897</v>
-      </c>
-      <c r="C87" s="114" t="s">
-        <v>1897</v>
+      <c r="B87" s="116" t="s">
+        <v>1907</v>
+      </c>
+      <c r="C87" s="116" t="s">
+        <v>1907</v>
       </c>
       <c r="D87" s="40" t="s">
-        <v>1867</v>
+        <v>1877</v>
       </c>
       <c r="E87" s="41" t="s">
-        <v>1898</v>
-      </c>
-      <c r="F87" s="116"/>
+        <v>1908</v>
+      </c>
+      <c r="F87" s="118"/>
     </row>
     <row r="88" ht="22.5" customHeight="1">
-      <c r="A88" s="114" t="s">
+      <c r="A88" s="116" t="s">
         <v>35</v>
       </c>
-      <c r="B88" s="114" t="s">
-        <v>1899</v>
-      </c>
-      <c r="C88" s="114" t="s">
-        <v>1899</v>
+      <c r="B88" s="116" t="s">
+        <v>1909</v>
+      </c>
+      <c r="C88" s="116" t="s">
+        <v>1909</v>
       </c>
       <c r="D88" s="40" t="s">
-        <v>1867</v>
+        <v>1877</v>
       </c>
       <c r="E88" s="41" t="s">
-        <v>1900</v>
-      </c>
-      <c r="F88" s="116"/>
+        <v>1910</v>
+      </c>
+      <c r="F88" s="118"/>
     </row>
     <row r="89" ht="22.5" customHeight="1">
-      <c r="A89" s="114" t="s">
+      <c r="A89" s="116" t="s">
         <v>35</v>
       </c>
-      <c r="B89" s="114" t="s">
-        <v>1901</v>
-      </c>
-      <c r="C89" s="114" t="s">
-        <v>1901</v>
+      <c r="B89" s="116" t="s">
+        <v>1911</v>
+      </c>
+      <c r="C89" s="116" t="s">
+        <v>1911</v>
       </c>
       <c r="D89" s="40" t="s">
-        <v>1867</v>
+        <v>1877</v>
       </c>
       <c r="E89" s="41" t="s">
-        <v>1902</v>
-      </c>
-      <c r="F89" s="116"/>
+        <v>1912</v>
+      </c>
+      <c r="F89" s="118"/>
     </row>
     <row r="90" ht="22.5" customHeight="1">
-      <c r="A90" s="114" t="s">
+      <c r="A90" s="116" t="s">
         <v>35</v>
       </c>
-      <c r="B90" s="114" t="s">
-        <v>1903</v>
-      </c>
-      <c r="C90" s="114" t="s">
-        <v>1903</v>
+      <c r="B90" s="116" t="s">
+        <v>1913</v>
+      </c>
+      <c r="C90" s="116" t="s">
+        <v>1913</v>
       </c>
       <c r="D90" s="40" t="s">
-        <v>1867</v>
+        <v>1877</v>
       </c>
       <c r="E90" s="41" t="s">
-        <v>1904</v>
-      </c>
-      <c r="F90" s="116"/>
+        <v>1914</v>
+      </c>
+      <c r="F90" s="118"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -16312,7 +16456,7 @@
         <v>50</v>
       </c>
       <c r="D1" s="20" t="s">
-        <v>1905</v>
+        <v>1915</v>
       </c>
       <c r="E1" s="20" t="s">
         <v>261</v>
@@ -16329,14 +16473,14 @@
         <v>57</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>1906</v>
+        <v>1916</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>1907</v>
+        <v>1917</v>
       </c>
       <c r="E2" s="21"/>
-      <c r="F2" s="108" t="s">
-        <v>1908</v>
+      <c r="F2" s="110" t="s">
+        <v>1918</v>
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1">
@@ -16347,14 +16491,14 @@
         <v>57</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>1909</v>
+        <v>1919</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>1910</v>
+        <v>1920</v>
       </c>
       <c r="E3" s="22"/>
-      <c r="F3" s="109" t="s">
-        <v>1911</v>
+      <c r="F3" s="111" t="s">
+        <v>1921</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
@@ -16365,14 +16509,14 @@
         <v>61</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>1912</v>
+        <v>1922</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>1913</v>
+        <v>1923</v>
       </c>
       <c r="E4" s="21"/>
       <c r="F4" s="53" t="s">
-        <v>1914</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1">
@@ -16383,14 +16527,14 @@
         <v>64</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>1906</v>
+        <v>1916</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>1915</v>
+        <v>1925</v>
       </c>
       <c r="E5" s="22"/>
-      <c r="F5" s="109" t="s">
-        <v>1916</v>
+      <c r="F5" s="111" t="s">
+        <v>1926</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1">
@@ -16401,14 +16545,14 @@
         <v>67</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>1912</v>
+        <v>1922</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>1917</v>
+        <v>1927</v>
       </c>
       <c r="E6" s="21"/>
-      <c r="F6" s="108" t="s">
-        <v>1918</v>
+      <c r="F6" s="110" t="s">
+        <v>1928</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
@@ -16419,14 +16563,14 @@
         <v>67</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>1919</v>
+        <v>1929</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>1920</v>
+        <v>1930</v>
       </c>
       <c r="E7" s="22"/>
-      <c r="F7" s="109" t="s">
-        <v>1921</v>
+      <c r="F7" s="111" t="s">
+        <v>1931</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
@@ -16437,14 +16581,14 @@
         <v>70</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>1912</v>
+        <v>1922</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>1922</v>
+        <v>1932</v>
       </c>
       <c r="E8" s="21"/>
-      <c r="F8" s="108" t="s">
-        <v>1923</v>
+      <c r="F8" s="110" t="s">
+        <v>1933</v>
       </c>
     </row>
     <row r="9" ht="22.5" customHeight="1">
@@ -16455,14 +16599,14 @@
         <v>70</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>1919</v>
+        <v>1929</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>1924</v>
+        <v>1934</v>
       </c>
       <c r="E9" s="22"/>
-      <c r="F9" s="109" t="s">
-        <v>1925</v>
+      <c r="F9" s="111" t="s">
+        <v>1935</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
@@ -16473,14 +16617,14 @@
         <v>70</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>1926</v>
+        <v>1936</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>1927</v>
+        <v>1937</v>
       </c>
       <c r="E10" s="21"/>
-      <c r="F10" s="108" t="s">
-        <v>1928</v>
+      <c r="F10" s="110" t="s">
+        <v>1938</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
@@ -16491,14 +16635,14 @@
         <v>70</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>1929</v>
+        <v>1939</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>1930</v>
+        <v>1940</v>
       </c>
       <c r="E11" s="22"/>
-      <c r="F11" s="109" t="s">
-        <v>1931</v>
+      <c r="F11" s="111" t="s">
+        <v>1941</v>
       </c>
     </row>
     <row r="12" ht="22.5" customHeight="1">
@@ -16509,14 +16653,14 @@
         <v>71</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>1932</v>
+        <v>1942</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>1933</v>
+        <v>1943</v>
       </c>
       <c r="E12" s="21"/>
-      <c r="F12" s="108" t="s">
-        <v>1934</v>
+      <c r="F12" s="110" t="s">
+        <v>1944</v>
       </c>
     </row>
     <row r="13" ht="22.5" customHeight="1">
@@ -16527,14 +16671,14 @@
         <v>71</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>1912</v>
+        <v>1922</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>1935</v>
+        <v>1945</v>
       </c>
       <c r="E13" s="22"/>
-      <c r="F13" s="109" t="s">
-        <v>1936</v>
+      <c r="F13" s="111" t="s">
+        <v>1946</v>
       </c>
     </row>
     <row r="14" ht="22.5" customHeight="1">
@@ -16545,14 +16689,14 @@
         <v>71</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>1919</v>
+        <v>1929</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>1937</v>
+        <v>1947</v>
       </c>
       <c r="E14" s="21"/>
-      <c r="F14" s="108" t="s">
-        <v>1938</v>
+      <c r="F14" s="110" t="s">
+        <v>1948</v>
       </c>
     </row>
     <row r="15" ht="22.5" customHeight="1">
@@ -16563,14 +16707,14 @@
         <v>73</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>1912</v>
+        <v>1922</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>1939</v>
+        <v>1949</v>
       </c>
       <c r="E15" s="22"/>
-      <c r="F15" s="109" t="s">
-        <v>1940</v>
+      <c r="F15" s="111" t="s">
+        <v>1950</v>
       </c>
     </row>
     <row r="16" ht="22.5" customHeight="1">
@@ -16581,14 +16725,14 @@
         <v>73</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>1919</v>
+        <v>1929</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>1941</v>
+        <v>1951</v>
       </c>
       <c r="E16" s="21"/>
-      <c r="F16" s="108" t="s">
-        <v>1942</v>
+      <c r="F16" s="110" t="s">
+        <v>1952</v>
       </c>
     </row>
     <row r="17" ht="22.5" customHeight="1">
@@ -16599,14 +16743,14 @@
         <v>76</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>1912</v>
+        <v>1922</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>1943</v>
+        <v>1953</v>
       </c>
       <c r="E17" s="22"/>
-      <c r="F17" s="109" t="s">
-        <v>1944</v>
+      <c r="F17" s="111" t="s">
+        <v>1954</v>
       </c>
     </row>
     <row r="18" ht="22.5" customHeight="1">
@@ -16617,14 +16761,14 @@
         <v>78</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>1912</v>
+        <v>1922</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>1945</v>
+        <v>1955</v>
       </c>
       <c r="E18" s="21"/>
-      <c r="F18" s="108" t="s">
-        <v>1908</v>
+      <c r="F18" s="110" t="s">
+        <v>1918</v>
       </c>
     </row>
     <row r="19" ht="22.5" customHeight="1">
@@ -16635,14 +16779,14 @@
         <v>78</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>1906</v>
+        <v>1916</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>1946</v>
+        <v>1956</v>
       </c>
       <c r="E19" s="22"/>
-      <c r="F19" s="109" t="s">
-        <v>1947</v>
+      <c r="F19" s="111" t="s">
+        <v>1957</v>
       </c>
     </row>
     <row r="20" ht="22.5" customHeight="1">
@@ -16653,14 +16797,14 @@
         <v>78</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>1948</v>
+        <v>1958</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>1949</v>
+        <v>1959</v>
       </c>
       <c r="E20" s="21"/>
-      <c r="F20" s="108" t="s">
-        <v>1950</v>
+      <c r="F20" s="110" t="s">
+        <v>1960</v>
       </c>
     </row>
     <row r="21" ht="22.5" customHeight="1">
@@ -16671,14 +16815,14 @@
         <v>79</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>1912</v>
+        <v>1922</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>1951</v>
+        <v>1961</v>
       </c>
       <c r="E21" s="22"/>
-      <c r="F21" s="109" t="s">
-        <v>1952</v>
+      <c r="F21" s="111" t="s">
+        <v>1962</v>
       </c>
     </row>
     <row r="22" ht="22.5" customHeight="1">
@@ -16689,14 +16833,14 @@
         <v>80</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>1906</v>
+        <v>1916</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>1953</v>
+        <v>1963</v>
       </c>
       <c r="E22" s="21"/>
-      <c r="F22" s="108" t="s">
-        <v>1954</v>
+      <c r="F22" s="110" t="s">
+        <v>1964</v>
       </c>
     </row>
     <row r="23" ht="22.5" customHeight="1">
@@ -16707,14 +16851,14 @@
         <v>81</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>1906</v>
+        <v>1916</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>1955</v>
+        <v>1965</v>
       </c>
       <c r="E23" s="22"/>
-      <c r="F23" s="109" t="s">
-        <v>1956</v>
+      <c r="F23" s="111" t="s">
+        <v>1966</v>
       </c>
     </row>
     <row r="24" ht="22.5" customHeight="1">
@@ -16725,14 +16869,14 @@
         <v>81</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>1919</v>
+        <v>1929</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>1957</v>
+        <v>1967</v>
       </c>
       <c r="E24" s="21"/>
-      <c r="F24" s="108" t="s">
-        <v>1958</v>
+      <c r="F24" s="110" t="s">
+        <v>1968</v>
       </c>
     </row>
     <row r="25" ht="22.5" customHeight="1">
@@ -16740,17 +16884,17 @@
         <v>10</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>1959</v>
+        <v>1969</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>1912</v>
+        <v>1922</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>1960</v>
+        <v>1970</v>
       </c>
       <c r="E25" s="22"/>
-      <c r="F25" s="109" t="s">
-        <v>1961</v>
+      <c r="F25" s="111" t="s">
+        <v>1971</v>
       </c>
     </row>
     <row r="26" ht="22.5" customHeight="1">
@@ -16761,14 +16905,14 @@
         <v>82</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>1906</v>
+        <v>1916</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>1962</v>
+        <v>1972</v>
       </c>
       <c r="E26" s="21"/>
-      <c r="F26" s="108" t="s">
-        <v>1963</v>
+      <c r="F26" s="110" t="s">
+        <v>1973</v>
       </c>
     </row>
     <row r="27" ht="22.5" customHeight="1">
@@ -16779,14 +16923,14 @@
         <v>82</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>1926</v>
+        <v>1936</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>1964</v>
+        <v>1974</v>
       </c>
       <c r="E27" s="22"/>
-      <c r="F27" s="109" t="s">
-        <v>1965</v>
+      <c r="F27" s="111" t="s">
+        <v>1975</v>
       </c>
     </row>
     <row r="28" ht="22.5" customHeight="1">
@@ -16797,14 +16941,14 @@
         <v>83</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>1906</v>
+        <v>1916</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>1966</v>
+        <v>1976</v>
       </c>
       <c r="E28" s="21"/>
-      <c r="F28" s="108" t="s">
-        <v>1967</v>
+      <c r="F28" s="110" t="s">
+        <v>1977</v>
       </c>
     </row>
     <row r="29" ht="22.5" customHeight="1">
@@ -16812,17 +16956,17 @@
         <v>10</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>1968</v>
+        <v>1978</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>1906</v>
+        <v>1916</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>1969</v>
+        <v>1979</v>
       </c>
       <c r="E29" s="22"/>
-      <c r="F29" s="109" t="s">
-        <v>1970</v>
+      <c r="F29" s="111" t="s">
+        <v>1980</v>
       </c>
     </row>
     <row r="30" ht="22.5" customHeight="1">
@@ -16833,14 +16977,14 @@
         <v>84</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>1912</v>
+        <v>1922</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>1971</v>
+        <v>1981</v>
       </c>
       <c r="E30" s="21"/>
-      <c r="F30" s="108" t="s">
-        <v>1972</v>
+      <c r="F30" s="110" t="s">
+        <v>1982</v>
       </c>
     </row>
     <row r="31" ht="22.5" customHeight="1">
@@ -16851,14 +16995,14 @@
         <v>85</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>1912</v>
+        <v>1922</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>1973</v>
+        <v>1983</v>
       </c>
       <c r="E31" s="22"/>
-      <c r="F31" s="109" t="s">
-        <v>1974</v>
+      <c r="F31" s="111" t="s">
+        <v>1984</v>
       </c>
     </row>
     <row r="32" ht="22.5" customHeight="1">
@@ -16869,14 +17013,14 @@
         <v>85</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>1906</v>
+        <v>1916</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>1975</v>
+        <v>1985</v>
       </c>
       <c r="E32" s="21"/>
-      <c r="F32" s="108" t="s">
-        <v>1976</v>
+      <c r="F32" s="110" t="s">
+        <v>1986</v>
       </c>
     </row>
     <row r="33" ht="22.5" customHeight="1">
@@ -16887,14 +17031,14 @@
         <v>86</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>1912</v>
+        <v>1922</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>1977</v>
+        <v>1987</v>
       </c>
       <c r="E33" s="22"/>
-      <c r="F33" s="109" t="s">
-        <v>1978</v>
+      <c r="F33" s="111" t="s">
+        <v>1988</v>
       </c>
     </row>
     <row r="34" ht="22.5" customHeight="1">
@@ -16905,14 +17049,14 @@
         <v>86</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>1906</v>
+        <v>1916</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>1979</v>
+        <v>1989</v>
       </c>
       <c r="E34" s="21"/>
-      <c r="F34" s="108" t="s">
-        <v>1980</v>
+      <c r="F34" s="110" t="s">
+        <v>1990</v>
       </c>
     </row>
     <row r="35" ht="22.5" customHeight="1">
@@ -16923,14 +17067,14 @@
         <v>86</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>1929</v>
+        <v>1939</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>1981</v>
+        <v>1991</v>
       </c>
       <c r="E35" s="22"/>
-      <c r="F35" s="109" t="s">
-        <v>1982</v>
+      <c r="F35" s="111" t="s">
+        <v>1992</v>
       </c>
     </row>
     <row r="36" ht="22.5" customHeight="1">
@@ -16941,14 +17085,14 @@
         <v>87</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>1912</v>
+        <v>1922</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>1983</v>
+        <v>1993</v>
       </c>
       <c r="E36" s="21"/>
-      <c r="F36" s="108" t="s">
-        <v>1954</v>
+      <c r="F36" s="110" t="s">
+        <v>1964</v>
       </c>
     </row>
     <row r="37" ht="22.5" customHeight="1">
@@ -16959,14 +17103,14 @@
         <v>87</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>1984</v>
+        <v>1994</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>1985</v>
+        <v>1995</v>
       </c>
       <c r="E37" s="22"/>
-      <c r="F37" s="109" t="s">
-        <v>1986</v>
+      <c r="F37" s="111" t="s">
+        <v>1996</v>
       </c>
     </row>
     <row r="38" ht="22.5" customHeight="1">
@@ -16977,14 +17121,14 @@
         <v>88</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>1906</v>
+        <v>1916</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>1987</v>
+        <v>1997</v>
       </c>
       <c r="E38" s="21"/>
-      <c r="F38" s="108" t="s">
-        <v>1988</v>
+      <c r="F38" s="110" t="s">
+        <v>1998</v>
       </c>
     </row>
     <row r="39" ht="22.5" customHeight="1">
@@ -16995,14 +17139,14 @@
         <v>89</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>1912</v>
+        <v>1922</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>1989</v>
+        <v>1999</v>
       </c>
       <c r="E39" s="22"/>
-      <c r="F39" s="109" t="s">
-        <v>1990</v>
+      <c r="F39" s="111" t="s">
+        <v>2000</v>
       </c>
     </row>
     <row r="40" ht="22.5" customHeight="1">
@@ -17013,14 +17157,14 @@
         <v>92</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>1912</v>
+        <v>1922</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>1991</v>
+        <v>2001</v>
       </c>
       <c r="E40" s="21"/>
-      <c r="F40" s="108" t="s">
-        <v>1992</v>
+      <c r="F40" s="110" t="s">
+        <v>2002</v>
       </c>
     </row>
     <row r="41" ht="22.5" customHeight="1">
@@ -17031,14 +17175,14 @@
         <v>93</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>1912</v>
+        <v>1922</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>1993</v>
+        <v>2003</v>
       </c>
       <c r="E41" s="22"/>
-      <c r="F41" s="109" t="s">
-        <v>1994</v>
+      <c r="F41" s="111" t="s">
+        <v>2004</v>
       </c>
     </row>
     <row r="42" ht="22.5" customHeight="1">
@@ -17049,14 +17193,14 @@
         <v>94</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>1912</v>
+        <v>1922</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>1995</v>
+        <v>2005</v>
       </c>
       <c r="E42" s="21"/>
-      <c r="F42" s="108" t="s">
-        <v>1996</v>
+      <c r="F42" s="110" t="s">
+        <v>2006</v>
       </c>
     </row>
     <row r="43" ht="22.5" customHeight="1">
@@ -17067,14 +17211,14 @@
         <v>94</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>1906</v>
+        <v>1916</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>1997</v>
+        <v>2007</v>
       </c>
       <c r="E43" s="22"/>
-      <c r="F43" s="109" t="s">
-        <v>1998</v>
+      <c r="F43" s="111" t="s">
+        <v>2008</v>
       </c>
     </row>
     <row r="44" ht="22.5" customHeight="1">
@@ -17085,14 +17229,14 @@
         <v>94</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>1984</v>
+        <v>1994</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>1999</v>
+        <v>2009</v>
       </c>
       <c r="E44" s="21"/>
-      <c r="F44" s="108" t="s">
-        <v>2000</v>
+      <c r="F44" s="110" t="s">
+        <v>2010</v>
       </c>
     </row>
     <row r="45" ht="22.5" customHeight="1">
@@ -17103,14 +17247,14 @@
         <v>94</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>1909</v>
+        <v>1919</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>2001</v>
+        <v>2011</v>
       </c>
       <c r="E45" s="22"/>
-      <c r="F45" s="109" t="s">
-        <v>2002</v>
+      <c r="F45" s="111" t="s">
+        <v>2012</v>
       </c>
     </row>
     <row r="46" ht="22.5" customHeight="1">
@@ -17121,14 +17265,14 @@
         <v>96</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>1912</v>
+        <v>1922</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>2003</v>
+        <v>2013</v>
       </c>
       <c r="E46" s="21"/>
-      <c r="F46" s="108" t="s">
-        <v>2004</v>
+      <c r="F46" s="110" t="s">
+        <v>2014</v>
       </c>
     </row>
     <row r="47" ht="22.5" customHeight="1">
@@ -17139,14 +17283,14 @@
         <v>96</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>1906</v>
+        <v>1916</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>2005</v>
+        <v>2015</v>
       </c>
       <c r="E47" s="22"/>
-      <c r="F47" s="109" t="s">
-        <v>2006</v>
+      <c r="F47" s="111" t="s">
+        <v>2016</v>
       </c>
     </row>
     <row r="48" ht="22.5" customHeight="1">
@@ -17157,14 +17301,14 @@
         <v>96</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>1926</v>
+        <v>1936</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>2007</v>
+        <v>2017</v>
       </c>
       <c r="E48" s="21"/>
-      <c r="F48" s="108" t="s">
-        <v>2008</v>
+      <c r="F48" s="110" t="s">
+        <v>2018</v>
       </c>
     </row>
     <row r="49" ht="22.5" customHeight="1">
@@ -17175,14 +17319,14 @@
         <v>97</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>1919</v>
+        <v>1929</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>2009</v>
+        <v>2019</v>
       </c>
       <c r="E49" s="22"/>
-      <c r="F49" s="109" t="s">
-        <v>2010</v>
+      <c r="F49" s="111" t="s">
+        <v>2020</v>
       </c>
     </row>
     <row r="50" ht="22.5" customHeight="1">
@@ -17193,14 +17337,14 @@
         <v>97</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>1926</v>
+        <v>1936</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>2011</v>
+        <v>2021</v>
       </c>
       <c r="E50" s="21"/>
-      <c r="F50" s="108" t="s">
-        <v>2012</v>
+      <c r="F50" s="110" t="s">
+        <v>2022</v>
       </c>
     </row>
     <row r="51" ht="22.5" customHeight="1">
@@ -17211,14 +17355,14 @@
         <v>97</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>1929</v>
+        <v>1939</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>2013</v>
+        <v>2023</v>
       </c>
       <c r="E51" s="22"/>
-      <c r="F51" s="109" t="s">
-        <v>2014</v>
+      <c r="F51" s="111" t="s">
+        <v>2024</v>
       </c>
     </row>
     <row r="52" ht="22.5" customHeight="1">
@@ -17229,14 +17373,14 @@
         <v>98</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>1912</v>
+        <v>1922</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="E52" s="21"/>
-      <c r="F52" s="108" t="s">
-        <v>2016</v>
+      <c r="F52" s="110" t="s">
+        <v>2026</v>
       </c>
     </row>
     <row r="53" ht="22.5" customHeight="1">
@@ -17247,14 +17391,14 @@
         <v>99</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>1912</v>
+        <v>1922</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>2017</v>
+        <v>2027</v>
       </c>
       <c r="E53" s="22"/>
-      <c r="F53" s="109" t="s">
-        <v>2018</v>
+      <c r="F53" s="111" t="s">
+        <v>2028</v>
       </c>
     </row>
     <row r="54" ht="22.5" customHeight="1">
@@ -17265,14 +17409,14 @@
         <v>99</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>1919</v>
+        <v>1929</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>2019</v>
+        <v>2029</v>
       </c>
       <c r="E54" s="21"/>
-      <c r="F54" s="108" t="s">
-        <v>2020</v>
+      <c r="F54" s="110" t="s">
+        <v>2030</v>
       </c>
     </row>
     <row r="55" ht="22.5" customHeight="1">
@@ -17283,14 +17427,14 @@
         <v>99</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>2021</v>
+        <v>2031</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>2022</v>
+        <v>2032</v>
       </c>
       <c r="E55" s="22"/>
-      <c r="F55" s="109" t="s">
-        <v>2023</v>
+      <c r="F55" s="111" t="s">
+        <v>2033</v>
       </c>
     </row>
     <row r="56" ht="22.5" customHeight="1">
@@ -17301,14 +17445,14 @@
         <v>100</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>1912</v>
+        <v>1922</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>2024</v>
+        <v>2034</v>
       </c>
       <c r="E56" s="21"/>
-      <c r="F56" s="108" t="s">
-        <v>2025</v>
+      <c r="F56" s="110" t="s">
+        <v>2035</v>
       </c>
     </row>
     <row r="57" ht="22.5" customHeight="1">
@@ -17319,14 +17463,14 @@
         <v>101</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>1912</v>
+        <v>1922</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>2026</v>
+        <v>2036</v>
       </c>
       <c r="E57" s="22"/>
-      <c r="F57" s="109" t="s">
-        <v>2027</v>
+      <c r="F57" s="111" t="s">
+        <v>2037</v>
       </c>
     </row>
     <row r="58" ht="22.5" customHeight="1">
@@ -17337,14 +17481,14 @@
         <v>101</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>1919</v>
+        <v>1929</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>2028</v>
+        <v>2038</v>
       </c>
       <c r="E58" s="21"/>
-      <c r="F58" s="108" t="s">
-        <v>2029</v>
+      <c r="F58" s="110" t="s">
+        <v>2039</v>
       </c>
     </row>
     <row r="59" ht="22.5" customHeight="1">
@@ -17355,14 +17499,14 @@
         <v>101</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>1909</v>
+        <v>1919</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>2030</v>
+        <v>2040</v>
       </c>
       <c r="E59" s="22"/>
-      <c r="F59" s="109" t="s">
-        <v>2002</v>
+      <c r="F59" s="111" t="s">
+        <v>2012</v>
       </c>
     </row>
     <row r="60" ht="22.5" customHeight="1">
@@ -17373,14 +17517,14 @@
         <v>102</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>1932</v>
+        <v>1942</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>2031</v>
+        <v>2041</v>
       </c>
       <c r="E60" s="21"/>
-      <c r="F60" s="108" t="s">
-        <v>2032</v>
+      <c r="F60" s="110" t="s">
+        <v>2042</v>
       </c>
     </row>
     <row r="61" ht="22.5" customHeight="1">
@@ -17391,14 +17535,14 @@
         <v>102</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>1919</v>
+        <v>1929</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>2033</v>
+        <v>2043</v>
       </c>
       <c r="E61" s="22"/>
-      <c r="F61" s="109" t="s">
-        <v>2034</v>
+      <c r="F61" s="111" t="s">
+        <v>2044</v>
       </c>
     </row>
     <row r="62" ht="22.5" customHeight="1">
@@ -17409,14 +17553,14 @@
         <v>102</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>1984</v>
+        <v>1994</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>2035</v>
+        <v>2045</v>
       </c>
       <c r="E62" s="21"/>
-      <c r="F62" s="108" t="s">
-        <v>2036</v>
+      <c r="F62" s="110" t="s">
+        <v>2046</v>
       </c>
     </row>
     <row r="63" ht="22.5" customHeight="1">
@@ -17427,14 +17571,14 @@
         <v>104</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>1912</v>
+        <v>1922</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>2037</v>
+        <v>2047</v>
       </c>
       <c r="E63" s="22"/>
-      <c r="F63" s="109" t="s">
-        <v>2038</v>
+      <c r="F63" s="111" t="s">
+        <v>2048</v>
       </c>
     </row>
     <row r="64" ht="22.5" customHeight="1">
@@ -17445,14 +17589,14 @@
         <v>104</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>1919</v>
+        <v>1929</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>2039</v>
+        <v>2049</v>
       </c>
       <c r="E64" s="21"/>
-      <c r="F64" s="108" t="s">
-        <v>2040</v>
+      <c r="F64" s="110" t="s">
+        <v>2050</v>
       </c>
     </row>
     <row r="65" ht="22.5" customHeight="1">
@@ -17460,17 +17604,17 @@
         <v>10</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>2041</v>
+        <v>2051</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>1906</v>
+        <v>1916</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>2042</v>
+        <v>2052</v>
       </c>
       <c r="E65" s="22"/>
-      <c r="F65" s="109" t="s">
-        <v>2043</v>
+      <c r="F65" s="111" t="s">
+        <v>2053</v>
       </c>
     </row>
     <row r="66" ht="22.5" customHeight="1">
@@ -17481,14 +17625,14 @@
         <v>107</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>1912</v>
+        <v>1922</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>2044</v>
+        <v>2054</v>
       </c>
       <c r="E66" s="21"/>
-      <c r="F66" s="108" t="s">
-        <v>2045</v>
+      <c r="F66" s="110" t="s">
+        <v>2055</v>
       </c>
     </row>
     <row r="67" ht="22.5" customHeight="1">
@@ -17499,14 +17643,14 @@
         <v>108</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>1912</v>
+        <v>1922</v>
       </c>
       <c r="D67" s="9" t="s">
-        <v>2046</v>
+        <v>2056</v>
       </c>
       <c r="E67" s="22"/>
-      <c r="F67" s="109" t="s">
-        <v>2047</v>
+      <c r="F67" s="111" t="s">
+        <v>2057</v>
       </c>
     </row>
     <row r="68" ht="22.5" customHeight="1">
@@ -17517,14 +17661,14 @@
         <v>108</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>1906</v>
+        <v>1916</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>2048</v>
+        <v>2058</v>
       </c>
       <c r="E68" s="21"/>
-      <c r="F68" s="108" t="s">
-        <v>2049</v>
+      <c r="F68" s="110" t="s">
+        <v>2059</v>
       </c>
     </row>
     <row r="69" ht="22.5" customHeight="1">
@@ -17535,14 +17679,14 @@
         <v>109</v>
       </c>
       <c r="C69" s="9" t="s">
-        <v>1912</v>
+        <v>1922</v>
       </c>
       <c r="D69" s="9" t="s">
-        <v>2050</v>
+        <v>2060</v>
       </c>
       <c r="E69" s="22"/>
-      <c r="F69" s="109" t="s">
-        <v>2051</v>
+      <c r="F69" s="111" t="s">
+        <v>2061</v>
       </c>
     </row>
     <row r="70" ht="22.5" customHeight="1">
@@ -17553,14 +17697,14 @@
         <v>109</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>1906</v>
+        <v>1916</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>2052</v>
+        <v>2062</v>
       </c>
       <c r="E70" s="21"/>
-      <c r="F70" s="108" t="s">
-        <v>2053</v>
+      <c r="F70" s="110" t="s">
+        <v>2063</v>
       </c>
     </row>
     <row r="71" ht="22.5" customHeight="1">
@@ -17571,14 +17715,14 @@
         <v>109</v>
       </c>
       <c r="C71" s="9" t="s">
-        <v>1926</v>
+        <v>1936</v>
       </c>
       <c r="D71" s="9" t="s">
-        <v>2054</v>
+        <v>2064</v>
       </c>
       <c r="E71" s="22"/>
-      <c r="F71" s="109" t="s">
-        <v>2055</v>
+      <c r="F71" s="111" t="s">
+        <v>2065</v>
       </c>
     </row>
     <row r="72" ht="22.5" customHeight="1">
@@ -17589,14 +17733,14 @@
         <v>110</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>1906</v>
+        <v>1916</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>2056</v>
+        <v>2066</v>
       </c>
       <c r="E72" s="21"/>
-      <c r="F72" s="108" t="s">
-        <v>2057</v>
+      <c r="F72" s="110" t="s">
+        <v>2067</v>
       </c>
     </row>
     <row r="73" ht="22.5" customHeight="1">
@@ -17607,14 +17751,14 @@
         <v>111</v>
       </c>
       <c r="C73" s="9" t="s">
-        <v>1932</v>
+        <v>1942</v>
       </c>
       <c r="D73" s="9" t="s">
-        <v>2058</v>
+        <v>2068</v>
       </c>
       <c r="E73" s="22"/>
-      <c r="F73" s="109" t="s">
-        <v>2059</v>
+      <c r="F73" s="111" t="s">
+        <v>2069</v>
       </c>
     </row>
     <row r="74" ht="22.5" customHeight="1">
@@ -17625,14 +17769,14 @@
         <v>111</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>1912</v>
+        <v>1922</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>2060</v>
+        <v>2070</v>
       </c>
       <c r="E74" s="21"/>
-      <c r="F74" s="108" t="s">
-        <v>2061</v>
+      <c r="F74" s="110" t="s">
+        <v>2071</v>
       </c>
     </row>
     <row r="75" ht="22.5" customHeight="1">
@@ -17643,14 +17787,14 @@
         <v>112</v>
       </c>
       <c r="C75" s="9" t="s">
-        <v>1932</v>
+        <v>1942</v>
       </c>
       <c r="D75" s="9" t="s">
-        <v>2062</v>
+        <v>2072</v>
       </c>
       <c r="E75" s="22"/>
-      <c r="F75" s="109" t="s">
-        <v>2063</v>
+      <c r="F75" s="111" t="s">
+        <v>2073</v>
       </c>
     </row>
     <row r="76" ht="22.5" customHeight="1">
@@ -17661,14 +17805,14 @@
         <v>112</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>1912</v>
+        <v>1922</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>2064</v>
+        <v>2074</v>
       </c>
       <c r="E76" s="21"/>
-      <c r="F76" s="108" t="s">
-        <v>2065</v>
+      <c r="F76" s="110" t="s">
+        <v>2075</v>
       </c>
     </row>
     <row r="77" ht="22.5" customHeight="1">
@@ -17679,14 +17823,14 @@
         <v>113</v>
       </c>
       <c r="C77" s="9" t="s">
-        <v>1912</v>
+        <v>1922</v>
       </c>
       <c r="D77" s="9" t="s">
-        <v>2066</v>
+        <v>2076</v>
       </c>
       <c r="E77" s="22"/>
-      <c r="F77" s="109" t="s">
-        <v>2067</v>
+      <c r="F77" s="111" t="s">
+        <v>2077</v>
       </c>
     </row>
     <row r="78" ht="22.5" customHeight="1">
@@ -17697,14 +17841,14 @@
         <v>113</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>1919</v>
+        <v>1929</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>2068</v>
+        <v>2078</v>
       </c>
       <c r="E78" s="21"/>
-      <c r="F78" s="108" t="s">
-        <v>2069</v>
+      <c r="F78" s="110" t="s">
+        <v>2079</v>
       </c>
     </row>
     <row r="79" ht="22.5" customHeight="1">
@@ -17715,14 +17859,14 @@
         <v>114</v>
       </c>
       <c r="C79" s="9" t="s">
-        <v>1906</v>
+        <v>1916</v>
       </c>
       <c r="D79" s="9" t="s">
-        <v>2070</v>
+        <v>2080</v>
       </c>
       <c r="E79" s="22"/>
-      <c r="F79" s="109" t="s">
-        <v>2071</v>
+      <c r="F79" s="111" t="s">
+        <v>2081</v>
       </c>
     </row>
     <row r="80" ht="22.5" customHeight="1">
@@ -17733,14 +17877,14 @@
         <v>114</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>2072</v>
+        <v>2082</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>2073</v>
+        <v>2083</v>
       </c>
       <c r="E80" s="21"/>
-      <c r="F80" s="108" t="s">
-        <v>2074</v>
+      <c r="F80" s="110" t="s">
+        <v>2084</v>
       </c>
     </row>
     <row r="81" ht="22.5" customHeight="1">
@@ -17751,14 +17895,14 @@
         <v>115</v>
       </c>
       <c r="C81" s="9" t="s">
-        <v>1932</v>
+        <v>1942</v>
       </c>
       <c r="D81" s="9" t="s">
-        <v>2075</v>
+        <v>2085</v>
       </c>
       <c r="E81" s="22"/>
-      <c r="F81" s="109" t="s">
-        <v>2076</v>
+      <c r="F81" s="111" t="s">
+        <v>2086</v>
       </c>
     </row>
     <row r="82" ht="22.5" customHeight="1">
@@ -17769,14 +17913,14 @@
         <v>115</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>1912</v>
+        <v>1922</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>2077</v>
+        <v>2087</v>
       </c>
       <c r="E82" s="21"/>
-      <c r="F82" s="108" t="s">
-        <v>2078</v>
+      <c r="F82" s="110" t="s">
+        <v>2088</v>
       </c>
     </row>
     <row r="83" ht="22.5" customHeight="1">
@@ -17787,14 +17931,14 @@
         <v>115</v>
       </c>
       <c r="C83" s="9" t="s">
-        <v>1919</v>
+        <v>1929</v>
       </c>
       <c r="D83" s="9" t="s">
-        <v>2079</v>
+        <v>2089</v>
       </c>
       <c r="E83" s="22"/>
-      <c r="F83" s="109" t="s">
-        <v>2080</v>
+      <c r="F83" s="111" t="s">
+        <v>2090</v>
       </c>
     </row>
     <row r="84" ht="22.5" customHeight="1">
@@ -17805,14 +17949,14 @@
         <v>115</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>1984</v>
+        <v>1994</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>2081</v>
+        <v>2091</v>
       </c>
       <c r="E84" s="21"/>
-      <c r="F84" s="108" t="s">
-        <v>2082</v>
+      <c r="F84" s="110" t="s">
+        <v>2092</v>
       </c>
     </row>
     <row r="85" ht="22.5" customHeight="1">
@@ -17823,14 +17967,14 @@
         <v>1550</v>
       </c>
       <c r="C85" s="9" t="s">
-        <v>1906</v>
+        <v>1916</v>
       </c>
       <c r="D85" s="9" t="s">
-        <v>2083</v>
+        <v>2093</v>
       </c>
       <c r="E85" s="22"/>
-      <c r="F85" s="109" t="s">
-        <v>1956</v>
+      <c r="F85" s="111" t="s">
+        <v>1966</v>
       </c>
     </row>
     <row r="86" ht="22.5" customHeight="1">
@@ -17841,14 +17985,14 @@
         <v>116</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>1906</v>
+        <v>1916</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>2084</v>
+        <v>2094</v>
       </c>
       <c r="E86" s="21"/>
-      <c r="F86" s="108" t="s">
-        <v>2085</v>
+      <c r="F86" s="110" t="s">
+        <v>2095</v>
       </c>
     </row>
     <row r="87" ht="22.5" customHeight="1">
@@ -17859,14 +18003,14 @@
         <v>117</v>
       </c>
       <c r="C87" s="9" t="s">
-        <v>1912</v>
+        <v>1922</v>
       </c>
       <c r="D87" s="9" t="s">
-        <v>2086</v>
+        <v>2096</v>
       </c>
       <c r="E87" s="22"/>
-      <c r="F87" s="109" t="s">
-        <v>2087</v>
+      <c r="F87" s="111" t="s">
+        <v>2097</v>
       </c>
     </row>
     <row r="88" ht="22.5" customHeight="1">
@@ -17877,14 +18021,14 @@
         <v>118</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>1906</v>
+        <v>1916</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>2088</v>
+        <v>2098</v>
       </c>
       <c r="E88" s="21"/>
-      <c r="F88" s="108" t="s">
-        <v>2089</v>
+      <c r="F88" s="110" t="s">
+        <v>2099</v>
       </c>
     </row>
     <row r="89" ht="22.5" customHeight="1">
@@ -17895,14 +18039,14 @@
         <v>119</v>
       </c>
       <c r="C89" s="9" t="s">
-        <v>1912</v>
+        <v>1922</v>
       </c>
       <c r="D89" s="9" t="s">
-        <v>2090</v>
+        <v>2100</v>
       </c>
       <c r="E89" s="22"/>
-      <c r="F89" s="109" t="s">
-        <v>2091</v>
+      <c r="F89" s="111" t="s">
+        <v>2101</v>
       </c>
     </row>
     <row r="90" ht="22.5" customHeight="1">
@@ -17913,14 +18057,14 @@
         <v>120</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>1906</v>
+        <v>1916</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>2092</v>
+        <v>2102</v>
       </c>
       <c r="E90" s="21"/>
-      <c r="F90" s="108" t="s">
-        <v>2089</v>
+      <c r="F90" s="110" t="s">
+        <v>2099</v>
       </c>
     </row>
     <row r="91" ht="22.5" customHeight="1">
@@ -17931,14 +18075,14 @@
         <v>121</v>
       </c>
       <c r="C91" s="9" t="s">
-        <v>1912</v>
+        <v>1922</v>
       </c>
       <c r="D91" s="9" t="s">
-        <v>2093</v>
+        <v>2103</v>
       </c>
       <c r="E91" s="22"/>
-      <c r="F91" s="109" t="s">
-        <v>2094</v>
+      <c r="F91" s="111" t="s">
+        <v>2104</v>
       </c>
     </row>
     <row r="92" ht="22.5" customHeight="1">
@@ -17952,11 +18096,11 @@
         <v>1630</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>2095</v>
+        <v>2105</v>
       </c>
       <c r="E92" s="21"/>
-      <c r="F92" s="108" t="s">
-        <v>2096</v>
+      <c r="F92" s="110" t="s">
+        <v>2106</v>
       </c>
     </row>
     <row r="93" ht="22.5" customHeight="1">
@@ -17967,14 +18111,14 @@
         <v>122</v>
       </c>
       <c r="C93" s="9" t="s">
-        <v>2097</v>
+        <v>2107</v>
       </c>
       <c r="D93" s="9" t="s">
-        <v>2098</v>
+        <v>2108</v>
       </c>
       <c r="E93" s="22"/>
-      <c r="F93" s="109" t="s">
-        <v>2099</v>
+      <c r="F93" s="111" t="s">
+        <v>2109</v>
       </c>
     </row>
     <row r="94" ht="22.5" customHeight="1">
@@ -17985,14 +18129,14 @@
         <v>122</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>1926</v>
+        <v>1936</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>2100</v>
+        <v>2110</v>
       </c>
       <c r="E94" s="21"/>
-      <c r="F94" s="108" t="s">
-        <v>2101</v>
+      <c r="F94" s="110" t="s">
+        <v>2111</v>
       </c>
     </row>
     <row r="95" ht="22.5" customHeight="1">
@@ -18003,14 +18147,14 @@
         <v>125</v>
       </c>
       <c r="C95" s="9" t="s">
-        <v>2102</v>
+        <v>2112</v>
       </c>
       <c r="D95" s="9" t="s">
-        <v>2103</v>
+        <v>2113</v>
       </c>
       <c r="E95" s="22"/>
-      <c r="F95" s="109" t="s">
-        <v>2104</v>
+      <c r="F95" s="111" t="s">
+        <v>2114</v>
       </c>
     </row>
     <row r="96" ht="22.5" customHeight="1">
@@ -18021,14 +18165,14 @@
         <v>128</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>2102</v>
+        <v>2112</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>2105</v>
+        <v>2115</v>
       </c>
       <c r="E96" s="21"/>
-      <c r="F96" s="108" t="s">
-        <v>2106</v>
+      <c r="F96" s="110" t="s">
+        <v>2116</v>
       </c>
     </row>
     <row r="97" ht="22.5" customHeight="1">
@@ -18039,14 +18183,14 @@
         <v>128</v>
       </c>
       <c r="C97" s="9" t="s">
-        <v>2097</v>
+        <v>2107</v>
       </c>
       <c r="D97" s="9" t="s">
-        <v>2107</v>
+        <v>2117</v>
       </c>
       <c r="E97" s="22"/>
-      <c r="F97" s="109" t="s">
-        <v>2108</v>
+      <c r="F97" s="111" t="s">
+        <v>2118</v>
       </c>
     </row>
     <row r="98" ht="22.5" customHeight="1">
@@ -18057,14 +18201,14 @@
         <v>131</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>2097</v>
+        <v>2107</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>2109</v>
+        <v>2119</v>
       </c>
       <c r="E98" s="21"/>
-      <c r="F98" s="108" t="s">
-        <v>2110</v>
+      <c r="F98" s="110" t="s">
+        <v>2120</v>
       </c>
     </row>
     <row r="99" ht="22.5" customHeight="1">
@@ -18075,14 +18219,14 @@
         <v>133</v>
       </c>
       <c r="C99" s="9" t="s">
-        <v>2102</v>
+        <v>2112</v>
       </c>
       <c r="D99" s="9" t="s">
-        <v>2111</v>
+        <v>2121</v>
       </c>
       <c r="E99" s="22"/>
-      <c r="F99" s="109" t="s">
-        <v>2112</v>
+      <c r="F99" s="111" t="s">
+        <v>2122</v>
       </c>
     </row>
     <row r="100" ht="22.5" customHeight="1">
@@ -18093,14 +18237,14 @@
         <v>133</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>2097</v>
+        <v>2107</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>2113</v>
+        <v>2123</v>
       </c>
       <c r="E100" s="21"/>
-      <c r="F100" s="108" t="s">
-        <v>2114</v>
+      <c r="F100" s="110" t="s">
+        <v>2124</v>
       </c>
     </row>
     <row r="101" ht="22.5" customHeight="1">
@@ -18111,14 +18255,14 @@
         <v>135</v>
       </c>
       <c r="C101" s="9" t="s">
-        <v>2102</v>
+        <v>2112</v>
       </c>
       <c r="D101" s="9" t="s">
-        <v>2115</v>
+        <v>2125</v>
       </c>
       <c r="E101" s="22"/>
-      <c r="F101" s="109" t="s">
-        <v>2116</v>
+      <c r="F101" s="111" t="s">
+        <v>2126</v>
       </c>
     </row>
     <row r="102" ht="22.5" customHeight="1">
@@ -18132,11 +18276,11 @@
         <v>1630</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>2117</v>
+        <v>2127</v>
       </c>
       <c r="E102" s="21"/>
-      <c r="F102" s="108" t="s">
-        <v>2118</v>
+      <c r="F102" s="110" t="s">
+        <v>2128</v>
       </c>
     </row>
     <row r="103" ht="22.5" customHeight="1">
@@ -18150,11 +18294,11 @@
         <v>1630</v>
       </c>
       <c r="D103" s="9" t="s">
-        <v>2119</v>
+        <v>2129</v>
       </c>
       <c r="E103" s="22"/>
-      <c r="F103" s="109" t="s">
-        <v>2120</v>
+      <c r="F103" s="111" t="s">
+        <v>2130</v>
       </c>
     </row>
     <row r="104" ht="22.5" customHeight="1">
@@ -18165,14 +18309,14 @@
         <v>137</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>2097</v>
+        <v>2107</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>2121</v>
+        <v>2131</v>
       </c>
       <c r="E104" s="21"/>
-      <c r="F104" s="108" t="s">
-        <v>2122</v>
+      <c r="F104" s="110" t="s">
+        <v>2132</v>
       </c>
     </row>
     <row r="105" ht="22.5" customHeight="1">
@@ -18186,11 +18330,11 @@
         <v>1630</v>
       </c>
       <c r="D105" s="9" t="s">
-        <v>2123</v>
+        <v>2133</v>
       </c>
       <c r="E105" s="22"/>
-      <c r="F105" s="109" t="s">
-        <v>2124</v>
+      <c r="F105" s="111" t="s">
+        <v>2134</v>
       </c>
     </row>
     <row r="106" ht="22.5" customHeight="1">
@@ -18201,14 +18345,14 @@
         <v>139</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>2097</v>
+        <v>2107</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>2125</v>
+        <v>2135</v>
       </c>
       <c r="E106" s="21"/>
-      <c r="F106" s="108" t="s">
-        <v>2126</v>
+      <c r="F106" s="110" t="s">
+        <v>2136</v>
       </c>
     </row>
     <row r="107" ht="22.5" customHeight="1">
@@ -18219,14 +18363,14 @@
         <v>141</v>
       </c>
       <c r="C107" s="9" t="s">
-        <v>2102</v>
+        <v>2112</v>
       </c>
       <c r="D107" s="9" t="s">
-        <v>2127</v>
+        <v>2137</v>
       </c>
       <c r="E107" s="22"/>
-      <c r="F107" s="109" t="s">
-        <v>2128</v>
+      <c r="F107" s="111" t="s">
+        <v>2138</v>
       </c>
     </row>
     <row r="108" ht="22.5" customHeight="1">
@@ -18240,11 +18384,11 @@
         <v>1630</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>2129</v>
+        <v>2139</v>
       </c>
       <c r="E108" s="21"/>
-      <c r="F108" s="108" t="s">
-        <v>2130</v>
+      <c r="F108" s="110" t="s">
+        <v>2140</v>
       </c>
     </row>
     <row r="109" ht="22.5" customHeight="1">
@@ -18255,14 +18399,14 @@
         <v>141</v>
       </c>
       <c r="C109" s="9" t="s">
-        <v>2097</v>
+        <v>2107</v>
       </c>
       <c r="D109" s="9" t="s">
-        <v>2131</v>
+        <v>2141</v>
       </c>
       <c r="E109" s="22"/>
-      <c r="F109" s="109" t="s">
-        <v>2132</v>
+      <c r="F109" s="111" t="s">
+        <v>2142</v>
       </c>
     </row>
     <row r="110" ht="22.5" customHeight="1">
@@ -18273,14 +18417,14 @@
         <v>143</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>2102</v>
+        <v>2112</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>2133</v>
+        <v>2143</v>
       </c>
       <c r="E110" s="21"/>
-      <c r="F110" s="108" t="s">
-        <v>2134</v>
+      <c r="F110" s="110" t="s">
+        <v>2144</v>
       </c>
     </row>
     <row r="111" ht="22.5" customHeight="1">
@@ -18291,14 +18435,14 @@
         <v>144</v>
       </c>
       <c r="C111" s="9" t="s">
-        <v>2102</v>
+        <v>2112</v>
       </c>
       <c r="D111" s="9" t="s">
-        <v>2135</v>
+        <v>2145</v>
       </c>
       <c r="E111" s="22"/>
-      <c r="F111" s="109" t="s">
-        <v>2106</v>
+      <c r="F111" s="111" t="s">
+        <v>2116</v>
       </c>
     </row>
     <row r="112" ht="22.5" customHeight="1">
@@ -18309,14 +18453,14 @@
         <v>144</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>2097</v>
+        <v>2107</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>2136</v>
+        <v>2146</v>
       </c>
       <c r="E112" s="21"/>
-      <c r="F112" s="108" t="s">
-        <v>2137</v>
+      <c r="F112" s="110" t="s">
+        <v>2147</v>
       </c>
     </row>
     <row r="113" ht="22.5" customHeight="1">
@@ -18327,14 +18471,14 @@
         <v>147</v>
       </c>
       <c r="C113" s="9" t="s">
-        <v>2102</v>
+        <v>2112</v>
       </c>
       <c r="D113" s="9" t="s">
-        <v>2138</v>
+        <v>2148</v>
       </c>
       <c r="E113" s="22"/>
-      <c r="F113" s="109" t="s">
-        <v>2139</v>
+      <c r="F113" s="111" t="s">
+        <v>2149</v>
       </c>
     </row>
     <row r="114" ht="22.5" customHeight="1">
@@ -18345,14 +18489,14 @@
         <v>147</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>2097</v>
+        <v>2107</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>2140</v>
+        <v>2150</v>
       </c>
       <c r="E114" s="21"/>
-      <c r="F114" s="108" t="s">
-        <v>2141</v>
+      <c r="F114" s="110" t="s">
+        <v>2151</v>
       </c>
     </row>
     <row r="115" ht="22.5" customHeight="1">
@@ -18363,14 +18507,14 @@
         <v>147</v>
       </c>
       <c r="C115" s="9" t="s">
-        <v>2142</v>
+        <v>2152</v>
       </c>
       <c r="D115" s="9" t="s">
-        <v>2143</v>
+        <v>2153</v>
       </c>
       <c r="E115" s="22"/>
-      <c r="F115" s="109" t="s">
-        <v>2144</v>
+      <c r="F115" s="111" t="s">
+        <v>2154</v>
       </c>
     </row>
     <row r="116" ht="22.5" customHeight="1">
@@ -18384,11 +18528,11 @@
         <v>1630</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>2145</v>
+        <v>2155</v>
       </c>
       <c r="E116" s="21"/>
-      <c r="F116" s="108" t="s">
-        <v>2146</v>
+      <c r="F116" s="110" t="s">
+        <v>2156</v>
       </c>
     </row>
     <row r="117" ht="22.5" customHeight="1">
@@ -18399,14 +18543,14 @@
         <v>148</v>
       </c>
       <c r="C117" s="9" t="s">
-        <v>2097</v>
+        <v>2107</v>
       </c>
       <c r="D117" s="9" t="s">
-        <v>2147</v>
+        <v>2157</v>
       </c>
       <c r="E117" s="22"/>
-      <c r="F117" s="109" t="s">
-        <v>2148</v>
+      <c r="F117" s="111" t="s">
+        <v>2158</v>
       </c>
     </row>
     <row r="118" ht="22.5" customHeight="1">
@@ -18417,14 +18561,14 @@
         <v>148</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>2149</v>
+        <v>2159</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>2150</v>
+        <v>2160</v>
       </c>
       <c r="E118" s="21"/>
-      <c r="F118" s="108" t="s">
-        <v>2151</v>
+      <c r="F118" s="110" t="s">
+        <v>2161</v>
       </c>
     </row>
     <row r="119" ht="22.5" customHeight="1">
@@ -18438,11 +18582,11 @@
         <v>1630</v>
       </c>
       <c r="D119" s="9" t="s">
-        <v>2152</v>
+        <v>2162</v>
       </c>
       <c r="E119" s="22"/>
-      <c r="F119" s="109" t="s">
-        <v>2153</v>
+      <c r="F119" s="111" t="s">
+        <v>2163</v>
       </c>
     </row>
     <row r="120" ht="22.5" customHeight="1">
@@ -18453,14 +18597,14 @@
         <v>149</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>1926</v>
+        <v>1936</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>2154</v>
+        <v>2164</v>
       </c>
       <c r="E120" s="21"/>
-      <c r="F120" s="108" t="s">
-        <v>2155</v>
+      <c r="F120" s="110" t="s">
+        <v>2165</v>
       </c>
     </row>
     <row r="121" ht="22.5" customHeight="1">
@@ -18471,14 +18615,14 @@
         <v>149</v>
       </c>
       <c r="C121" s="9" t="s">
-        <v>2156</v>
+        <v>2166</v>
       </c>
       <c r="D121" s="9" t="s">
-        <v>2157</v>
+        <v>2167</v>
       </c>
       <c r="E121" s="22"/>
-      <c r="F121" s="109" t="s">
-        <v>2158</v>
+      <c r="F121" s="111" t="s">
+        <v>2168</v>
       </c>
     </row>
     <row r="122" ht="22.5" customHeight="1">
@@ -18489,14 +18633,14 @@
         <v>151</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>2102</v>
+        <v>2112</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>2159</v>
+        <v>2169</v>
       </c>
       <c r="E122" s="21"/>
-      <c r="F122" s="108" t="s">
-        <v>2160</v>
+      <c r="F122" s="110" t="s">
+        <v>2170</v>
       </c>
     </row>
     <row r="123" ht="22.5" customHeight="1">
@@ -18507,14 +18651,14 @@
         <v>151</v>
       </c>
       <c r="C123" s="9" t="s">
-        <v>1926</v>
+        <v>1936</v>
       </c>
       <c r="D123" s="9" t="s">
-        <v>2161</v>
+        <v>2171</v>
       </c>
       <c r="E123" s="22"/>
-      <c r="F123" s="109" t="s">
-        <v>2162</v>
+      <c r="F123" s="111" t="s">
+        <v>2172</v>
       </c>
     </row>
     <row r="124" ht="22.5" customHeight="1">
@@ -18525,14 +18669,14 @@
         <v>152</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>2102</v>
+        <v>2112</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>2163</v>
+        <v>2173</v>
       </c>
       <c r="E124" s="21"/>
-      <c r="F124" s="108" t="s">
-        <v>2164</v>
+      <c r="F124" s="110" t="s">
+        <v>2174</v>
       </c>
     </row>
     <row r="125" ht="22.5" customHeight="1">
@@ -18543,14 +18687,14 @@
         <v>152</v>
       </c>
       <c r="C125" s="9" t="s">
-        <v>2097</v>
+        <v>2107</v>
       </c>
       <c r="D125" s="9" t="s">
-        <v>2165</v>
+        <v>2175</v>
       </c>
       <c r="E125" s="22"/>
-      <c r="F125" s="109" t="s">
-        <v>2166</v>
+      <c r="F125" s="111" t="s">
+        <v>2176</v>
       </c>
     </row>
     <row r="126" ht="22.5" customHeight="1">
@@ -18561,14 +18705,14 @@
         <v>153</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>2102</v>
+        <v>2112</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>2167</v>
+        <v>2177</v>
       </c>
       <c r="E126" s="21"/>
-      <c r="F126" s="108" t="s">
-        <v>2168</v>
+      <c r="F126" s="110" t="s">
+        <v>2178</v>
       </c>
     </row>
     <row r="127" ht="22.5" customHeight="1">
@@ -18582,11 +18726,11 @@
         <v>1630</v>
       </c>
       <c r="D127" s="9" t="s">
-        <v>2169</v>
+        <v>2179</v>
       </c>
       <c r="E127" s="22"/>
-      <c r="F127" s="109" t="s">
-        <v>2170</v>
+      <c r="F127" s="111" t="s">
+        <v>2180</v>
       </c>
     </row>
     <row r="128" ht="22.5" customHeight="1">
@@ -18597,14 +18741,14 @@
         <v>153</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>2097</v>
+        <v>2107</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>2171</v>
+        <v>2181</v>
       </c>
       <c r="E128" s="21"/>
-      <c r="F128" s="108" t="s">
-        <v>2172</v>
+      <c r="F128" s="110" t="s">
+        <v>2182</v>
       </c>
     </row>
     <row r="129" ht="22.5" customHeight="1">
@@ -18612,17 +18756,17 @@
         <v>17</v>
       </c>
       <c r="B129" s="9" t="s">
-        <v>2173</v>
+        <v>2183</v>
       </c>
       <c r="C129" s="9" t="s">
         <v>1630</v>
       </c>
       <c r="D129" s="9" t="s">
-        <v>2174</v>
+        <v>2184</v>
       </c>
       <c r="E129" s="22"/>
-      <c r="F129" s="109" t="s">
-        <v>2106</v>
+      <c r="F129" s="111" t="s">
+        <v>2116</v>
       </c>
     </row>
     <row r="130" ht="22.5" customHeight="1">
@@ -18633,14 +18777,14 @@
         <v>155</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>2097</v>
+        <v>2107</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>2175</v>
+        <v>2185</v>
       </c>
       <c r="E130" s="21"/>
-      <c r="F130" s="108" t="s">
-        <v>2176</v>
+      <c r="F130" s="110" t="s">
+        <v>2186</v>
       </c>
     </row>
     <row r="131" ht="22.5" customHeight="1">
@@ -18651,14 +18795,14 @@
         <v>157</v>
       </c>
       <c r="C131" s="9" t="s">
-        <v>2102</v>
+        <v>2112</v>
       </c>
       <c r="D131" s="9" t="s">
-        <v>2177</v>
+        <v>2187</v>
       </c>
       <c r="E131" s="22"/>
-      <c r="F131" s="109" t="s">
-        <v>2178</v>
+      <c r="F131" s="111" t="s">
+        <v>2188</v>
       </c>
     </row>
     <row r="132" ht="22.5" customHeight="1">
@@ -18672,11 +18816,11 @@
         <v>1630</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>2179</v>
+        <v>2189</v>
       </c>
       <c r="E132" s="21"/>
-      <c r="F132" s="108" t="s">
-        <v>2180</v>
+      <c r="F132" s="110" t="s">
+        <v>2190</v>
       </c>
     </row>
     <row r="133" ht="22.5" customHeight="1">
@@ -18687,14 +18831,14 @@
         <v>158</v>
       </c>
       <c r="C133" s="9" t="s">
-        <v>2102</v>
+        <v>2112</v>
       </c>
       <c r="D133" s="9" t="s">
-        <v>2181</v>
+        <v>2191</v>
       </c>
       <c r="E133" s="22"/>
-      <c r="F133" s="109" t="s">
-        <v>2182</v>
+      <c r="F133" s="111" t="s">
+        <v>2192</v>
       </c>
     </row>
     <row r="134" ht="22.5" customHeight="1">
@@ -18708,11 +18852,11 @@
         <v>1630</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>2183</v>
+        <v>2193</v>
       </c>
       <c r="E134" s="21"/>
-      <c r="F134" s="108" t="s">
-        <v>2184</v>
+      <c r="F134" s="110" t="s">
+        <v>2194</v>
       </c>
     </row>
     <row r="135" ht="22.5" customHeight="1">
@@ -18726,11 +18870,11 @@
         <v>1630</v>
       </c>
       <c r="D135" s="9" t="s">
-        <v>2185</v>
+        <v>2195</v>
       </c>
       <c r="E135" s="22"/>
-      <c r="F135" s="109" t="s">
-        <v>2186</v>
+      <c r="F135" s="111" t="s">
+        <v>2196</v>
       </c>
     </row>
     <row r="136" ht="22.5" customHeight="1">
@@ -18741,14 +18885,14 @@
         <v>160</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>2102</v>
+        <v>2112</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>2187</v>
+        <v>2197</v>
       </c>
       <c r="E136" s="21"/>
-      <c r="F136" s="108" t="s">
-        <v>2188</v>
+      <c r="F136" s="110" t="s">
+        <v>2198</v>
       </c>
     </row>
     <row r="137" ht="22.5" customHeight="1">
@@ -18759,14 +18903,14 @@
         <v>160</v>
       </c>
       <c r="C137" s="9" t="s">
-        <v>2097</v>
+        <v>2107</v>
       </c>
       <c r="D137" s="9" t="s">
-        <v>2189</v>
+        <v>2199</v>
       </c>
       <c r="E137" s="22"/>
-      <c r="F137" s="109" t="s">
-        <v>2190</v>
+      <c r="F137" s="111" t="s">
+        <v>2200</v>
       </c>
     </row>
     <row r="138" ht="22.5" customHeight="1">
@@ -18777,14 +18921,14 @@
         <v>161</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>2191</v>
+        <v>2201</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>2192</v>
+        <v>2202</v>
       </c>
       <c r="E138" s="21"/>
-      <c r="F138" s="108" t="s">
-        <v>2193</v>
+      <c r="F138" s="110" t="s">
+        <v>2203</v>
       </c>
     </row>
     <row r="139" ht="22.5" customHeight="1">
@@ -18795,14 +18939,14 @@
         <v>162</v>
       </c>
       <c r="C139" s="9" t="s">
-        <v>2097</v>
+        <v>2107</v>
       </c>
       <c r="D139" s="9" t="s">
-        <v>2194</v>
+        <v>2204</v>
       </c>
       <c r="E139" s="22"/>
-      <c r="F139" s="109" t="s">
-        <v>2195</v>
+      <c r="F139" s="111" t="s">
+        <v>2205</v>
       </c>
     </row>
     <row r="140" ht="22.5" customHeight="1">
@@ -18813,14 +18957,14 @@
         <v>163</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>2102</v>
+        <v>2112</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>2196</v>
+        <v>2206</v>
       </c>
       <c r="E140" s="21"/>
-      <c r="F140" s="108" t="s">
-        <v>2197</v>
+      <c r="F140" s="110" t="s">
+        <v>2207</v>
       </c>
     </row>
     <row r="141" ht="22.5" customHeight="1">
@@ -18834,11 +18978,11 @@
         <v>1630</v>
       </c>
       <c r="D141" s="9" t="s">
-        <v>2198</v>
+        <v>2208</v>
       </c>
       <c r="E141" s="22"/>
-      <c r="F141" s="109" t="s">
-        <v>2199</v>
+      <c r="F141" s="111" t="s">
+        <v>2209</v>
       </c>
     </row>
     <row r="142" ht="22.5" customHeight="1">
@@ -18849,14 +18993,14 @@
         <v>164</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>2102</v>
+        <v>2112</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>2200</v>
+        <v>2210</v>
       </c>
       <c r="E142" s="21"/>
-      <c r="F142" s="108" t="s">
-        <v>2201</v>
+      <c r="F142" s="110" t="s">
+        <v>2211</v>
       </c>
     </row>
     <row r="143" ht="22.5" customHeight="1">
@@ -18867,14 +19011,14 @@
         <v>164</v>
       </c>
       <c r="C143" s="9" t="s">
-        <v>2097</v>
+        <v>2107</v>
       </c>
       <c r="D143" s="9" t="s">
-        <v>2202</v>
+        <v>2212</v>
       </c>
       <c r="E143" s="22"/>
-      <c r="F143" s="109" t="s">
-        <v>2203</v>
+      <c r="F143" s="111" t="s">
+        <v>2213</v>
       </c>
     </row>
     <row r="144" ht="22.5" customHeight="1">
@@ -18882,17 +19026,17 @@
         <v>17</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>2204</v>
+        <v>2214</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>2102</v>
+        <v>2112</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>2205</v>
+        <v>2215</v>
       </c>
       <c r="E144" s="21"/>
-      <c r="F144" s="108" t="s">
-        <v>2206</v>
+      <c r="F144" s="110" t="s">
+        <v>2216</v>
       </c>
     </row>
     <row r="145" ht="22.5" customHeight="1">
@@ -18906,11 +19050,11 @@
         <v>1630</v>
       </c>
       <c r="D145" s="9" t="s">
-        <v>2207</v>
+        <v>2217</v>
       </c>
       <c r="E145" s="22"/>
-      <c r="F145" s="109" t="s">
-        <v>2208</v>
+      <c r="F145" s="111" t="s">
+        <v>2218</v>
       </c>
     </row>
     <row r="146" ht="22.5" customHeight="1">
@@ -18921,14 +19065,14 @@
         <v>167</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>2142</v>
+        <v>2152</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>2209</v>
+        <v>2219</v>
       </c>
       <c r="E146" s="21"/>
-      <c r="F146" s="108" t="s">
-        <v>2210</v>
+      <c r="F146" s="110" t="s">
+        <v>2220</v>
       </c>
     </row>
     <row r="147" ht="22.5" customHeight="1">
@@ -18939,14 +19083,14 @@
         <v>168</v>
       </c>
       <c r="C147" s="9" t="s">
-        <v>2097</v>
+        <v>2107</v>
       </c>
       <c r="D147" s="9" t="s">
-        <v>2211</v>
+        <v>2221</v>
       </c>
       <c r="E147" s="22"/>
-      <c r="F147" s="109" t="s">
-        <v>2212</v>
+      <c r="F147" s="111" t="s">
+        <v>2222</v>
       </c>
     </row>
     <row r="148" ht="22.5" customHeight="1">
@@ -18957,14 +19101,14 @@
         <v>168</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>2149</v>
+        <v>2159</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>2213</v>
+        <v>2223</v>
       </c>
       <c r="E148" s="21"/>
-      <c r="F148" s="108" t="s">
-        <v>2214</v>
+      <c r="F148" s="110" t="s">
+        <v>2224</v>
       </c>
     </row>
     <row r="149" ht="22.5" customHeight="1">
@@ -18978,11 +19122,11 @@
         <v>1630</v>
       </c>
       <c r="D149" s="9" t="s">
-        <v>2215</v>
+        <v>2225</v>
       </c>
       <c r="E149" s="22"/>
-      <c r="F149" s="109" t="s">
-        <v>2216</v>
+      <c r="F149" s="111" t="s">
+        <v>2226</v>
       </c>
     </row>
     <row r="150" ht="22.5" customHeight="1">
@@ -18993,14 +19137,14 @@
         <v>169</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>2217</v>
+        <v>2227</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>2218</v>
+        <v>2228</v>
       </c>
       <c r="E150" s="21"/>
-      <c r="F150" s="108" t="s">
-        <v>2219</v>
+      <c r="F150" s="110" t="s">
+        <v>2229</v>
       </c>
     </row>
     <row r="151" ht="22.5" customHeight="1">
@@ -19014,11 +19158,11 @@
         <v>1630</v>
       </c>
       <c r="D151" s="9" t="s">
-        <v>2220</v>
+        <v>2230</v>
       </c>
       <c r="E151" s="22"/>
-      <c r="F151" s="109" t="s">
-        <v>2221</v>
+      <c r="F151" s="111" t="s">
+        <v>2231</v>
       </c>
     </row>
     <row r="152" ht="22.5" customHeight="1">
@@ -19029,14 +19173,14 @@
         <v>170</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>2097</v>
+        <v>2107</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>2222</v>
+        <v>2232</v>
       </c>
       <c r="E152" s="21"/>
-      <c r="F152" s="108" t="s">
-        <v>2223</v>
+      <c r="F152" s="110" t="s">
+        <v>2233</v>
       </c>
     </row>
     <row r="153" ht="22.5" customHeight="1">
@@ -19050,11 +19194,11 @@
         <v>1630</v>
       </c>
       <c r="D153" s="9" t="s">
-        <v>2224</v>
+        <v>2234</v>
       </c>
       <c r="E153" s="22"/>
-      <c r="F153" s="109" t="s">
-        <v>2225</v>
+      <c r="F153" s="111" t="s">
+        <v>2235</v>
       </c>
     </row>
     <row r="154" ht="22.5" customHeight="1">
@@ -19065,14 +19209,14 @@
         <v>171</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>1926</v>
+        <v>1936</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>2226</v>
+        <v>2236</v>
       </c>
       <c r="E154" s="21"/>
-      <c r="F154" s="108" t="s">
-        <v>2227</v>
+      <c r="F154" s="110" t="s">
+        <v>2237</v>
       </c>
     </row>
     <row r="155" ht="22.5" customHeight="1">
@@ -19083,14 +19227,14 @@
         <v>172</v>
       </c>
       <c r="C155" s="9" t="s">
-        <v>2102</v>
+        <v>2112</v>
       </c>
       <c r="D155" s="9" t="s">
-        <v>2228</v>
+        <v>2238</v>
       </c>
       <c r="E155" s="22"/>
-      <c r="F155" s="109" t="s">
-        <v>2229</v>
+      <c r="F155" s="111" t="s">
+        <v>2239</v>
       </c>
     </row>
     <row r="156" ht="22.5" customHeight="1">
@@ -19104,11 +19248,11 @@
         <v>1630</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>2230</v>
+        <v>2240</v>
       </c>
       <c r="E156" s="21"/>
-      <c r="F156" s="108" t="s">
-        <v>2231</v>
+      <c r="F156" s="110" t="s">
+        <v>2241</v>
       </c>
     </row>
     <row r="157" ht="22.5" customHeight="1">
@@ -19119,14 +19263,14 @@
         <v>173</v>
       </c>
       <c r="C157" s="9" t="s">
-        <v>2102</v>
+        <v>2112</v>
       </c>
       <c r="D157" s="9" t="s">
-        <v>2232</v>
+        <v>2242</v>
       </c>
       <c r="E157" s="22"/>
-      <c r="F157" s="109" t="s">
-        <v>2233</v>
+      <c r="F157" s="111" t="s">
+        <v>2243</v>
       </c>
     </row>
     <row r="158" ht="22.5" customHeight="1">
@@ -19140,11 +19284,11 @@
         <v>1630</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>2234</v>
+        <v>2244</v>
       </c>
       <c r="E158" s="21"/>
-      <c r="F158" s="108" t="s">
-        <v>2235</v>
+      <c r="F158" s="110" t="s">
+        <v>2245</v>
       </c>
     </row>
     <row r="159" ht="22.5" customHeight="1">
@@ -19155,14 +19299,14 @@
         <v>175</v>
       </c>
       <c r="C159" s="9" t="s">
-        <v>2097</v>
+        <v>2107</v>
       </c>
       <c r="D159" s="9" t="s">
-        <v>2236</v>
+        <v>2246</v>
       </c>
       <c r="E159" s="22"/>
-      <c r="F159" s="109" t="s">
-        <v>2237</v>
+      <c r="F159" s="111" t="s">
+        <v>2247</v>
       </c>
     </row>
     <row r="160" ht="22.5" customHeight="1">
@@ -19173,14 +19317,14 @@
         <v>176</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>2102</v>
+        <v>2112</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>2238</v>
+        <v>2248</v>
       </c>
       <c r="E160" s="21"/>
-      <c r="F160" s="108" t="s">
-        <v>2239</v>
+      <c r="F160" s="110" t="s">
+        <v>2249</v>
       </c>
     </row>
     <row r="161" ht="22.5" customHeight="1">
@@ -19194,11 +19338,11 @@
         <v>1630</v>
       </c>
       <c r="D161" s="9" t="s">
-        <v>2240</v>
+        <v>2250</v>
       </c>
       <c r="E161" s="22"/>
-      <c r="F161" s="109" t="s">
-        <v>2216</v>
+      <c r="F161" s="111" t="s">
+        <v>2226</v>
       </c>
     </row>
     <row r="162" ht="22.5" customHeight="1">
@@ -19209,14 +19353,14 @@
         <v>178</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>2102</v>
+        <v>2112</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>2241</v>
+        <v>2251</v>
       </c>
       <c r="E162" s="21"/>
-      <c r="F162" s="108" t="s">
-        <v>2242</v>
+      <c r="F162" s="110" t="s">
+        <v>2252</v>
       </c>
     </row>
     <row r="163" ht="22.5" customHeight="1">
@@ -19227,14 +19371,14 @@
         <v>178</v>
       </c>
       <c r="C163" s="9" t="s">
-        <v>2097</v>
+        <v>2107</v>
       </c>
       <c r="D163" s="9" t="s">
-        <v>2243</v>
+        <v>2253</v>
       </c>
       <c r="E163" s="22"/>
-      <c r="F163" s="109" t="s">
-        <v>2244</v>
+      <c r="F163" s="111" t="s">
+        <v>2254</v>
       </c>
     </row>
     <row r="164" ht="22.5" customHeight="1">
@@ -19245,14 +19389,14 @@
         <v>179</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>2102</v>
+        <v>2112</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>2245</v>
+        <v>2255</v>
       </c>
       <c r="E164" s="21"/>
-      <c r="F164" s="108" t="s">
-        <v>2246</v>
+      <c r="F164" s="110" t="s">
+        <v>2256</v>
       </c>
     </row>
     <row r="165" ht="22.5" customHeight="1">
@@ -19263,13 +19407,13 @@
         <v>179</v>
       </c>
       <c r="C165" s="9" t="s">
-        <v>2247</v>
+        <v>2257</v>
       </c>
       <c r="D165" s="9" t="s">
-        <v>2248</v>
+        <v>2258</v>
       </c>
       <c r="E165" s="22"/>
-      <c r="F165" s="109" t="s">
+      <c r="F165" s="111" t="s">
         <v>1676</v>
       </c>
     </row>
@@ -19281,14 +19425,14 @@
         <v>180</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>2102</v>
+        <v>2112</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>2249</v>
+        <v>2259</v>
       </c>
       <c r="E166" s="21"/>
-      <c r="F166" s="108" t="s">
-        <v>2250</v>
+      <c r="F166" s="110" t="s">
+        <v>2260</v>
       </c>
     </row>
     <row r="167" ht="22.5" customHeight="1">
@@ -19302,11 +19446,11 @@
         <v>1630</v>
       </c>
       <c r="D167" s="9" t="s">
-        <v>2251</v>
+        <v>2261</v>
       </c>
       <c r="E167" s="22"/>
-      <c r="F167" s="109" t="s">
-        <v>2252</v>
+      <c r="F167" s="111" t="s">
+        <v>2262</v>
       </c>
     </row>
     <row r="168" ht="22.5" customHeight="1">
@@ -19317,14 +19461,14 @@
         <v>181</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>2102</v>
+        <v>2112</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>2253</v>
+        <v>2263</v>
       </c>
       <c r="E168" s="21"/>
-      <c r="F168" s="108" t="s">
-        <v>2254</v>
+      <c r="F168" s="110" t="s">
+        <v>2264</v>
       </c>
     </row>
     <row r="169" ht="22.5" customHeight="1">
@@ -19335,14 +19479,14 @@
         <v>181</v>
       </c>
       <c r="C169" s="9" t="s">
-        <v>2097</v>
+        <v>2107</v>
       </c>
       <c r="D169" s="9" t="s">
-        <v>2255</v>
+        <v>2265</v>
       </c>
       <c r="E169" s="22"/>
-      <c r="F169" s="109" t="s">
-        <v>2256</v>
+      <c r="F169" s="111" t="s">
+        <v>2266</v>
       </c>
     </row>
     <row r="170" ht="22.5" customHeight="1">
@@ -19356,11 +19500,11 @@
         <v>1630</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>2257</v>
+        <v>2267</v>
       </c>
       <c r="E170" s="21"/>
-      <c r="F170" s="108" t="s">
-        <v>2258</v>
+      <c r="F170" s="110" t="s">
+        <v>2268</v>
       </c>
     </row>
     <row r="171" ht="22.5" customHeight="1">
@@ -19371,14 +19515,14 @@
         <v>183</v>
       </c>
       <c r="C171" s="9" t="s">
-        <v>2102</v>
+        <v>2112</v>
       </c>
       <c r="D171" s="9" t="s">
-        <v>2259</v>
+        <v>2269</v>
       </c>
       <c r="E171" s="22"/>
-      <c r="F171" s="109" t="s">
-        <v>2260</v>
+      <c r="F171" s="111" t="s">
+        <v>2270</v>
       </c>
     </row>
     <row r="172" ht="22.5" customHeight="1">
@@ -19392,11 +19536,11 @@
         <v>1630</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>2261</v>
+        <v>2271</v>
       </c>
       <c r="E172" s="21"/>
-      <c r="F172" s="108" t="s">
-        <v>2262</v>
+      <c r="F172" s="110" t="s">
+        <v>2272</v>
       </c>
     </row>
     <row r="173" ht="22.5" customHeight="1">
@@ -19410,11 +19554,11 @@
         <v>1630</v>
       </c>
       <c r="D173" s="9" t="s">
-        <v>2263</v>
+        <v>2273</v>
       </c>
       <c r="E173" s="22"/>
-      <c r="F173" s="109" t="s">
-        <v>2264</v>
+      <c r="F173" s="111" t="s">
+        <v>2274</v>
       </c>
     </row>
     <row r="174" ht="22.5" customHeight="1">
@@ -19425,14 +19569,14 @@
         <v>184</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>2097</v>
+        <v>2107</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>2265</v>
+        <v>2275</v>
       </c>
       <c r="E174" s="21"/>
-      <c r="F174" s="108" t="s">
-        <v>2266</v>
+      <c r="F174" s="110" t="s">
+        <v>2276</v>
       </c>
     </row>
     <row r="175" ht="22.5" customHeight="1">
@@ -19443,14 +19587,14 @@
         <v>185</v>
       </c>
       <c r="C175" s="9" t="s">
-        <v>2102</v>
+        <v>2112</v>
       </c>
       <c r="D175" s="9" t="s">
-        <v>2267</v>
+        <v>2277</v>
       </c>
       <c r="E175" s="22"/>
-      <c r="F175" s="109" t="s">
-        <v>2268</v>
+      <c r="F175" s="111" t="s">
+        <v>2278</v>
       </c>
     </row>
     <row r="176" ht="22.5" customHeight="1">
@@ -19461,14 +19605,14 @@
         <v>185</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>2156</v>
+        <v>2166</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>2269</v>
+        <v>2279</v>
       </c>
       <c r="E176" s="21"/>
-      <c r="F176" s="108" t="s">
-        <v>2270</v>
+      <c r="F176" s="110" t="s">
+        <v>2280</v>
       </c>
     </row>
     <row r="177" ht="22.5" customHeight="1">
@@ -19482,11 +19626,11 @@
         <v>1630</v>
       </c>
       <c r="D177" s="9" t="s">
-        <v>2271</v>
+        <v>2281</v>
       </c>
       <c r="E177" s="22"/>
-      <c r="F177" s="109" t="s">
-        <v>2124</v>
+      <c r="F177" s="111" t="s">
+        <v>2134</v>
       </c>
     </row>
     <row r="178" ht="22.5" customHeight="1">
@@ -19497,14 +19641,14 @@
         <v>187</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>2097</v>
+        <v>2107</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>2272</v>
+        <v>2282</v>
       </c>
       <c r="E178" s="21"/>
-      <c r="F178" s="108" t="s">
-        <v>2126</v>
+      <c r="F178" s="110" t="s">
+        <v>2136</v>
       </c>
     </row>
     <row r="179" ht="22.5" customHeight="1">
@@ -19515,13 +19659,13 @@
         <v>192</v>
       </c>
       <c r="C179" s="9" t="s">
-        <v>2273</v>
+        <v>2283</v>
       </c>
       <c r="D179" s="9" t="s">
-        <v>2274</v>
+        <v>2284</v>
       </c>
       <c r="E179" s="22"/>
-      <c r="F179" s="117"/>
+      <c r="F179" s="119"/>
     </row>
     <row r="180" ht="22.5" customHeight="1">
       <c r="A180" s="2" t="s">
@@ -19531,14 +19675,14 @@
         <v>195</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>2273</v>
+        <v>2283</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>2275</v>
+        <v>2285</v>
       </c>
       <c r="E180" s="21"/>
-      <c r="F180" s="108" t="s">
-        <v>2276</v>
+      <c r="F180" s="110" t="s">
+        <v>2286</v>
       </c>
     </row>
     <row r="181" ht="22.5" customHeight="1">
@@ -19549,14 +19693,14 @@
         <v>197</v>
       </c>
       <c r="C181" s="9" t="s">
-        <v>2273</v>
+        <v>2283</v>
       </c>
       <c r="D181" s="9" t="s">
-        <v>2277</v>
+        <v>2287</v>
       </c>
       <c r="E181" s="22"/>
-      <c r="F181" s="109" t="s">
-        <v>2278</v>
+      <c r="F181" s="111" t="s">
+        <v>2288</v>
       </c>
     </row>
     <row r="182" ht="22.5" customHeight="1">
@@ -19567,14 +19711,14 @@
         <v>198</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>2273</v>
+        <v>2283</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>2279</v>
+        <v>2289</v>
       </c>
       <c r="E182" s="21"/>
-      <c r="F182" s="108" t="s">
-        <v>2280</v>
+      <c r="F182" s="110" t="s">
+        <v>2290</v>
       </c>
     </row>
     <row r="183" ht="22.5" customHeight="1">
@@ -19588,11 +19732,11 @@
         <v>1627</v>
       </c>
       <c r="D183" s="9" t="s">
-        <v>2281</v>
+        <v>2291</v>
       </c>
       <c r="E183" s="22"/>
-      <c r="F183" s="109" t="s">
-        <v>2282</v>
+      <c r="F183" s="111" t="s">
+        <v>2292</v>
       </c>
     </row>
     <row r="184" ht="22.5" customHeight="1">
@@ -19603,14 +19747,14 @@
         <v>201</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>2273</v>
+        <v>2283</v>
       </c>
       <c r="D184" s="3" t="s">
-        <v>2283</v>
+        <v>2293</v>
       </c>
       <c r="E184" s="21"/>
-      <c r="F184" s="108" t="s">
-        <v>2284</v>
+      <c r="F184" s="110" t="s">
+        <v>2294</v>
       </c>
     </row>
     <row r="185" ht="22.5" customHeight="1">
@@ -19621,14 +19765,14 @@
         <v>202</v>
       </c>
       <c r="C185" s="9" t="s">
-        <v>2273</v>
+        <v>2283</v>
       </c>
       <c r="D185" s="9" t="s">
-        <v>2285</v>
+        <v>2295</v>
       </c>
       <c r="E185" s="22"/>
-      <c r="F185" s="109" t="s">
-        <v>2286</v>
+      <c r="F185" s="111" t="s">
+        <v>2296</v>
       </c>
     </row>
     <row r="186" ht="22.5" customHeight="1">
@@ -19639,14 +19783,14 @@
         <v>203</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>2287</v>
+        <v>2297</v>
       </c>
       <c r="D186" s="3" t="s">
-        <v>2288</v>
+        <v>2298</v>
       </c>
       <c r="E186" s="21"/>
-      <c r="F186" s="108" t="s">
-        <v>2289</v>
+      <c r="F186" s="110" t="s">
+        <v>2299</v>
       </c>
     </row>
     <row r="187" ht="22.5" customHeight="1">
@@ -19657,14 +19801,14 @@
         <v>204</v>
       </c>
       <c r="C187" s="9" t="s">
-        <v>2273</v>
+        <v>2283</v>
       </c>
       <c r="D187" s="9" t="s">
-        <v>2290</v>
+        <v>2300</v>
       </c>
       <c r="E187" s="22"/>
-      <c r="F187" s="109" t="s">
-        <v>2291</v>
+      <c r="F187" s="111" t="s">
+        <v>2301</v>
       </c>
     </row>
     <row r="188" ht="22.5" customHeight="1">
@@ -19675,14 +19819,14 @@
         <v>204</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>2292</v>
+        <v>2302</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>2293</v>
+        <v>2303</v>
       </c>
       <c r="E188" s="21"/>
-      <c r="F188" s="108" t="s">
-        <v>2294</v>
+      <c r="F188" s="110" t="s">
+        <v>2304</v>
       </c>
     </row>
     <row r="189" ht="22.5" customHeight="1">
@@ -19693,14 +19837,14 @@
         <v>207</v>
       </c>
       <c r="C189" s="9" t="s">
-        <v>2292</v>
+        <v>2302</v>
       </c>
       <c r="D189" s="9" t="s">
-        <v>2295</v>
+        <v>2305</v>
       </c>
       <c r="E189" s="22"/>
       <c r="F189" s="55" t="s">
-        <v>2296</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="190" ht="22.5" customHeight="1">
@@ -19711,14 +19855,14 @@
         <v>208</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>2273</v>
+        <v>2283</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>2297</v>
+        <v>2307</v>
       </c>
       <c r="E190" s="21"/>
-      <c r="F190" s="108" t="s">
-        <v>2298</v>
+      <c r="F190" s="110" t="s">
+        <v>2308</v>
       </c>
     </row>
     <row r="191" ht="22.5" customHeight="1">
@@ -19729,14 +19873,14 @@
         <v>209</v>
       </c>
       <c r="C191" s="9" t="s">
-        <v>2273</v>
+        <v>2283</v>
       </c>
       <c r="D191" s="9" t="s">
-        <v>2299</v>
+        <v>2309</v>
       </c>
       <c r="E191" s="22"/>
-      <c r="F191" s="109" t="s">
-        <v>2300</v>
+      <c r="F191" s="111" t="s">
+        <v>2310</v>
       </c>
     </row>
     <row r="192" ht="22.5" customHeight="1">
@@ -19750,11 +19894,11 @@
         <v>1627</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>2301</v>
+        <v>2311</v>
       </c>
       <c r="E192" s="21"/>
-      <c r="F192" s="108" t="s">
-        <v>2302</v>
+      <c r="F192" s="110" t="s">
+        <v>2312</v>
       </c>
     </row>
     <row r="193" ht="22.5" customHeight="1">
@@ -19765,14 +19909,14 @@
         <v>209</v>
       </c>
       <c r="C193" s="9" t="s">
-        <v>2292</v>
+        <v>2302</v>
       </c>
       <c r="D193" s="9" t="s">
-        <v>2303</v>
+        <v>2313</v>
       </c>
       <c r="E193" s="22"/>
-      <c r="F193" s="109" t="s">
-        <v>2304</v>
+      <c r="F193" s="111" t="s">
+        <v>2314</v>
       </c>
     </row>
     <row r="194" ht="22.5" customHeight="1">
@@ -19783,14 +19927,14 @@
         <v>209</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>2305</v>
+        <v>2315</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>2306</v>
+        <v>2316</v>
       </c>
       <c r="E194" s="21"/>
-      <c r="F194" s="108" t="s">
-        <v>2307</v>
+      <c r="F194" s="110" t="s">
+        <v>2317</v>
       </c>
     </row>
     <row r="195" ht="22.5" customHeight="1">
@@ -19801,14 +19945,14 @@
         <v>103</v>
       </c>
       <c r="C195" s="9" t="s">
-        <v>2273</v>
+        <v>2283</v>
       </c>
       <c r="D195" s="9" t="s">
-        <v>2308</v>
+        <v>2318</v>
       </c>
       <c r="E195" s="22"/>
-      <c r="F195" s="109" t="s">
-        <v>2309</v>
+      <c r="F195" s="111" t="s">
+        <v>2319</v>
       </c>
     </row>
     <row r="196" ht="22.5" customHeight="1">
@@ -19819,14 +19963,14 @@
         <v>211</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>2273</v>
+        <v>2283</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>2310</v>
+        <v>2320</v>
       </c>
       <c r="E196" s="21"/>
-      <c r="F196" s="108" t="s">
-        <v>2311</v>
+      <c r="F196" s="110" t="s">
+        <v>2321</v>
       </c>
     </row>
     <row r="197" ht="22.5" customHeight="1">
@@ -19837,14 +19981,14 @@
         <v>212</v>
       </c>
       <c r="C197" s="9" t="s">
-        <v>2273</v>
+        <v>2283</v>
       </c>
       <c r="D197" s="9" t="s">
-        <v>2312</v>
+        <v>2322</v>
       </c>
       <c r="E197" s="22"/>
-      <c r="F197" s="109" t="s">
-        <v>2313</v>
+      <c r="F197" s="111" t="s">
+        <v>2323</v>
       </c>
     </row>
     <row r="198" ht="22.5" customHeight="1">
@@ -19855,14 +19999,14 @@
         <v>214</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>2314</v>
+        <v>2324</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>2315</v>
+        <v>2325</v>
       </c>
       <c r="E198" s="21"/>
-      <c r="F198" s="108" t="s">
-        <v>2316</v>
+      <c r="F198" s="110" t="s">
+        <v>2326</v>
       </c>
     </row>
     <row r="199" ht="22.5" customHeight="1">
@@ -19873,14 +20017,14 @@
         <v>216</v>
       </c>
       <c r="C199" s="9" t="s">
-        <v>2273</v>
+        <v>2283</v>
       </c>
       <c r="D199" s="9" t="s">
-        <v>2317</v>
+        <v>2327</v>
       </c>
       <c r="E199" s="22"/>
-      <c r="F199" s="109" t="s">
-        <v>2318</v>
+      <c r="F199" s="111" t="s">
+        <v>2328</v>
       </c>
     </row>
     <row r="200" ht="22.5" customHeight="1">
@@ -19891,14 +20035,14 @@
         <v>217</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>2314</v>
+        <v>2324</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>2319</v>
+        <v>2329</v>
       </c>
       <c r="E200" s="21"/>
-      <c r="F200" s="108" t="s">
-        <v>2320</v>
+      <c r="F200" s="110" t="s">
+        <v>2330</v>
       </c>
     </row>
     <row r="201" ht="22.5" customHeight="1">
@@ -19909,14 +20053,14 @@
         <v>217</v>
       </c>
       <c r="C201" s="9" t="s">
-        <v>2292</v>
+        <v>2302</v>
       </c>
       <c r="D201" s="9" t="s">
-        <v>2321</v>
+        <v>2331</v>
       </c>
       <c r="E201" s="22"/>
-      <c r="F201" s="109" t="s">
-        <v>2322</v>
+      <c r="F201" s="111" t="s">
+        <v>2332</v>
       </c>
     </row>
     <row r="202" ht="22.5" customHeight="1">
@@ -19930,11 +20074,11 @@
         <v>1630</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>2323</v>
+        <v>2333</v>
       </c>
       <c r="E202" s="21"/>
-      <c r="F202" s="108" t="s">
-        <v>2322</v>
+      <c r="F202" s="110" t="s">
+        <v>2332</v>
       </c>
     </row>
     <row r="203" ht="22.5" customHeight="1">
@@ -19948,11 +20092,11 @@
         <v>1627</v>
       </c>
       <c r="D203" s="9" t="s">
-        <v>2324</v>
+        <v>2334</v>
       </c>
       <c r="E203" s="22"/>
-      <c r="F203" s="109" t="s">
-        <v>2325</v>
+      <c r="F203" s="111" t="s">
+        <v>2335</v>
       </c>
     </row>
     <row r="204" ht="22.5" customHeight="1">
@@ -19963,14 +20107,14 @@
         <v>219</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>2273</v>
+        <v>2283</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>2326</v>
+        <v>2336</v>
       </c>
       <c r="E204" s="21"/>
-      <c r="F204" s="108" t="s">
-        <v>2327</v>
+      <c r="F204" s="110" t="s">
+        <v>2337</v>
       </c>
     </row>
     <row r="205" ht="22.5" customHeight="1">
@@ -19981,14 +20125,14 @@
         <v>219</v>
       </c>
       <c r="C205" s="9" t="s">
-        <v>2287</v>
+        <v>2297</v>
       </c>
       <c r="D205" s="9" t="s">
-        <v>2328</v>
+        <v>2338</v>
       </c>
       <c r="E205" s="22"/>
-      <c r="F205" s="109" t="s">
-        <v>2329</v>
+      <c r="F205" s="111" t="s">
+        <v>2339</v>
       </c>
     </row>
     <row r="206" ht="22.5" customHeight="1">
@@ -19999,14 +20143,14 @@
         <v>219</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>2330</v>
+        <v>2340</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>2331</v>
+        <v>2341</v>
       </c>
       <c r="E206" s="21"/>
-      <c r="F206" s="108" t="s">
-        <v>2332</v>
+      <c r="F206" s="110" t="s">
+        <v>2342</v>
       </c>
     </row>
     <row r="207" ht="22.5" customHeight="1">
@@ -20020,11 +20164,11 @@
         <v>1627</v>
       </c>
       <c r="D207" s="9" t="s">
-        <v>2333</v>
+        <v>2343</v>
       </c>
       <c r="E207" s="22"/>
-      <c r="F207" s="109" t="s">
-        <v>2334</v>
+      <c r="F207" s="111" t="s">
+        <v>2344</v>
       </c>
     </row>
     <row r="208" ht="22.5" customHeight="1">
@@ -20038,11 +20182,11 @@
         <v>1627</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>2335</v>
+        <v>2345</v>
       </c>
       <c r="E208" s="21"/>
-      <c r="F208" s="108" t="s">
-        <v>2336</v>
+      <c r="F208" s="110" t="s">
+        <v>2346</v>
       </c>
     </row>
     <row r="209" ht="22.5" customHeight="1">
@@ -20053,14 +20197,14 @@
         <v>224</v>
       </c>
       <c r="C209" s="9" t="s">
-        <v>2273</v>
+        <v>2283</v>
       </c>
       <c r="D209" s="9" t="s">
-        <v>2337</v>
+        <v>2347</v>
       </c>
       <c r="E209" s="22"/>
-      <c r="F209" s="109" t="s">
-        <v>2338</v>
+      <c r="F209" s="111" t="s">
+        <v>2348</v>
       </c>
     </row>
     <row r="210" ht="22.5" customHeight="1">
@@ -20071,14 +20215,14 @@
         <v>224</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>2287</v>
+        <v>2297</v>
       </c>
       <c r="D210" s="3" t="s">
-        <v>2339</v>
+        <v>2349</v>
       </c>
       <c r="E210" s="21"/>
-      <c r="F210" s="108" t="s">
-        <v>2340</v>
+      <c r="F210" s="110" t="s">
+        <v>2350</v>
       </c>
     </row>
     <row r="211" ht="22.5" customHeight="1">
@@ -20089,14 +20233,14 @@
         <v>225</v>
       </c>
       <c r="C211" s="9" t="s">
-        <v>2292</v>
+        <v>2302</v>
       </c>
       <c r="D211" s="9" t="s">
-        <v>2341</v>
+        <v>2351</v>
       </c>
       <c r="E211" s="22"/>
-      <c r="F211" s="109" t="s">
-        <v>2342</v>
+      <c r="F211" s="111" t="s">
+        <v>2352</v>
       </c>
     </row>
     <row r="212" ht="22.5" customHeight="1">
@@ -20107,13 +20251,13 @@
         <v>226</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>2343</v>
+        <v>2353</v>
       </c>
       <c r="D212" s="3" t="s">
-        <v>2343</v>
+        <v>2353</v>
       </c>
       <c r="E212" s="21"/>
-      <c r="F212" s="118"/>
+      <c r="F212" s="120"/>
     </row>
     <row r="213" ht="22.5" customHeight="1">
       <c r="A213" s="8" t="s">
@@ -20123,14 +20267,14 @@
         <v>228</v>
       </c>
       <c r="C213" s="9" t="s">
-        <v>2273</v>
+        <v>2283</v>
       </c>
       <c r="D213" s="9" t="s">
-        <v>2344</v>
+        <v>2354</v>
       </c>
       <c r="E213" s="22"/>
-      <c r="F213" s="109" t="s">
-        <v>2345</v>
+      <c r="F213" s="111" t="s">
+        <v>2355</v>
       </c>
     </row>
     <row r="214" ht="22.5" customHeight="1">
@@ -20141,14 +20285,14 @@
         <v>228</v>
       </c>
       <c r="C214" s="3" t="s">
-        <v>2292</v>
+        <v>2302</v>
       </c>
       <c r="D214" s="3" t="s">
-        <v>2346</v>
+        <v>2356</v>
       </c>
       <c r="E214" s="21"/>
-      <c r="F214" s="108" t="s">
-        <v>2347</v>
+      <c r="F214" s="110" t="s">
+        <v>2357</v>
       </c>
     </row>
     <row r="215" ht="22.5" customHeight="1">
@@ -20159,14 +20303,14 @@
         <v>228</v>
       </c>
       <c r="C215" s="9" t="s">
-        <v>2292</v>
+        <v>2302</v>
       </c>
       <c r="D215" s="9" t="s">
-        <v>2348</v>
+        <v>2358</v>
       </c>
       <c r="E215" s="22"/>
-      <c r="F215" s="109" t="s">
-        <v>2349</v>
+      <c r="F215" s="111" t="s">
+        <v>2359</v>
       </c>
     </row>
     <row r="216" ht="22.5" customHeight="1">
@@ -20177,14 +20321,14 @@
         <v>228</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>2350</v>
+        <v>2360</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>2351</v>
+        <v>2361</v>
       </c>
       <c r="E216" s="21"/>
-      <c r="F216" s="108" t="s">
-        <v>2352</v>
+      <c r="F216" s="110" t="s">
+        <v>2362</v>
       </c>
     </row>
     <row r="217" ht="22.5" customHeight="1">
@@ -20195,14 +20339,14 @@
         <v>230</v>
       </c>
       <c r="C217" s="9" t="s">
-        <v>2273</v>
+        <v>2283</v>
       </c>
       <c r="D217" s="9" t="s">
-        <v>2353</v>
+        <v>2363</v>
       </c>
       <c r="E217" s="22"/>
-      <c r="F217" s="109" t="s">
-        <v>2354</v>
+      <c r="F217" s="111" t="s">
+        <v>2364</v>
       </c>
     </row>
     <row r="218" ht="22.5" customHeight="1">
@@ -20213,13 +20357,13 @@
         <v>231</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>2343</v>
+        <v>2353</v>
       </c>
       <c r="D218" s="3" t="s">
-        <v>2343</v>
+        <v>2353</v>
       </c>
       <c r="E218" s="21"/>
-      <c r="F218" s="118"/>
+      <c r="F218" s="120"/>
     </row>
     <row r="219" ht="22.5" customHeight="1">
       <c r="A219" s="8" t="s">
@@ -20232,11 +20376,11 @@
         <v>1627</v>
       </c>
       <c r="D219" s="9" t="s">
-        <v>2355</v>
+        <v>2365</v>
       </c>
       <c r="E219" s="22"/>
       <c r="F219" s="55" t="s">
-        <v>2356</v>
+        <v>2366</v>
       </c>
     </row>
     <row r="220" ht="22.5" customHeight="1">
@@ -20250,11 +20394,11 @@
         <v>1627</v>
       </c>
       <c r="D220" s="34" t="s">
-        <v>2357</v>
+        <v>2367</v>
       </c>
       <c r="E220" s="35"/>
-      <c r="F220" s="113" t="s">
-        <v>2358</v>
+      <c r="F220" s="115" t="s">
+        <v>2368</v>
       </c>
     </row>
   </sheetData>
@@ -20285,7 +20429,7 @@
         <v>260</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2359</v>
+        <v>2369</v>
       </c>
     </row>
     <row r="2" ht="22.5" customHeight="1">
@@ -20296,7 +20440,7 @@
         <v>257</v>
       </c>
       <c r="C2" s="53" t="s">
-        <v>2360</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1">
@@ -20307,7 +20451,7 @@
         <v>257</v>
       </c>
       <c r="C3" s="55" t="s">
-        <v>2361</v>
+        <v>2371</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
@@ -20318,7 +20462,7 @@
         <v>257</v>
       </c>
       <c r="C4" s="53" t="s">
-        <v>2362</v>
+        <v>2372</v>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1">
@@ -20329,7 +20473,7 @@
         <v>257</v>
       </c>
       <c r="C5" s="55" t="s">
-        <v>1903</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1">
@@ -20339,8 +20483,8 @@
       <c r="B6" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="C6" s="119" t="s">
-        <v>2363</v>
+      <c r="C6" s="121" t="s">
+        <v>2373</v>
       </c>
     </row>
   </sheetData>

--- a/docs/assets/GaGu DB.xlsx
+++ b/docs/assets/GaGu DB.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10198" uniqueCount="2482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10198" uniqueCount="2504">
   <si>
     <t>CODE</t>
   </si>
@@ -4923,7 +4923,7 @@
     <t>assets/images/gi/icons/GI_Hydro.png</t>
   </si>
   <si>
-    <t>Hydro,Electro-Charged,Charged Attack,AoE,Ranged,ATK,CRIT</t>
+    <t>Hydro,Electro-Charged,Charged Attack,AoE,Ranged,HP,CRIT</t>
   </si>
   <si>
     <t>ELE_RE</t>
@@ -5949,6 +5949,24 @@
     <t>{ "style": "background-color: #ef7938" }</t>
   </si>
   <si>
+    <t>{ "style": "background-color: #4cc2f1" }</t>
+  </si>
+  <si>
+    <t>{ "style": "background-color: #a5c83b" }</t>
+  </si>
+  <si>
+    <t>{ "style": "background-color: #af8ec1" }</t>
+  </si>
+  <si>
+    <t>{ "style": "background-color: #74c2a8" }</t>
+  </si>
+  <si>
+    <t>{ "style": "background-color: #9fd6e3" }</t>
+  </si>
+  <si>
+    <t>{ "style": "background-color: #fab632" }</t>
+  </si>
+  <si>
     <t>{ "style": null }</t>
   </si>
   <si>
@@ -5976,15 +5994,30 @@
     <t>Lunar-Bloom</t>
   </si>
   <si>
+    <t>{ "style": "background: linear-gradient(0deg, white, #a5c83b);" }</t>
+  </si>
+  <si>
     <t>Lunar-Charged</t>
   </si>
   <si>
+    <t>{ "style": "background: linear-gradient(0deg, white, #af8ec1);" }</t>
+  </si>
+  <si>
     <t>Lunar-Crystalize</t>
   </si>
   <si>
+    <t>{ "style": "background: linear-gradient(0deg, white, #fab632);" }</t>
+  </si>
+  <si>
     <t>Stellar-Conduct</t>
   </si>
   <si>
+    <t>{ "style": "background: linear-gradient(0deg, #af8ec1, #9fd6e3);" }</t>
+  </si>
+  <si>
+    <t>{ "style": "background-color: black; border: 1px solid white" }</t>
+  </si>
+  <si>
     <t>Normal Attack</t>
   </si>
   <si>
@@ -6006,7 +6039,40 @@
     <t>Ranged</t>
   </si>
   <si>
+    <t>{ "style": "background-color: #979797" }</t>
+  </si>
+  <si>
+    <t>{ "style": "background-color: #ff5521" }</t>
+  </si>
+  <si>
+    <t>{ "style": "background-color: #98eff0" }</t>
+  </si>
+  <si>
+    <t>{ "style": "background-color: #c65ade" }</t>
+  </si>
+  <si>
+    <t>{ "style": "background-color: #61cf93" }</t>
+  </si>
+  <si>
+    <t>{ "style": "background-color: #766dd6" }</t>
+  </si>
+  <si>
+    <t>{ "style": "background-color: #f3e137" }</t>
+  </si>
+  <si>
     <t>FuA</t>
+  </si>
+  <si>
+    <t>{ "style": "background-color: #f0d12b" }</t>
+  </si>
+  <si>
+    <t>{ "style": "background-color: #2eb6ff" }</t>
+  </si>
+  <si>
+    <t>{ "style": "background-color: #fe437e" }</t>
+  </si>
+  <si>
+    <t>{ "style": "background-color: #61a6ff" }</t>
   </si>
   <si>
     <t>Chain Attack</t>
@@ -14247,7 +14313,7 @@
     <col customWidth="1" min="2" max="3" width="18.13"/>
     <col customWidth="1" min="4" max="4" width="12.63"/>
     <col customWidth="1" min="5" max="5" width="43.13"/>
-    <col customWidth="1" min="6" max="6" width="16.75"/>
+    <col customWidth="1" min="6" max="6" width="31.38"/>
   </cols>
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
@@ -15676,7 +15742,7 @@
         <v>1956</v>
       </c>
       <c r="F77" s="128" t="s">
-        <v>1958</v>
+        <v>1959</v>
       </c>
     </row>
     <row r="78" ht="22.5" customHeight="1">
@@ -15693,7 +15759,7 @@
         <v>1956</v>
       </c>
       <c r="F78" s="128" t="s">
-        <v>1958</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="79" ht="22.5" customHeight="1">
@@ -15710,7 +15776,7 @@
         <v>1956</v>
       </c>
       <c r="F79" s="128" t="s">
-        <v>1958</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="80" ht="22.5" customHeight="1">
@@ -15727,7 +15793,7 @@
         <v>1956</v>
       </c>
       <c r="F80" s="128" t="s">
-        <v>1958</v>
+        <v>1962</v>
       </c>
     </row>
     <row r="81" ht="22.5" customHeight="1">
@@ -15744,7 +15810,7 @@
         <v>1956</v>
       </c>
       <c r="F81" s="128" t="s">
-        <v>1958</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="82" ht="22.5" customHeight="1">
@@ -15761,7 +15827,7 @@
         <v>1956</v>
       </c>
       <c r="F82" s="128" t="s">
-        <v>1958</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="83" ht="22.5" customHeight="1">
@@ -15778,7 +15844,7 @@
         <v>1956</v>
       </c>
       <c r="F83" s="128" t="s">
-        <v>1958</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="84" ht="22.5" customHeight="1">
@@ -15795,7 +15861,7 @@
         <v>1956</v>
       </c>
       <c r="F84" s="128" t="s">
-        <v>1958</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="85" ht="22.5" customHeight="1">
@@ -15803,16 +15869,16 @@
         <v>10</v>
       </c>
       <c r="B85" s="128" t="s">
-        <v>1959</v>
+        <v>1965</v>
       </c>
       <c r="C85" s="128" t="s">
-        <v>1959</v>
+        <v>1965</v>
       </c>
       <c r="D85" s="42" t="s">
         <v>1956</v>
       </c>
       <c r="F85" s="128" t="s">
-        <v>1958</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="86" ht="22.5" customHeight="1">
@@ -15820,16 +15886,16 @@
         <v>10</v>
       </c>
       <c r="B86" s="128" t="s">
-        <v>1960</v>
+        <v>1966</v>
       </c>
       <c r="C86" s="128" t="s">
-        <v>1960</v>
+        <v>1966</v>
       </c>
       <c r="D86" s="42" t="s">
         <v>1956</v>
       </c>
       <c r="F86" s="128" t="s">
-        <v>1958</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="87" ht="22.5" customHeight="1">
@@ -15837,16 +15903,16 @@
         <v>10</v>
       </c>
       <c r="B87" s="128" t="s">
-        <v>1961</v>
+        <v>1967</v>
       </c>
       <c r="C87" s="128" t="s">
-        <v>1961</v>
+        <v>1967</v>
       </c>
       <c r="D87" s="42" t="s">
         <v>1956</v>
       </c>
       <c r="F87" s="128" t="s">
-        <v>1958</v>
+        <v>1962</v>
       </c>
     </row>
     <row r="88" ht="22.5" customHeight="1">
@@ -15854,16 +15920,16 @@
         <v>10</v>
       </c>
       <c r="B88" s="128" t="s">
-        <v>1962</v>
+        <v>1968</v>
       </c>
       <c r="C88" s="128" t="s">
-        <v>1962</v>
+        <v>1968</v>
       </c>
       <c r="D88" s="42" t="s">
         <v>1956</v>
       </c>
       <c r="F88" s="128" t="s">
-        <v>1958</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="89" ht="22.5" customHeight="1">
@@ -15871,16 +15937,16 @@
         <v>10</v>
       </c>
       <c r="B89" s="128" t="s">
-        <v>1963</v>
+        <v>1969</v>
       </c>
       <c r="C89" s="128" t="s">
-        <v>1963</v>
+        <v>1969</v>
       </c>
       <c r="D89" s="42" t="s">
         <v>1956</v>
       </c>
       <c r="F89" s="128" t="s">
-        <v>1958</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="90" ht="22.5" customHeight="1">
@@ -15888,16 +15954,16 @@
         <v>10</v>
       </c>
       <c r="B90" s="128" t="s">
-        <v>1964</v>
+        <v>1970</v>
       </c>
       <c r="C90" s="128" t="s">
-        <v>1964</v>
+        <v>1970</v>
       </c>
       <c r="D90" s="42" t="s">
         <v>1956</v>
       </c>
       <c r="F90" s="128" t="s">
-        <v>1958</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="91" ht="22.5" customHeight="1">
@@ -15905,16 +15971,16 @@
         <v>10</v>
       </c>
       <c r="B91" s="128" t="s">
-        <v>1965</v>
+        <v>1971</v>
       </c>
       <c r="C91" s="128" t="s">
-        <v>1965</v>
+        <v>1971</v>
       </c>
       <c r="D91" s="42" t="s">
         <v>1956</v>
       </c>
       <c r="F91" s="128" t="s">
-        <v>1958</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="92" ht="22.5" customHeight="1">
@@ -15931,7 +15997,7 @@
         <v>1956</v>
       </c>
       <c r="F92" s="128" t="s">
-        <v>1958</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="93" ht="22.5" customHeight="1">
@@ -15939,16 +16005,16 @@
         <v>10</v>
       </c>
       <c r="B93" s="128" t="s">
-        <v>1966</v>
+        <v>1972</v>
       </c>
       <c r="C93" s="128" t="s">
-        <v>1966</v>
+        <v>1972</v>
       </c>
       <c r="D93" s="42" t="s">
         <v>1956</v>
       </c>
       <c r="F93" s="128" t="s">
-        <v>1958</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="94" ht="22.5" customHeight="1">
@@ -15956,16 +16022,16 @@
         <v>10</v>
       </c>
       <c r="B94" s="128" t="s">
-        <v>1967</v>
+        <v>1974</v>
       </c>
       <c r="C94" s="128" t="s">
-        <v>1967</v>
+        <v>1974</v>
       </c>
       <c r="D94" s="42" t="s">
         <v>1956</v>
       </c>
       <c r="F94" s="128" t="s">
-        <v>1958</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="95" ht="22.5" customHeight="1">
@@ -15973,16 +16039,16 @@
         <v>10</v>
       </c>
       <c r="B95" s="128" t="s">
-        <v>1968</v>
+        <v>1976</v>
       </c>
       <c r="C95" s="128" t="s">
-        <v>1968</v>
+        <v>1976</v>
       </c>
       <c r="D95" s="42" t="s">
         <v>1956</v>
       </c>
       <c r="F95" s="128" t="s">
-        <v>1958</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="96" ht="22.5" customHeight="1">
@@ -15990,16 +16056,16 @@
         <v>10</v>
       </c>
       <c r="B96" s="128" t="s">
-        <v>1969</v>
+        <v>1978</v>
       </c>
       <c r="C96" s="128" t="s">
-        <v>1969</v>
+        <v>1978</v>
       </c>
       <c r="D96" s="42" t="s">
         <v>1956</v>
       </c>
       <c r="F96" s="128" t="s">
-        <v>1958</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="97" ht="22.5" customHeight="1">
@@ -16016,7 +16082,7 @@
         <v>1956</v>
       </c>
       <c r="F97" s="128" t="s">
-        <v>1958</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="98" ht="22.5" customHeight="1">
@@ -16033,7 +16099,7 @@
         <v>1956</v>
       </c>
       <c r="F98" s="128" t="s">
-        <v>1958</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="99" ht="22.5" customHeight="1">
@@ -16050,7 +16116,7 @@
         <v>1956</v>
       </c>
       <c r="F99" s="128" t="s">
-        <v>1958</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="100" ht="22.5" customHeight="1">
@@ -16058,16 +16124,16 @@
         <v>10</v>
       </c>
       <c r="B100" s="128" t="s">
-        <v>1970</v>
+        <v>1981</v>
       </c>
       <c r="C100" s="128" t="s">
-        <v>1970</v>
+        <v>1981</v>
       </c>
       <c r="D100" s="42" t="s">
         <v>1956</v>
       </c>
       <c r="F100" s="128" t="s">
-        <v>1958</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="101" ht="22.5" customHeight="1">
@@ -16084,7 +16150,7 @@
         <v>1956</v>
       </c>
       <c r="F101" s="128" t="s">
-        <v>1958</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="102" ht="22.5" customHeight="1">
@@ -16092,16 +16158,16 @@
         <v>10</v>
       </c>
       <c r="B102" s="128" t="s">
-        <v>1971</v>
+        <v>1982</v>
       </c>
       <c r="C102" s="128" t="s">
-        <v>1971</v>
+        <v>1982</v>
       </c>
       <c r="D102" s="42" t="s">
         <v>1956</v>
       </c>
       <c r="F102" s="128" t="s">
-        <v>1958</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="103" ht="22.5" customHeight="1">
@@ -16118,7 +16184,7 @@
         <v>1956</v>
       </c>
       <c r="F103" s="128" t="s">
-        <v>1958</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="104" ht="22.5" customHeight="1">
@@ -16135,7 +16201,7 @@
         <v>1956</v>
       </c>
       <c r="F104" s="128" t="s">
-        <v>1958</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="105" ht="22.5" customHeight="1">
@@ -16152,7 +16218,7 @@
         <v>1956</v>
       </c>
       <c r="F105" s="128" t="s">
-        <v>1958</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="106" ht="22.5" customHeight="1">
@@ -16160,16 +16226,16 @@
         <v>10</v>
       </c>
       <c r="B106" s="128" t="s">
-        <v>1972</v>
+        <v>1983</v>
       </c>
       <c r="C106" s="128" t="s">
-        <v>1972</v>
+        <v>1983</v>
       </c>
       <c r="D106" s="42" t="s">
         <v>1956</v>
       </c>
       <c r="F106" s="128" t="s">
-        <v>1958</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="107" ht="22.5" customHeight="1">
@@ -16177,16 +16243,16 @@
         <v>10</v>
       </c>
       <c r="B107" s="128" t="s">
-        <v>1973</v>
+        <v>1984</v>
       </c>
       <c r="C107" s="128" t="s">
-        <v>1973</v>
+        <v>1984</v>
       </c>
       <c r="D107" s="42" t="s">
         <v>1956</v>
       </c>
       <c r="F107" s="128" t="s">
-        <v>1958</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="108" ht="22.5" customHeight="1">
@@ -16203,7 +16269,7 @@
         <v>1956</v>
       </c>
       <c r="F108" s="128" t="s">
-        <v>1958</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="109" ht="22.5" customHeight="1">
@@ -16211,16 +16277,16 @@
         <v>10</v>
       </c>
       <c r="B109" s="128" t="s">
-        <v>1974</v>
+        <v>1985</v>
       </c>
       <c r="C109" s="128" t="s">
-        <v>1974</v>
+        <v>1985</v>
       </c>
       <c r="D109" s="42" t="s">
         <v>1956</v>
       </c>
       <c r="F109" s="128" t="s">
-        <v>1958</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="110" ht="22.5" customHeight="1">
@@ -16228,16 +16294,16 @@
         <v>10</v>
       </c>
       <c r="B110" s="128" t="s">
-        <v>1975</v>
+        <v>1986</v>
       </c>
       <c r="C110" s="128" t="s">
-        <v>1975</v>
+        <v>1986</v>
       </c>
       <c r="D110" s="42" t="s">
         <v>1956</v>
       </c>
       <c r="F110" s="128" t="s">
-        <v>1958</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="111" ht="22.5" customHeight="1">
@@ -16245,16 +16311,16 @@
         <v>10</v>
       </c>
       <c r="B111" s="128" t="s">
-        <v>1976</v>
+        <v>1987</v>
       </c>
       <c r="C111" s="128" t="s">
-        <v>1976</v>
+        <v>1987</v>
       </c>
       <c r="D111" s="42" t="s">
         <v>1956</v>
       </c>
       <c r="F111" s="128" t="s">
-        <v>1958</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="112" ht="22.5" customHeight="1">
@@ -16271,7 +16337,7 @@
         <v>1956</v>
       </c>
       <c r="F112" s="128" t="s">
-        <v>1958</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="113" ht="22.5" customHeight="1">
@@ -16288,7 +16354,7 @@
         <v>1956</v>
       </c>
       <c r="F113" s="128" t="s">
-        <v>1958</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="114" ht="22.5" customHeight="1">
@@ -16305,7 +16371,7 @@
         <v>1956</v>
       </c>
       <c r="F114" s="128" t="s">
-        <v>1958</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="115" ht="22.5" customHeight="1">
@@ -16322,7 +16388,7 @@
         <v>1956</v>
       </c>
       <c r="F115" s="128" t="s">
-        <v>1958</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="116" ht="22.5" customHeight="1">
@@ -16339,7 +16405,7 @@
         <v>1956</v>
       </c>
       <c r="F116" s="128" t="s">
-        <v>1958</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="117" ht="22.5" customHeight="1">
@@ -16356,7 +16422,7 @@
         <v>1956</v>
       </c>
       <c r="F117" s="128" t="s">
-        <v>1958</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="118" ht="22.5" customHeight="1">
@@ -16373,7 +16439,7 @@
         <v>1956</v>
       </c>
       <c r="F118" s="128" t="s">
-        <v>1958</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="119" ht="22.5" customHeight="1">
@@ -16390,7 +16456,7 @@
         <v>1956</v>
       </c>
       <c r="F119" s="128" t="s">
-        <v>1958</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="120" ht="22.5" customHeight="1">
@@ -16407,7 +16473,7 @@
         <v>1956</v>
       </c>
       <c r="F120" s="128" t="s">
-        <v>1958</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="121" ht="22.5" customHeight="1">
@@ -16415,16 +16481,16 @@
         <v>17</v>
       </c>
       <c r="B121" s="128" t="s">
-        <v>1972</v>
+        <v>1983</v>
       </c>
       <c r="C121" s="128" t="s">
-        <v>1972</v>
+        <v>1983</v>
       </c>
       <c r="D121" s="42" t="s">
         <v>1956</v>
       </c>
       <c r="F121" s="128" t="s">
-        <v>1958</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="122" ht="22.5" customHeight="1">
@@ -16441,7 +16507,7 @@
         <v>1956</v>
       </c>
       <c r="F122" s="128" t="s">
-        <v>1958</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="123" ht="22.5" customHeight="1">
@@ -16458,7 +16524,7 @@
         <v>1956</v>
       </c>
       <c r="F123" s="128" t="s">
-        <v>1958</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="124" ht="22.5" customHeight="1">
@@ -16466,16 +16532,16 @@
         <v>17</v>
       </c>
       <c r="B124" s="128" t="s">
-        <v>1977</v>
+        <v>1995</v>
       </c>
       <c r="C124" s="128" t="s">
-        <v>1977</v>
+        <v>1995</v>
       </c>
       <c r="D124" s="42" t="s">
         <v>1956</v>
       </c>
       <c r="F124" s="128" t="s">
-        <v>1958</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="125" ht="22.5" customHeight="1">
@@ -16492,7 +16558,7 @@
         <v>1956</v>
       </c>
       <c r="F125" s="128" t="s">
-        <v>1958</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="126" ht="22.5" customHeight="1">
@@ -16509,7 +16575,7 @@
         <v>1956</v>
       </c>
       <c r="F126" s="128" t="s">
-        <v>1958</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="127" ht="22.5" customHeight="1">
@@ -16526,7 +16592,7 @@
         <v>1956</v>
       </c>
       <c r="F127" s="128" t="s">
-        <v>1958</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="128" ht="22.5" customHeight="1">
@@ -16534,16 +16600,16 @@
         <v>17</v>
       </c>
       <c r="B128" s="128" t="s">
-        <v>1971</v>
+        <v>1982</v>
       </c>
       <c r="C128" s="128" t="s">
-        <v>1971</v>
+        <v>1982</v>
       </c>
       <c r="D128" s="42" t="s">
         <v>1956</v>
       </c>
       <c r="F128" s="128" t="s">
-        <v>1958</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="129" ht="22.5" customHeight="1">
@@ -16560,7 +16626,7 @@
         <v>1956</v>
       </c>
       <c r="F129" s="128" t="s">
-        <v>1958</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="130" ht="22.5" customHeight="1">
@@ -16568,16 +16634,16 @@
         <v>17</v>
       </c>
       <c r="B130" s="128" t="s">
-        <v>1973</v>
+        <v>1984</v>
       </c>
       <c r="C130" s="128" t="s">
-        <v>1973</v>
+        <v>1984</v>
       </c>
       <c r="D130" s="42" t="s">
         <v>1956</v>
       </c>
       <c r="F130" s="128" t="s">
-        <v>1958</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="131" ht="22.5" customHeight="1">
@@ -16594,7 +16660,7 @@
         <v>1956</v>
       </c>
       <c r="F131" s="128" t="s">
-        <v>1958</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="132" ht="22.5" customHeight="1">
@@ -16611,7 +16677,7 @@
         <v>1956</v>
       </c>
       <c r="F132" s="128" t="s">
-        <v>1958</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="133" ht="22.5" customHeight="1">
@@ -16628,7 +16694,7 @@
         <v>1956</v>
       </c>
       <c r="F133" s="128" t="s">
-        <v>1958</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="134" ht="22.5" customHeight="1">
@@ -16645,7 +16711,7 @@
         <v>1956</v>
       </c>
       <c r="F134" s="128" t="s">
-        <v>1958</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="135" ht="22.5" customHeight="1">
@@ -16662,7 +16728,7 @@
         <v>1956</v>
       </c>
       <c r="F135" s="128" t="s">
-        <v>1958</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="136" ht="22.5" customHeight="1">
@@ -16679,7 +16745,7 @@
         <v>1956</v>
       </c>
       <c r="F136" s="128" t="s">
-        <v>1958</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="137" ht="22.5" customHeight="1">
@@ -16696,7 +16762,7 @@
         <v>1956</v>
       </c>
       <c r="F137" s="128" t="s">
-        <v>1958</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="138" ht="22.5" customHeight="1">
@@ -16713,7 +16779,7 @@
         <v>1956</v>
       </c>
       <c r="F138" s="128" t="s">
-        <v>1958</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="139" ht="22.5" customHeight="1">
@@ -16730,7 +16796,7 @@
         <v>1956</v>
       </c>
       <c r="F139" s="128" t="s">
-        <v>1958</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="140" ht="22.5" customHeight="1">
@@ -16738,16 +16804,16 @@
         <v>23</v>
       </c>
       <c r="B140" s="128" t="s">
-        <v>1972</v>
+        <v>1983</v>
       </c>
       <c r="C140" s="128" t="s">
-        <v>1972</v>
+        <v>1983</v>
       </c>
       <c r="D140" s="42" t="s">
         <v>1956</v>
       </c>
       <c r="F140" s="128" t="s">
-        <v>1958</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="141" ht="22.5" customHeight="1">
@@ -16764,7 +16830,7 @@
         <v>1956</v>
       </c>
       <c r="F141" s="128" t="s">
-        <v>1958</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="142" ht="22.5" customHeight="1">
@@ -16781,7 +16847,7 @@
         <v>1956</v>
       </c>
       <c r="F142" s="128" t="s">
-        <v>1958</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="143" ht="22.5" customHeight="1">
@@ -16798,7 +16864,7 @@
         <v>1956</v>
       </c>
       <c r="F143" s="128" t="s">
-        <v>1958</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="144" ht="22.5" customHeight="1">
@@ -16815,7 +16881,7 @@
         <v>1956</v>
       </c>
       <c r="F144" s="128" t="s">
-        <v>1958</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="145" ht="22.5" customHeight="1">
@@ -16823,16 +16889,16 @@
         <v>23</v>
       </c>
       <c r="B145" s="128" t="s">
-        <v>1978</v>
+        <v>2000</v>
       </c>
       <c r="C145" s="128" t="s">
-        <v>1978</v>
+        <v>2000</v>
       </c>
       <c r="D145" s="42" t="s">
         <v>1956</v>
       </c>
       <c r="F145" s="128" t="s">
-        <v>1958</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="146" ht="22.5" customHeight="1">
@@ -16849,7 +16915,7 @@
         <v>1956</v>
       </c>
       <c r="F146" s="128" t="s">
-        <v>1958</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="147" ht="22.5" customHeight="1">
@@ -16866,7 +16932,7 @@
         <v>1956</v>
       </c>
       <c r="F147" s="128" t="s">
-        <v>1958</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="148" ht="22.5" customHeight="1">
@@ -16883,7 +16949,7 @@
         <v>1956</v>
       </c>
       <c r="F148" s="128" t="s">
-        <v>1958</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="149" ht="22.5" customHeight="1">
@@ -16891,16 +16957,16 @@
         <v>23</v>
       </c>
       <c r="B149" s="128" t="s">
-        <v>1979</v>
+        <v>2001</v>
       </c>
       <c r="C149" s="128" t="s">
-        <v>1979</v>
+        <v>2001</v>
       </c>
       <c r="D149" s="42" t="s">
         <v>1956</v>
       </c>
       <c r="F149" s="128" t="s">
-        <v>1958</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="150" ht="22.5" customHeight="1">
@@ -16917,7 +16983,7 @@
         <v>1956</v>
       </c>
       <c r="F150" s="128" t="s">
-        <v>1958</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="151" ht="22.5" customHeight="1">
@@ -16928,14 +16994,14 @@
         <v>1610</v>
       </c>
       <c r="C151" s="126" t="s">
-        <v>1980</v>
+        <v>2002</v>
       </c>
       <c r="D151" s="129" t="s">
         <v>1605</v>
       </c>
       <c r="E151" s="130"/>
       <c r="F151" s="128" t="s">
-        <v>1981</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="152" ht="22.5" customHeight="1">
@@ -16946,14 +17012,14 @@
         <v>1617</v>
       </c>
       <c r="C152" s="126" t="s">
-        <v>1982</v>
+        <v>2004</v>
       </c>
       <c r="D152" s="129" t="s">
         <v>1605</v>
       </c>
       <c r="E152" s="130"/>
       <c r="F152" s="128" t="s">
-        <v>1983</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="153" ht="22.5" customHeight="1">
@@ -16964,14 +17030,14 @@
         <v>1633</v>
       </c>
       <c r="C153" s="126" t="s">
-        <v>1984</v>
+        <v>2006</v>
       </c>
       <c r="D153" s="129" t="s">
         <v>1605</v>
       </c>
       <c r="E153" s="130"/>
       <c r="F153" s="128" t="s">
-        <v>1985</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="154" ht="22.5" customHeight="1">
@@ -16982,14 +17048,14 @@
         <v>1610</v>
       </c>
       <c r="C154" s="126" t="s">
-        <v>1980</v>
+        <v>2002</v>
       </c>
       <c r="D154" s="129" t="s">
         <v>1605</v>
       </c>
       <c r="E154" s="130"/>
       <c r="F154" s="128" t="s">
-        <v>1981</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="155" ht="22.5" customHeight="1">
@@ -17000,14 +17066,14 @@
         <v>1652</v>
       </c>
       <c r="C155" s="126" t="s">
-        <v>1986</v>
+        <v>2008</v>
       </c>
       <c r="D155" s="129" t="s">
         <v>1605</v>
       </c>
       <c r="E155" s="130"/>
       <c r="F155" s="128" t="s">
-        <v>1983</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="156" ht="22.5" customHeight="1">
@@ -17018,14 +17084,14 @@
         <v>1610</v>
       </c>
       <c r="C156" s="126" t="s">
-        <v>1980</v>
+        <v>2002</v>
       </c>
       <c r="D156" s="129" t="s">
         <v>1605</v>
       </c>
       <c r="E156" s="130"/>
       <c r="F156" s="128" t="s">
-        <v>1981</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="157" ht="22.5" customHeight="1">
@@ -17043,7 +17109,7 @@
       </c>
       <c r="E157" s="130"/>
       <c r="F157" s="128" t="s">
-        <v>1983</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="158" ht="22.5" customHeight="1">
@@ -17054,14 +17120,14 @@
         <v>1652</v>
       </c>
       <c r="C158" s="126" t="s">
-        <v>1986</v>
+        <v>2008</v>
       </c>
       <c r="D158" s="129" t="s">
         <v>1605</v>
       </c>
       <c r="E158" s="130"/>
       <c r="F158" s="128" t="s">
-        <v>1987</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="159" ht="22.5" customHeight="1">
@@ -17072,14 +17138,14 @@
         <v>1610</v>
       </c>
       <c r="C159" s="126" t="s">
-        <v>1980</v>
+        <v>2002</v>
       </c>
       <c r="D159" s="129" t="s">
         <v>1605</v>
       </c>
       <c r="E159" s="130"/>
       <c r="F159" s="128" t="s">
-        <v>1981</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="160" ht="22.5" customHeight="1">
@@ -17090,14 +17156,14 @@
         <v>1633</v>
       </c>
       <c r="C160" s="126" t="s">
-        <v>1984</v>
+        <v>2006</v>
       </c>
       <c r="D160" s="129" t="s">
         <v>1605</v>
       </c>
       <c r="E160" s="130"/>
       <c r="F160" s="128" t="s">
-        <v>1983</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="161" ht="22.5" customHeight="1">
@@ -17111,10 +17177,10 @@
         <v>192</v>
       </c>
       <c r="D161" s="42" t="s">
-        <v>1988</v>
+        <v>2010</v>
       </c>
       <c r="E161" s="43" t="s">
-        <v>1989</v>
+        <v>2011</v>
       </c>
       <c r="F161" s="128"/>
     </row>
@@ -17123,16 +17189,16 @@
         <v>35</v>
       </c>
       <c r="B162" s="126" t="s">
-        <v>1990</v>
+        <v>2012</v>
       </c>
       <c r="C162" s="126" t="s">
-        <v>1990</v>
+        <v>2012</v>
       </c>
       <c r="D162" s="42" t="s">
-        <v>1988</v>
+        <v>2010</v>
       </c>
       <c r="E162" s="43" t="s">
-        <v>1991</v>
+        <v>2013</v>
       </c>
       <c r="F162" s="128"/>
     </row>
@@ -17141,16 +17207,16 @@
         <v>35</v>
       </c>
       <c r="B163" s="126" t="s">
-        <v>1992</v>
+        <v>2014</v>
       </c>
       <c r="C163" s="126" t="s">
-        <v>1992</v>
+        <v>2014</v>
       </c>
       <c r="D163" s="42" t="s">
-        <v>1988</v>
+        <v>2010</v>
       </c>
       <c r="E163" s="43" t="s">
-        <v>1993</v>
+        <v>2015</v>
       </c>
       <c r="F163" s="128"/>
     </row>
@@ -17165,10 +17231,10 @@
         <v>1492</v>
       </c>
       <c r="D164" s="42" t="s">
-        <v>1988</v>
+        <v>2010</v>
       </c>
       <c r="E164" s="43" t="s">
-        <v>1994</v>
+        <v>2016</v>
       </c>
       <c r="F164" s="128"/>
     </row>
@@ -17177,16 +17243,16 @@
         <v>35</v>
       </c>
       <c r="B165" s="126" t="s">
-        <v>1995</v>
+        <v>2017</v>
       </c>
       <c r="C165" s="126" t="s">
-        <v>1996</v>
+        <v>2018</v>
       </c>
       <c r="D165" s="42" t="s">
-        <v>1988</v>
+        <v>2010</v>
       </c>
       <c r="E165" s="43" t="s">
-        <v>1997</v>
+        <v>2019</v>
       </c>
       <c r="F165" s="128"/>
     </row>
@@ -17195,16 +17261,16 @@
         <v>35</v>
       </c>
       <c r="B166" s="126" t="s">
-        <v>1998</v>
+        <v>2020</v>
       </c>
       <c r="C166" s="126" t="s">
-        <v>1999</v>
+        <v>2021</v>
       </c>
       <c r="D166" s="42" t="s">
-        <v>1988</v>
+        <v>2010</v>
       </c>
       <c r="E166" s="43" t="s">
-        <v>2000</v>
+        <v>2022</v>
       </c>
       <c r="F166" s="128"/>
     </row>
@@ -17213,16 +17279,16 @@
         <v>35</v>
       </c>
       <c r="B167" s="126" t="s">
-        <v>2001</v>
+        <v>2023</v>
       </c>
       <c r="C167" s="126" t="s">
-        <v>2002</v>
+        <v>2024</v>
       </c>
       <c r="D167" s="42" t="s">
-        <v>1988</v>
+        <v>2010</v>
       </c>
       <c r="E167" s="43" t="s">
-        <v>2003</v>
+        <v>2025</v>
       </c>
       <c r="F167" s="128"/>
     </row>
@@ -17234,13 +17300,13 @@
         <v>1049</v>
       </c>
       <c r="C168" s="126" t="s">
-        <v>2004</v>
+        <v>2026</v>
       </c>
       <c r="D168" s="42" t="s">
-        <v>1988</v>
+        <v>2010</v>
       </c>
       <c r="E168" s="43" t="s">
-        <v>2005</v>
+        <v>2027</v>
       </c>
       <c r="F168" s="128"/>
     </row>
@@ -17249,16 +17315,16 @@
         <v>35</v>
       </c>
       <c r="B169" s="126" t="s">
-        <v>2006</v>
+        <v>2028</v>
       </c>
       <c r="C169" s="126" t="s">
-        <v>2007</v>
+        <v>2029</v>
       </c>
       <c r="D169" s="42" t="s">
-        <v>1988</v>
+        <v>2010</v>
       </c>
       <c r="E169" s="43" t="s">
-        <v>2008</v>
+        <v>2030</v>
       </c>
       <c r="F169" s="128"/>
     </row>
@@ -17267,16 +17333,16 @@
         <v>35</v>
       </c>
       <c r="B170" s="126" t="s">
-        <v>2009</v>
+        <v>2031</v>
       </c>
       <c r="C170" s="126" t="s">
+        <v>2032</v>
+      </c>
+      <c r="D170" s="42" t="s">
         <v>2010</v>
       </c>
-      <c r="D170" s="42" t="s">
-        <v>1988</v>
-      </c>
       <c r="E170" s="43" t="s">
-        <v>2011</v>
+        <v>2033</v>
       </c>
       <c r="F170" s="128"/>
     </row>
@@ -17285,16 +17351,16 @@
         <v>35</v>
       </c>
       <c r="B171" s="126" t="s">
-        <v>2012</v>
+        <v>2034</v>
       </c>
       <c r="C171" s="126" t="s">
-        <v>2013</v>
+        <v>2035</v>
       </c>
       <c r="D171" s="42" t="s">
-        <v>1988</v>
+        <v>2010</v>
       </c>
       <c r="E171" s="43" t="s">
-        <v>2014</v>
+        <v>2036</v>
       </c>
       <c r="F171" s="128"/>
     </row>
@@ -17303,16 +17369,16 @@
         <v>35</v>
       </c>
       <c r="B172" s="126" t="s">
-        <v>2015</v>
+        <v>2037</v>
       </c>
       <c r="C172" s="126" t="s">
-        <v>2016</v>
+        <v>2038</v>
       </c>
       <c r="D172" s="42" t="s">
-        <v>1988</v>
+        <v>2010</v>
       </c>
       <c r="E172" s="43" t="s">
-        <v>2017</v>
+        <v>2039</v>
       </c>
       <c r="F172" s="128"/>
     </row>
@@ -17327,10 +17393,10 @@
         <v>217</v>
       </c>
       <c r="D173" s="42" t="s">
-        <v>1988</v>
+        <v>2010</v>
       </c>
       <c r="E173" s="43" t="s">
-        <v>2018</v>
+        <v>2040</v>
       </c>
       <c r="F173" s="128"/>
     </row>
@@ -17339,16 +17405,16 @@
         <v>35</v>
       </c>
       <c r="B174" s="126" t="s">
-        <v>2019</v>
+        <v>2041</v>
       </c>
       <c r="C174" s="126" t="s">
-        <v>2019</v>
+        <v>2041</v>
       </c>
       <c r="D174" s="42" t="s">
-        <v>1988</v>
+        <v>2010</v>
       </c>
       <c r="E174" s="43" t="s">
-        <v>2020</v>
+        <v>2042</v>
       </c>
       <c r="F174" s="128"/>
     </row>
@@ -17357,16 +17423,16 @@
         <v>35</v>
       </c>
       <c r="B175" s="126" t="s">
-        <v>2021</v>
+        <v>2043</v>
       </c>
       <c r="C175" s="126" t="s">
-        <v>2021</v>
+        <v>2043</v>
       </c>
       <c r="D175" s="42" t="s">
-        <v>1988</v>
+        <v>2010</v>
       </c>
       <c r="E175" s="43" t="s">
-        <v>2022</v>
+        <v>2044</v>
       </c>
       <c r="F175" s="128"/>
     </row>
@@ -17375,16 +17441,16 @@
         <v>35</v>
       </c>
       <c r="B176" s="126" t="s">
-        <v>2023</v>
+        <v>2045</v>
       </c>
       <c r="C176" s="126" t="s">
-        <v>2023</v>
+        <v>2045</v>
       </c>
       <c r="D176" s="42" t="s">
-        <v>1988</v>
+        <v>2010</v>
       </c>
       <c r="E176" s="43" t="s">
-        <v>2024</v>
+        <v>2046</v>
       </c>
       <c r="F176" s="128"/>
     </row>
@@ -17421,7 +17487,7 @@
         <v>50</v>
       </c>
       <c r="D1" s="20" t="s">
-        <v>2025</v>
+        <v>2047</v>
       </c>
       <c r="E1" s="20" t="s">
         <v>265</v>
@@ -17438,14 +17504,14 @@
         <v>57</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>2026</v>
+        <v>2048</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>2027</v>
+        <v>2049</v>
       </c>
       <c r="E2" s="21"/>
       <c r="F2" s="120" t="s">
-        <v>2028</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1">
@@ -17456,14 +17522,14 @@
         <v>57</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>2029</v>
+        <v>2051</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>2030</v>
+        <v>2052</v>
       </c>
       <c r="E3" s="22"/>
       <c r="F3" s="121" t="s">
-        <v>2031</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
@@ -17474,14 +17540,14 @@
         <v>61</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>2032</v>
+        <v>2054</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>2033</v>
+        <v>2055</v>
       </c>
       <c r="E4" s="21"/>
       <c r="F4" s="57" t="s">
-        <v>2034</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1">
@@ -17492,14 +17558,14 @@
         <v>64</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>2026</v>
+        <v>2048</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>2035</v>
+        <v>2057</v>
       </c>
       <c r="E5" s="22"/>
       <c r="F5" s="121" t="s">
-        <v>2036</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1">
@@ -17510,14 +17576,14 @@
         <v>67</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>2032</v>
+        <v>2054</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>2037</v>
+        <v>2059</v>
       </c>
       <c r="E6" s="21"/>
       <c r="F6" s="120" t="s">
-        <v>2038</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
@@ -17528,14 +17594,14 @@
         <v>67</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>2039</v>
+        <v>2061</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>2040</v>
+        <v>2062</v>
       </c>
       <c r="E7" s="22"/>
       <c r="F7" s="121" t="s">
-        <v>2041</v>
+        <v>2063</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
@@ -17546,14 +17612,14 @@
         <v>70</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>2032</v>
+        <v>2054</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>2042</v>
+        <v>2064</v>
       </c>
       <c r="E8" s="21"/>
       <c r="F8" s="120" t="s">
-        <v>2043</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="9" ht="22.5" customHeight="1">
@@ -17564,14 +17630,14 @@
         <v>70</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>2039</v>
+        <v>2061</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>2044</v>
+        <v>2066</v>
       </c>
       <c r="E9" s="22"/>
       <c r="F9" s="121" t="s">
-        <v>2045</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
@@ -17582,14 +17648,14 @@
         <v>70</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>2046</v>
+        <v>2068</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>2047</v>
+        <v>2069</v>
       </c>
       <c r="E10" s="21"/>
       <c r="F10" s="120" t="s">
-        <v>2048</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
@@ -17600,14 +17666,14 @@
         <v>70</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>2049</v>
+        <v>2071</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>2050</v>
+        <v>2072</v>
       </c>
       <c r="E11" s="22"/>
       <c r="F11" s="121" t="s">
-        <v>2051</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="12" ht="22.5" customHeight="1">
@@ -17618,14 +17684,14 @@
         <v>71</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>1970</v>
+        <v>1981</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>2052</v>
+        <v>2074</v>
       </c>
       <c r="E12" s="21"/>
       <c r="F12" s="120" t="s">
-        <v>2053</v>
+        <v>2075</v>
       </c>
     </row>
     <row r="13" ht="22.5" customHeight="1">
@@ -17636,14 +17702,14 @@
         <v>71</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>2032</v>
+        <v>2054</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>2054</v>
+        <v>2076</v>
       </c>
       <c r="E13" s="22"/>
       <c r="F13" s="121" t="s">
-        <v>2055</v>
+        <v>2077</v>
       </c>
     </row>
     <row r="14" ht="22.5" customHeight="1">
@@ -17654,14 +17720,14 @@
         <v>71</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>2039</v>
+        <v>2061</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>2056</v>
+        <v>2078</v>
       </c>
       <c r="E14" s="21"/>
       <c r="F14" s="120" t="s">
-        <v>2057</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="15" ht="22.5" customHeight="1">
@@ -17672,14 +17738,14 @@
         <v>73</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>2032</v>
+        <v>2054</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>2058</v>
+        <v>2080</v>
       </c>
       <c r="E15" s="22"/>
       <c r="F15" s="121" t="s">
-        <v>2059</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="16" ht="22.5" customHeight="1">
@@ -17690,14 +17756,14 @@
         <v>73</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>2039</v>
+        <v>2061</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>2060</v>
+        <v>2082</v>
       </c>
       <c r="E16" s="21"/>
       <c r="F16" s="120" t="s">
-        <v>2061</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="17" ht="22.5" customHeight="1">
@@ -17708,14 +17774,14 @@
         <v>76</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>2032</v>
+        <v>2054</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>2062</v>
+        <v>2084</v>
       </c>
       <c r="E17" s="22"/>
       <c r="F17" s="121" t="s">
-        <v>2063</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="18" ht="22.5" customHeight="1">
@@ -17726,14 +17792,14 @@
         <v>78</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>2032</v>
+        <v>2054</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>2064</v>
+        <v>2086</v>
       </c>
       <c r="E18" s="21"/>
       <c r="F18" s="120" t="s">
-        <v>2028</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="19" ht="22.5" customHeight="1">
@@ -17744,14 +17810,14 @@
         <v>78</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>2026</v>
+        <v>2048</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>2065</v>
+        <v>2087</v>
       </c>
       <c r="E19" s="22"/>
       <c r="F19" s="121" t="s">
-        <v>2066</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="20" ht="22.5" customHeight="1">
@@ -17762,14 +17828,14 @@
         <v>78</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>2067</v>
+        <v>2089</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>2068</v>
+        <v>2090</v>
       </c>
       <c r="E20" s="21"/>
       <c r="F20" s="120" t="s">
-        <v>2069</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="21" ht="22.5" customHeight="1">
@@ -17780,14 +17846,14 @@
         <v>79</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>2032</v>
+        <v>2054</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>2070</v>
+        <v>2092</v>
       </c>
       <c r="E21" s="22"/>
       <c r="F21" s="121" t="s">
-        <v>2071</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="22" ht="22.5" customHeight="1">
@@ -17798,14 +17864,14 @@
         <v>80</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>2026</v>
+        <v>2048</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>2072</v>
+        <v>2094</v>
       </c>
       <c r="E22" s="21"/>
       <c r="F22" s="120" t="s">
-        <v>2073</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="23" ht="22.5" customHeight="1">
@@ -17816,14 +17882,14 @@
         <v>81</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>2026</v>
+        <v>2048</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>2074</v>
+        <v>2096</v>
       </c>
       <c r="E23" s="22"/>
       <c r="F23" s="121" t="s">
-        <v>2075</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="24" ht="22.5" customHeight="1">
@@ -17834,14 +17900,14 @@
         <v>81</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>2039</v>
+        <v>2061</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>2076</v>
+        <v>2098</v>
       </c>
       <c r="E24" s="21"/>
       <c r="F24" s="120" t="s">
-        <v>2077</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="25" ht="22.5" customHeight="1">
@@ -17849,17 +17915,17 @@
         <v>10</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>2078</v>
+        <v>2100</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>2032</v>
+        <v>2054</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>2079</v>
+        <v>2101</v>
       </c>
       <c r="E25" s="22"/>
       <c r="F25" s="121" t="s">
-        <v>2080</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="26" ht="22.5" customHeight="1">
@@ -17870,14 +17936,14 @@
         <v>82</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>2026</v>
+        <v>2048</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>2081</v>
+        <v>2103</v>
       </c>
       <c r="E26" s="21"/>
       <c r="F26" s="120" t="s">
-        <v>2082</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="27" ht="22.5" customHeight="1">
@@ -17888,14 +17954,14 @@
         <v>82</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>2046</v>
+        <v>2068</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>2083</v>
+        <v>2105</v>
       </c>
       <c r="E27" s="22"/>
       <c r="F27" s="121" t="s">
-        <v>2084</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="28" ht="22.5" customHeight="1">
@@ -17906,14 +17972,14 @@
         <v>83</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>2026</v>
+        <v>2048</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>2085</v>
+        <v>2107</v>
       </c>
       <c r="E28" s="21"/>
       <c r="F28" s="120" t="s">
-        <v>2086</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="29" ht="22.5" customHeight="1">
@@ -17921,17 +17987,17 @@
         <v>10</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>2087</v>
+        <v>2109</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>2026</v>
+        <v>2048</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>2088</v>
+        <v>2110</v>
       </c>
       <c r="E29" s="22"/>
       <c r="F29" s="121" t="s">
-        <v>2089</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="30" ht="22.5" customHeight="1">
@@ -17942,14 +18008,14 @@
         <v>84</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>2032</v>
+        <v>2054</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>2090</v>
+        <v>2112</v>
       </c>
       <c r="E30" s="21"/>
       <c r="F30" s="120" t="s">
-        <v>2091</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="31" ht="22.5" customHeight="1">
@@ -17960,14 +18026,14 @@
         <v>85</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>2032</v>
+        <v>2054</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>2092</v>
+        <v>2114</v>
       </c>
       <c r="E31" s="22"/>
       <c r="F31" s="121" t="s">
-        <v>2093</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="32" ht="22.5" customHeight="1">
@@ -17978,14 +18044,14 @@
         <v>85</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>2026</v>
+        <v>2048</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>2094</v>
+        <v>2116</v>
       </c>
       <c r="E32" s="21"/>
       <c r="F32" s="120" t="s">
-        <v>2095</v>
+        <v>2117</v>
       </c>
     </row>
     <row r="33" ht="22.5" customHeight="1">
@@ -17996,14 +18062,14 @@
         <v>86</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>2032</v>
+        <v>2054</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>2096</v>
+        <v>2118</v>
       </c>
       <c r="E33" s="22"/>
       <c r="F33" s="121" t="s">
-        <v>2097</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="34" ht="22.5" customHeight="1">
@@ -18014,14 +18080,14 @@
         <v>86</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>2026</v>
+        <v>2048</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>2098</v>
+        <v>2120</v>
       </c>
       <c r="E34" s="21"/>
       <c r="F34" s="120" t="s">
-        <v>2099</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="35" ht="22.5" customHeight="1">
@@ -18032,14 +18098,14 @@
         <v>86</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>2049</v>
+        <v>2071</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>2100</v>
+        <v>2122</v>
       </c>
       <c r="E35" s="22"/>
       <c r="F35" s="121" t="s">
-        <v>2101</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="36" ht="22.5" customHeight="1">
@@ -18050,14 +18116,14 @@
         <v>87</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>2032</v>
+        <v>2054</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>2102</v>
+        <v>2124</v>
       </c>
       <c r="E36" s="21"/>
       <c r="F36" s="120" t="s">
-        <v>2073</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="37" ht="22.5" customHeight="1">
@@ -18068,14 +18134,14 @@
         <v>87</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>2103</v>
+        <v>2125</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>2104</v>
+        <v>2126</v>
       </c>
       <c r="E37" s="22"/>
       <c r="F37" s="121" t="s">
-        <v>2105</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="38" ht="22.5" customHeight="1">
@@ -18086,14 +18152,14 @@
         <v>88</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>2026</v>
+        <v>2048</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>2106</v>
+        <v>2128</v>
       </c>
       <c r="E38" s="21"/>
       <c r="F38" s="120" t="s">
-        <v>2107</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="39" ht="22.5" customHeight="1">
@@ -18104,14 +18170,14 @@
         <v>89</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>2032</v>
+        <v>2054</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>2108</v>
+        <v>2130</v>
       </c>
       <c r="E39" s="22"/>
       <c r="F39" s="121" t="s">
-        <v>2109</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="40" ht="22.5" customHeight="1">
@@ -18122,14 +18188,14 @@
         <v>92</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>2032</v>
+        <v>2054</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>2110</v>
+        <v>2132</v>
       </c>
       <c r="E40" s="21"/>
       <c r="F40" s="120" t="s">
-        <v>2111</v>
+        <v>2133</v>
       </c>
     </row>
     <row r="41" ht="22.5" customHeight="1">
@@ -18140,14 +18206,14 @@
         <v>93</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>2032</v>
+        <v>2054</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>2112</v>
+        <v>2134</v>
       </c>
       <c r="E41" s="22"/>
       <c r="F41" s="121" t="s">
-        <v>2113</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="42" ht="22.5" customHeight="1">
@@ -18158,14 +18224,14 @@
         <v>94</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>2032</v>
+        <v>2054</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>2114</v>
+        <v>2136</v>
       </c>
       <c r="E42" s="21"/>
       <c r="F42" s="120" t="s">
-        <v>2115</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="43" ht="22.5" customHeight="1">
@@ -18176,14 +18242,14 @@
         <v>94</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>2026</v>
+        <v>2048</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>2116</v>
+        <v>2138</v>
       </c>
       <c r="E43" s="22"/>
       <c r="F43" s="121" t="s">
-        <v>2117</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="44" ht="22.5" customHeight="1">
@@ -18194,14 +18260,14 @@
         <v>94</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>2103</v>
+        <v>2125</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>2118</v>
+        <v>2140</v>
       </c>
       <c r="E44" s="21"/>
       <c r="F44" s="120" t="s">
-        <v>2119</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="45" ht="22.5" customHeight="1">
@@ -18212,14 +18278,14 @@
         <v>94</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>2029</v>
+        <v>2051</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>2120</v>
+        <v>2142</v>
       </c>
       <c r="E45" s="22"/>
       <c r="F45" s="121" t="s">
-        <v>2121</v>
+        <v>2143</v>
       </c>
     </row>
     <row r="46" ht="22.5" customHeight="1">
@@ -18230,14 +18296,14 @@
         <v>96</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>2032</v>
+        <v>2054</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>2122</v>
+        <v>2144</v>
       </c>
       <c r="E46" s="21"/>
       <c r="F46" s="120" t="s">
-        <v>2123</v>
+        <v>2145</v>
       </c>
     </row>
     <row r="47" ht="22.5" customHeight="1">
@@ -18248,14 +18314,14 @@
         <v>96</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>2026</v>
+        <v>2048</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>2124</v>
+        <v>2146</v>
       </c>
       <c r="E47" s="22"/>
       <c r="F47" s="121" t="s">
-        <v>2125</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="48" ht="22.5" customHeight="1">
@@ -18266,14 +18332,14 @@
         <v>96</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>2046</v>
+        <v>2068</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>2126</v>
+        <v>2148</v>
       </c>
       <c r="E48" s="21"/>
       <c r="F48" s="120" t="s">
-        <v>2127</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="49" ht="22.5" customHeight="1">
@@ -18284,14 +18350,14 @@
         <v>97</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>2039</v>
+        <v>2061</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>2128</v>
+        <v>2150</v>
       </c>
       <c r="E49" s="22"/>
       <c r="F49" s="121" t="s">
-        <v>2129</v>
+        <v>2151</v>
       </c>
     </row>
     <row r="50" ht="22.5" customHeight="1">
@@ -18302,14 +18368,14 @@
         <v>97</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>2046</v>
+        <v>2068</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>2130</v>
+        <v>2152</v>
       </c>
       <c r="E50" s="21"/>
       <c r="F50" s="120" t="s">
-        <v>2131</v>
+        <v>2153</v>
       </c>
     </row>
     <row r="51" ht="22.5" customHeight="1">
@@ -18320,14 +18386,14 @@
         <v>97</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>2049</v>
+        <v>2071</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>2132</v>
+        <v>2154</v>
       </c>
       <c r="E51" s="22"/>
       <c r="F51" s="121" t="s">
-        <v>2133</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="52" ht="22.5" customHeight="1">
@@ -18338,14 +18404,14 @@
         <v>98</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>2032</v>
+        <v>2054</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>2134</v>
+        <v>2156</v>
       </c>
       <c r="E52" s="21"/>
       <c r="F52" s="120" t="s">
-        <v>2135</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="53" ht="22.5" customHeight="1">
@@ -18356,14 +18422,14 @@
         <v>99</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>2032</v>
+        <v>2054</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>2136</v>
+        <v>2158</v>
       </c>
       <c r="E53" s="22"/>
       <c r="F53" s="121" t="s">
-        <v>2137</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="54" ht="22.5" customHeight="1">
@@ -18374,14 +18440,14 @@
         <v>99</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>2039</v>
+        <v>2061</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>2138</v>
+        <v>2160</v>
       </c>
       <c r="E54" s="21"/>
       <c r="F54" s="120" t="s">
-        <v>2139</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="55" ht="22.5" customHeight="1">
@@ -18392,14 +18458,14 @@
         <v>99</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>2140</v>
+        <v>2162</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>2141</v>
+        <v>2163</v>
       </c>
       <c r="E55" s="22"/>
       <c r="F55" s="121" t="s">
-        <v>2142</v>
+        <v>2164</v>
       </c>
     </row>
     <row r="56" ht="22.5" customHeight="1">
@@ -18410,14 +18476,14 @@
         <v>100</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>2032</v>
+        <v>2054</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>2143</v>
+        <v>2165</v>
       </c>
       <c r="E56" s="21"/>
       <c r="F56" s="120" t="s">
-        <v>2144</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="57" ht="22.5" customHeight="1">
@@ -18428,14 +18494,14 @@
         <v>101</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>2032</v>
+        <v>2054</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>2145</v>
+        <v>2167</v>
       </c>
       <c r="E57" s="22"/>
       <c r="F57" s="121" t="s">
-        <v>2146</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="58" ht="22.5" customHeight="1">
@@ -18446,14 +18512,14 @@
         <v>101</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>2039</v>
+        <v>2061</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>2147</v>
+        <v>2169</v>
       </c>
       <c r="E58" s="21"/>
       <c r="F58" s="120" t="s">
-        <v>2148</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="59" ht="22.5" customHeight="1">
@@ -18464,14 +18530,14 @@
         <v>101</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>2029</v>
+        <v>2051</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>2149</v>
+        <v>2171</v>
       </c>
       <c r="E59" s="22"/>
       <c r="F59" s="121" t="s">
-        <v>2121</v>
+        <v>2143</v>
       </c>
     </row>
     <row r="60" ht="22.5" customHeight="1">
@@ -18482,14 +18548,14 @@
         <v>102</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>1970</v>
+        <v>1981</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>2150</v>
+        <v>2172</v>
       </c>
       <c r="E60" s="21"/>
       <c r="F60" s="120" t="s">
-        <v>2151</v>
+        <v>2173</v>
       </c>
     </row>
     <row r="61" ht="22.5" customHeight="1">
@@ -18500,14 +18566,14 @@
         <v>102</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>2039</v>
+        <v>2061</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>2152</v>
+        <v>2174</v>
       </c>
       <c r="E61" s="22"/>
       <c r="F61" s="121" t="s">
-        <v>2153</v>
+        <v>2175</v>
       </c>
     </row>
     <row r="62" ht="22.5" customHeight="1">
@@ -18518,14 +18584,14 @@
         <v>102</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>2103</v>
+        <v>2125</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>2154</v>
+        <v>2176</v>
       </c>
       <c r="E62" s="21"/>
       <c r="F62" s="120" t="s">
-        <v>2155</v>
+        <v>2177</v>
       </c>
     </row>
     <row r="63" ht="22.5" customHeight="1">
@@ -18536,14 +18602,14 @@
         <v>104</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>2032</v>
+        <v>2054</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>2156</v>
+        <v>2178</v>
       </c>
       <c r="E63" s="22"/>
       <c r="F63" s="121" t="s">
-        <v>2157</v>
+        <v>2179</v>
       </c>
     </row>
     <row r="64" ht="22.5" customHeight="1">
@@ -18554,14 +18620,14 @@
         <v>104</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>2039</v>
+        <v>2061</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>2158</v>
+        <v>2180</v>
       </c>
       <c r="E64" s="21"/>
       <c r="F64" s="120" t="s">
-        <v>2159</v>
+        <v>2181</v>
       </c>
     </row>
     <row r="65" ht="22.5" customHeight="1">
@@ -18569,17 +18635,17 @@
         <v>10</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>2160</v>
+        <v>2182</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>2026</v>
+        <v>2048</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>2161</v>
+        <v>2183</v>
       </c>
       <c r="E65" s="22"/>
       <c r="F65" s="121" t="s">
-        <v>2162</v>
+        <v>2184</v>
       </c>
     </row>
     <row r="66" ht="22.5" customHeight="1">
@@ -18590,14 +18656,14 @@
         <v>107</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>2032</v>
+        <v>2054</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>2163</v>
+        <v>2185</v>
       </c>
       <c r="E66" s="21"/>
       <c r="F66" s="120" t="s">
-        <v>2164</v>
+        <v>2186</v>
       </c>
     </row>
     <row r="67" ht="22.5" customHeight="1">
@@ -18608,14 +18674,14 @@
         <v>109</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>2032</v>
+        <v>2054</v>
       </c>
       <c r="D67" s="9" t="s">
-        <v>2165</v>
+        <v>2187</v>
       </c>
       <c r="E67" s="22"/>
       <c r="F67" s="121" t="s">
-        <v>2166</v>
+        <v>2188</v>
       </c>
     </row>
     <row r="68" ht="22.5" customHeight="1">
@@ -18626,14 +18692,14 @@
         <v>109</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>2026</v>
+        <v>2048</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>2167</v>
+        <v>2189</v>
       </c>
       <c r="E68" s="21"/>
       <c r="F68" s="120" t="s">
-        <v>2168</v>
+        <v>2190</v>
       </c>
     </row>
     <row r="69" ht="22.5" customHeight="1">
@@ -18644,14 +18710,14 @@
         <v>110</v>
       </c>
       <c r="C69" s="9" t="s">
-        <v>2032</v>
+        <v>2054</v>
       </c>
       <c r="D69" s="9" t="s">
-        <v>2169</v>
+        <v>2191</v>
       </c>
       <c r="E69" s="22"/>
       <c r="F69" s="121" t="s">
-        <v>2170</v>
+        <v>2192</v>
       </c>
     </row>
     <row r="70" ht="22.5" customHeight="1">
@@ -18662,14 +18728,14 @@
         <v>110</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>2026</v>
+        <v>2048</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>2171</v>
+        <v>2193</v>
       </c>
       <c r="E70" s="21"/>
       <c r="F70" s="120" t="s">
-        <v>2172</v>
+        <v>2194</v>
       </c>
     </row>
     <row r="71" ht="22.5" customHeight="1">
@@ -18680,14 +18746,14 @@
         <v>110</v>
       </c>
       <c r="C71" s="9" t="s">
-        <v>2046</v>
+        <v>2068</v>
       </c>
       <c r="D71" s="9" t="s">
-        <v>2173</v>
+        <v>2195</v>
       </c>
       <c r="E71" s="22"/>
       <c r="F71" s="121" t="s">
-        <v>2174</v>
+        <v>2196</v>
       </c>
     </row>
     <row r="72" ht="22.5" customHeight="1">
@@ -18698,14 +18764,14 @@
         <v>111</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>2026</v>
+        <v>2048</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>2175</v>
+        <v>2197</v>
       </c>
       <c r="E72" s="21"/>
       <c r="F72" s="120" t="s">
-        <v>2176</v>
+        <v>2198</v>
       </c>
     </row>
     <row r="73" ht="22.5" customHeight="1">
@@ -18716,14 +18782,14 @@
         <v>112</v>
       </c>
       <c r="C73" s="9" t="s">
-        <v>1970</v>
+        <v>1981</v>
       </c>
       <c r="D73" s="9" t="s">
-        <v>2177</v>
+        <v>2199</v>
       </c>
       <c r="E73" s="22"/>
       <c r="F73" s="121" t="s">
-        <v>2178</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="74" ht="22.5" customHeight="1">
@@ -18734,14 +18800,14 @@
         <v>112</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>2032</v>
+        <v>2054</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>2179</v>
+        <v>2201</v>
       </c>
       <c r="E74" s="21"/>
       <c r="F74" s="120" t="s">
-        <v>2180</v>
+        <v>2202</v>
       </c>
     </row>
     <row r="75" ht="22.5" customHeight="1">
@@ -18752,14 +18818,14 @@
         <v>113</v>
       </c>
       <c r="C75" s="9" t="s">
-        <v>1970</v>
+        <v>1981</v>
       </c>
       <c r="D75" s="9" t="s">
-        <v>2181</v>
+        <v>2203</v>
       </c>
       <c r="E75" s="22"/>
       <c r="F75" s="121" t="s">
-        <v>2182</v>
+        <v>2204</v>
       </c>
     </row>
     <row r="76" ht="22.5" customHeight="1">
@@ -18770,14 +18836,14 @@
         <v>113</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>2032</v>
+        <v>2054</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>2183</v>
+        <v>2205</v>
       </c>
       <c r="E76" s="21"/>
       <c r="F76" s="120" t="s">
-        <v>2184</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="77" ht="22.5" customHeight="1">
@@ -18788,14 +18854,14 @@
         <v>114</v>
       </c>
       <c r="C77" s="9" t="s">
-        <v>2032</v>
+        <v>2054</v>
       </c>
       <c r="D77" s="9" t="s">
-        <v>2185</v>
+        <v>2207</v>
       </c>
       <c r="E77" s="22"/>
       <c r="F77" s="121" t="s">
-        <v>2186</v>
+        <v>2208</v>
       </c>
     </row>
     <row r="78" ht="22.5" customHeight="1">
@@ -18806,14 +18872,14 @@
         <v>114</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>2039</v>
+        <v>2061</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>2187</v>
+        <v>2209</v>
       </c>
       <c r="E78" s="21"/>
       <c r="F78" s="120" t="s">
-        <v>2188</v>
+        <v>2210</v>
       </c>
     </row>
     <row r="79" ht="22.5" customHeight="1">
@@ -18824,14 +18890,14 @@
         <v>115</v>
       </c>
       <c r="C79" s="9" t="s">
-        <v>2026</v>
+        <v>2048</v>
       </c>
       <c r="D79" s="9" t="s">
-        <v>2189</v>
+        <v>2211</v>
       </c>
       <c r="E79" s="22"/>
       <c r="F79" s="121" t="s">
-        <v>2190</v>
+        <v>2212</v>
       </c>
     </row>
     <row r="80" ht="22.5" customHeight="1">
@@ -18842,14 +18908,14 @@
         <v>115</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>2191</v>
+        <v>2213</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>2192</v>
+        <v>2214</v>
       </c>
       <c r="E80" s="21"/>
       <c r="F80" s="120" t="s">
-        <v>2193</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="81" ht="22.5" customHeight="1">
@@ -18860,14 +18926,14 @@
         <v>116</v>
       </c>
       <c r="C81" s="9" t="s">
-        <v>1970</v>
+        <v>1981</v>
       </c>
       <c r="D81" s="9" t="s">
-        <v>2194</v>
+        <v>2216</v>
       </c>
       <c r="E81" s="22"/>
       <c r="F81" s="121" t="s">
-        <v>2195</v>
+        <v>2217</v>
       </c>
     </row>
     <row r="82" ht="22.5" customHeight="1">
@@ -18878,14 +18944,14 @@
         <v>116</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>2032</v>
+        <v>2054</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>2196</v>
+        <v>2218</v>
       </c>
       <c r="E82" s="21"/>
       <c r="F82" s="120" t="s">
-        <v>2197</v>
+        <v>2219</v>
       </c>
     </row>
     <row r="83" ht="22.5" customHeight="1">
@@ -18896,14 +18962,14 @@
         <v>116</v>
       </c>
       <c r="C83" s="9" t="s">
-        <v>2039</v>
+        <v>2061</v>
       </c>
       <c r="D83" s="9" t="s">
-        <v>2198</v>
+        <v>2220</v>
       </c>
       <c r="E83" s="22"/>
       <c r="F83" s="121" t="s">
-        <v>2199</v>
+        <v>2221</v>
       </c>
     </row>
     <row r="84" ht="22.5" customHeight="1">
@@ -18914,14 +18980,14 @@
         <v>116</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>2103</v>
+        <v>2125</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>2200</v>
+        <v>2222</v>
       </c>
       <c r="E84" s="21"/>
       <c r="F84" s="120" t="s">
-        <v>2201</v>
+        <v>2223</v>
       </c>
     </row>
     <row r="85" ht="22.5" customHeight="1">
@@ -18932,14 +18998,14 @@
         <v>1580</v>
       </c>
       <c r="C85" s="9" t="s">
-        <v>2026</v>
+        <v>2048</v>
       </c>
       <c r="D85" s="9" t="s">
-        <v>2202</v>
+        <v>2224</v>
       </c>
       <c r="E85" s="22"/>
       <c r="F85" s="121" t="s">
-        <v>2075</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="86" ht="22.5" customHeight="1">
@@ -18950,14 +19016,14 @@
         <v>117</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>2026</v>
+        <v>2048</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>2203</v>
+        <v>2225</v>
       </c>
       <c r="E86" s="21"/>
       <c r="F86" s="120" t="s">
-        <v>2204</v>
+        <v>2226</v>
       </c>
     </row>
     <row r="87" ht="22.5" customHeight="1">
@@ -18968,14 +19034,14 @@
         <v>118</v>
       </c>
       <c r="C87" s="9" t="s">
-        <v>2032</v>
+        <v>2054</v>
       </c>
       <c r="D87" s="9" t="s">
-        <v>2205</v>
+        <v>2227</v>
       </c>
       <c r="E87" s="22"/>
       <c r="F87" s="121" t="s">
-        <v>2206</v>
+        <v>2228</v>
       </c>
     </row>
     <row r="88" ht="22.5" customHeight="1">
@@ -18986,14 +19052,14 @@
         <v>119</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>2026</v>
+        <v>2048</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>2207</v>
+        <v>2229</v>
       </c>
       <c r="E88" s="21"/>
       <c r="F88" s="120" t="s">
-        <v>2208</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="89" ht="22.5" customHeight="1">
@@ -19004,14 +19070,14 @@
         <v>120</v>
       </c>
       <c r="C89" s="9" t="s">
-        <v>2032</v>
+        <v>2054</v>
       </c>
       <c r="D89" s="9" t="s">
-        <v>2209</v>
+        <v>2231</v>
       </c>
       <c r="E89" s="22"/>
       <c r="F89" s="121" t="s">
-        <v>2210</v>
+        <v>2232</v>
       </c>
     </row>
     <row r="90" ht="22.5" customHeight="1">
@@ -19022,14 +19088,14 @@
         <v>121</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>2026</v>
+        <v>2048</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>2211</v>
+        <v>2233</v>
       </c>
       <c r="E90" s="21"/>
       <c r="F90" s="120" t="s">
-        <v>2208</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="91" ht="22.5" customHeight="1">
@@ -19040,14 +19106,14 @@
         <v>122</v>
       </c>
       <c r="C91" s="9" t="s">
-        <v>2032</v>
+        <v>2054</v>
       </c>
       <c r="D91" s="9" t="s">
-        <v>2212</v>
+        <v>2234</v>
       </c>
       <c r="E91" s="22"/>
       <c r="F91" s="121" t="s">
-        <v>2213</v>
+        <v>2235</v>
       </c>
     </row>
     <row r="92" ht="22.5" customHeight="1">
@@ -19061,11 +19127,11 @@
         <v>1676</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>2214</v>
+        <v>2236</v>
       </c>
       <c r="E92" s="21"/>
       <c r="F92" s="120" t="s">
-        <v>2215</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="93" ht="22.5" customHeight="1">
@@ -19076,14 +19142,14 @@
         <v>123</v>
       </c>
       <c r="C93" s="9" t="s">
-        <v>2216</v>
+        <v>2238</v>
       </c>
       <c r="D93" s="9" t="s">
-        <v>2217</v>
+        <v>2239</v>
       </c>
       <c r="E93" s="22"/>
       <c r="F93" s="121" t="s">
-        <v>2218</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="94" ht="22.5" customHeight="1">
@@ -19094,14 +19160,14 @@
         <v>123</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>2046</v>
+        <v>2068</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>2219</v>
+        <v>2241</v>
       </c>
       <c r="E94" s="21"/>
       <c r="F94" s="120" t="s">
-        <v>2220</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="95" ht="22.5" customHeight="1">
@@ -19112,14 +19178,14 @@
         <v>126</v>
       </c>
       <c r="C95" s="9" t="s">
-        <v>1971</v>
+        <v>1982</v>
       </c>
       <c r="D95" s="9" t="s">
-        <v>2221</v>
+        <v>2243</v>
       </c>
       <c r="E95" s="22"/>
       <c r="F95" s="121" t="s">
-        <v>2222</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="96" ht="22.5" customHeight="1">
@@ -19130,14 +19196,14 @@
         <v>129</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>1971</v>
+        <v>1982</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>2223</v>
+        <v>2245</v>
       </c>
       <c r="E96" s="21"/>
       <c r="F96" s="120" t="s">
-        <v>2224</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="97" ht="22.5" customHeight="1">
@@ -19148,14 +19214,14 @@
         <v>129</v>
       </c>
       <c r="C97" s="9" t="s">
-        <v>2216</v>
+        <v>2238</v>
       </c>
       <c r="D97" s="9" t="s">
-        <v>2225</v>
+        <v>2247</v>
       </c>
       <c r="E97" s="22"/>
       <c r="F97" s="121" t="s">
-        <v>2226</v>
+        <v>2248</v>
       </c>
     </row>
     <row r="98" ht="22.5" customHeight="1">
@@ -19166,14 +19232,14 @@
         <v>132</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>2216</v>
+        <v>2238</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>2227</v>
+        <v>2249</v>
       </c>
       <c r="E98" s="21"/>
       <c r="F98" s="120" t="s">
-        <v>2228</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="99" ht="22.5" customHeight="1">
@@ -19184,14 +19250,14 @@
         <v>134</v>
       </c>
       <c r="C99" s="9" t="s">
-        <v>1971</v>
+        <v>1982</v>
       </c>
       <c r="D99" s="9" t="s">
-        <v>2229</v>
+        <v>2251</v>
       </c>
       <c r="E99" s="22"/>
       <c r="F99" s="121" t="s">
-        <v>2230</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="100" ht="22.5" customHeight="1">
@@ -19202,14 +19268,14 @@
         <v>134</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>2216</v>
+        <v>2238</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>2231</v>
+        <v>2253</v>
       </c>
       <c r="E100" s="21"/>
       <c r="F100" s="120" t="s">
-        <v>2232</v>
+        <v>2254</v>
       </c>
     </row>
     <row r="101" ht="22.5" customHeight="1">
@@ -19220,14 +19286,14 @@
         <v>136</v>
       </c>
       <c r="C101" s="9" t="s">
-        <v>1971</v>
+        <v>1982</v>
       </c>
       <c r="D101" s="9" t="s">
-        <v>2233</v>
+        <v>2255</v>
       </c>
       <c r="E101" s="22"/>
       <c r="F101" s="121" t="s">
-        <v>2234</v>
+        <v>2256</v>
       </c>
     </row>
     <row r="102" ht="22.5" customHeight="1">
@@ -19241,11 +19307,11 @@
         <v>1676</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>2235</v>
+        <v>2257</v>
       </c>
       <c r="E102" s="21"/>
       <c r="F102" s="120" t="s">
-        <v>2236</v>
+        <v>2258</v>
       </c>
     </row>
     <row r="103" ht="22.5" customHeight="1">
@@ -19259,11 +19325,11 @@
         <v>1676</v>
       </c>
       <c r="D103" s="9" t="s">
-        <v>2237</v>
+        <v>2259</v>
       </c>
       <c r="E103" s="22"/>
       <c r="F103" s="121" t="s">
-        <v>2238</v>
+        <v>2260</v>
       </c>
     </row>
     <row r="104" ht="22.5" customHeight="1">
@@ -19274,14 +19340,14 @@
         <v>138</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>2216</v>
+        <v>2238</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>2239</v>
+        <v>2261</v>
       </c>
       <c r="E104" s="21"/>
       <c r="F104" s="120" t="s">
-        <v>2240</v>
+        <v>2262</v>
       </c>
     </row>
     <row r="105" ht="22.5" customHeight="1">
@@ -19295,11 +19361,11 @@
         <v>1676</v>
       </c>
       <c r="D105" s="9" t="s">
-        <v>2241</v>
+        <v>2263</v>
       </c>
       <c r="E105" s="22"/>
       <c r="F105" s="121" t="s">
-        <v>2242</v>
+        <v>2264</v>
       </c>
     </row>
     <row r="106" ht="22.5" customHeight="1">
@@ -19310,14 +19376,14 @@
         <v>140</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>2216</v>
+        <v>2238</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>2243</v>
+        <v>2265</v>
       </c>
       <c r="E106" s="21"/>
       <c r="F106" s="120" t="s">
-        <v>2244</v>
+        <v>2266</v>
       </c>
     </row>
     <row r="107" ht="22.5" customHeight="1">
@@ -19328,14 +19394,14 @@
         <v>142</v>
       </c>
       <c r="C107" s="9" t="s">
-        <v>1971</v>
+        <v>1982</v>
       </c>
       <c r="D107" s="9" t="s">
-        <v>2245</v>
+        <v>2267</v>
       </c>
       <c r="E107" s="22"/>
       <c r="F107" s="121" t="s">
-        <v>2246</v>
+        <v>2268</v>
       </c>
     </row>
     <row r="108" ht="22.5" customHeight="1">
@@ -19349,11 +19415,11 @@
         <v>1676</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>2247</v>
+        <v>2269</v>
       </c>
       <c r="E108" s="21"/>
       <c r="F108" s="120" t="s">
-        <v>2248</v>
+        <v>2270</v>
       </c>
     </row>
     <row r="109" ht="22.5" customHeight="1">
@@ -19364,14 +19430,14 @@
         <v>142</v>
       </c>
       <c r="C109" s="9" t="s">
-        <v>2216</v>
+        <v>2238</v>
       </c>
       <c r="D109" s="9" t="s">
-        <v>2249</v>
+        <v>2271</v>
       </c>
       <c r="E109" s="22"/>
       <c r="F109" s="121" t="s">
-        <v>2250</v>
+        <v>2272</v>
       </c>
     </row>
     <row r="110" ht="22.5" customHeight="1">
@@ -19382,14 +19448,14 @@
         <v>144</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>1971</v>
+        <v>1982</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>2251</v>
+        <v>2273</v>
       </c>
       <c r="E110" s="21"/>
       <c r="F110" s="120" t="s">
-        <v>2252</v>
+        <v>2274</v>
       </c>
     </row>
     <row r="111" ht="22.5" customHeight="1">
@@ -19400,14 +19466,14 @@
         <v>145</v>
       </c>
       <c r="C111" s="9" t="s">
-        <v>1971</v>
+        <v>1982</v>
       </c>
       <c r="D111" s="9" t="s">
-        <v>2253</v>
+        <v>2275</v>
       </c>
       <c r="E111" s="22"/>
       <c r="F111" s="121" t="s">
-        <v>2224</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="112" ht="22.5" customHeight="1">
@@ -19418,14 +19484,14 @@
         <v>145</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>2216</v>
+        <v>2238</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>2254</v>
+        <v>2276</v>
       </c>
       <c r="E112" s="21"/>
       <c r="F112" s="120" t="s">
-        <v>2255</v>
+        <v>2277</v>
       </c>
     </row>
     <row r="113" ht="22.5" customHeight="1">
@@ -19436,14 +19502,14 @@
         <v>148</v>
       </c>
       <c r="C113" s="9" t="s">
-        <v>1971</v>
+        <v>1982</v>
       </c>
       <c r="D113" s="9" t="s">
-        <v>2256</v>
+        <v>2278</v>
       </c>
       <c r="E113" s="22"/>
       <c r="F113" s="121" t="s">
-        <v>2257</v>
+        <v>2279</v>
       </c>
     </row>
     <row r="114" ht="22.5" customHeight="1">
@@ -19454,14 +19520,14 @@
         <v>148</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>2216</v>
+        <v>2238</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>2258</v>
+        <v>2280</v>
       </c>
       <c r="E114" s="21"/>
       <c r="F114" s="120" t="s">
-        <v>2259</v>
+        <v>2281</v>
       </c>
     </row>
     <row r="115" ht="22.5" customHeight="1">
@@ -19472,14 +19538,14 @@
         <v>148</v>
       </c>
       <c r="C115" s="9" t="s">
-        <v>2260</v>
+        <v>2282</v>
       </c>
       <c r="D115" s="9" t="s">
-        <v>2261</v>
+        <v>2283</v>
       </c>
       <c r="E115" s="22"/>
       <c r="F115" s="121" t="s">
-        <v>2262</v>
+        <v>2284</v>
       </c>
     </row>
     <row r="116" ht="22.5" customHeight="1">
@@ -19493,11 +19559,11 @@
         <v>1676</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>2263</v>
+        <v>2285</v>
       </c>
       <c r="E116" s="21"/>
       <c r="F116" s="120" t="s">
-        <v>2264</v>
+        <v>2286</v>
       </c>
     </row>
     <row r="117" ht="22.5" customHeight="1">
@@ -19508,14 +19574,14 @@
         <v>149</v>
       </c>
       <c r="C117" s="9" t="s">
-        <v>2216</v>
+        <v>2238</v>
       </c>
       <c r="D117" s="9" t="s">
-        <v>2265</v>
+        <v>2287</v>
       </c>
       <c r="E117" s="22"/>
       <c r="F117" s="121" t="s">
-        <v>2266</v>
+        <v>2288</v>
       </c>
     </row>
     <row r="118" ht="22.5" customHeight="1">
@@ -19526,14 +19592,14 @@
         <v>149</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>2267</v>
+        <v>2289</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>2268</v>
+        <v>2290</v>
       </c>
       <c r="E118" s="21"/>
       <c r="F118" s="120" t="s">
-        <v>2269</v>
+        <v>2291</v>
       </c>
     </row>
     <row r="119" ht="22.5" customHeight="1">
@@ -19547,11 +19613,11 @@
         <v>1676</v>
       </c>
       <c r="D119" s="9" t="s">
-        <v>2270</v>
+        <v>2292</v>
       </c>
       <c r="E119" s="22"/>
       <c r="F119" s="121" t="s">
-        <v>2271</v>
+        <v>2293</v>
       </c>
     </row>
     <row r="120" ht="22.5" customHeight="1">
@@ -19562,14 +19628,14 @@
         <v>150</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>2046</v>
+        <v>2068</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>2272</v>
+        <v>2294</v>
       </c>
       <c r="E120" s="21"/>
       <c r="F120" s="120" t="s">
-        <v>2273</v>
+        <v>2295</v>
       </c>
     </row>
     <row r="121" ht="22.5" customHeight="1">
@@ -19580,14 +19646,14 @@
         <v>150</v>
       </c>
       <c r="C121" s="9" t="s">
-        <v>2274</v>
+        <v>2296</v>
       </c>
       <c r="D121" s="9" t="s">
-        <v>2275</v>
+        <v>2297</v>
       </c>
       <c r="E121" s="22"/>
       <c r="F121" s="121" t="s">
-        <v>2276</v>
+        <v>2298</v>
       </c>
     </row>
     <row r="122" ht="22.5" customHeight="1">
@@ -19598,14 +19664,14 @@
         <v>152</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>1971</v>
+        <v>1982</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>2277</v>
+        <v>2299</v>
       </c>
       <c r="E122" s="21"/>
       <c r="F122" s="120" t="s">
-        <v>2278</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="123" ht="22.5" customHeight="1">
@@ -19616,14 +19682,14 @@
         <v>152</v>
       </c>
       <c r="C123" s="9" t="s">
-        <v>2046</v>
+        <v>2068</v>
       </c>
       <c r="D123" s="9" t="s">
-        <v>2279</v>
+        <v>2301</v>
       </c>
       <c r="E123" s="22"/>
       <c r="F123" s="121" t="s">
-        <v>2280</v>
+        <v>2302</v>
       </c>
     </row>
     <row r="124" ht="22.5" customHeight="1">
@@ -19634,14 +19700,14 @@
         <v>153</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>1971</v>
+        <v>1982</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>2281</v>
+        <v>2303</v>
       </c>
       <c r="E124" s="21"/>
       <c r="F124" s="120" t="s">
-        <v>2282</v>
+        <v>2304</v>
       </c>
     </row>
     <row r="125" ht="22.5" customHeight="1">
@@ -19652,14 +19718,14 @@
         <v>153</v>
       </c>
       <c r="C125" s="9" t="s">
-        <v>2216</v>
+        <v>2238</v>
       </c>
       <c r="D125" s="9" t="s">
-        <v>2283</v>
+        <v>2305</v>
       </c>
       <c r="E125" s="22"/>
       <c r="F125" s="121" t="s">
-        <v>2284</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="126" ht="22.5" customHeight="1">
@@ -19670,14 +19736,14 @@
         <v>154</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>1971</v>
+        <v>1982</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>2285</v>
+        <v>2307</v>
       </c>
       <c r="E126" s="21"/>
       <c r="F126" s="120" t="s">
-        <v>2286</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="127" ht="22.5" customHeight="1">
@@ -19691,11 +19757,11 @@
         <v>1676</v>
       </c>
       <c r="D127" s="9" t="s">
-        <v>2287</v>
+        <v>2309</v>
       </c>
       <c r="E127" s="22"/>
       <c r="F127" s="121" t="s">
-        <v>2288</v>
+        <v>2310</v>
       </c>
     </row>
     <row r="128" ht="22.5" customHeight="1">
@@ -19706,14 +19772,14 @@
         <v>154</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>2216</v>
+        <v>2238</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>2289</v>
+        <v>2311</v>
       </c>
       <c r="E128" s="21"/>
       <c r="F128" s="120" t="s">
-        <v>2290</v>
+        <v>2312</v>
       </c>
     </row>
     <row r="129" ht="22.5" customHeight="1">
@@ -19721,17 +19787,17 @@
         <v>17</v>
       </c>
       <c r="B129" s="9" t="s">
-        <v>2291</v>
+        <v>2313</v>
       </c>
       <c r="C129" s="9" t="s">
         <v>1676</v>
       </c>
       <c r="D129" s="9" t="s">
-        <v>2292</v>
+        <v>2314</v>
       </c>
       <c r="E129" s="22"/>
       <c r="F129" s="121" t="s">
-        <v>2224</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="130" ht="22.5" customHeight="1">
@@ -19742,14 +19808,14 @@
         <v>156</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>2216</v>
+        <v>2238</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>2293</v>
+        <v>2315</v>
       </c>
       <c r="E130" s="21"/>
       <c r="F130" s="120" t="s">
-        <v>2294</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="131" ht="22.5" customHeight="1">
@@ -19760,14 +19826,14 @@
         <v>158</v>
       </c>
       <c r="C131" s="9" t="s">
-        <v>1971</v>
+        <v>1982</v>
       </c>
       <c r="D131" s="9" t="s">
-        <v>2295</v>
+        <v>2317</v>
       </c>
       <c r="E131" s="22"/>
       <c r="F131" s="121" t="s">
-        <v>2296</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="132" ht="22.5" customHeight="1">
@@ -19781,11 +19847,11 @@
         <v>1676</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>2297</v>
+        <v>2319</v>
       </c>
       <c r="E132" s="21"/>
       <c r="F132" s="120" t="s">
-        <v>2298</v>
+        <v>2320</v>
       </c>
     </row>
     <row r="133" ht="22.5" customHeight="1">
@@ -19796,14 +19862,14 @@
         <v>159</v>
       </c>
       <c r="C133" s="9" t="s">
-        <v>1971</v>
+        <v>1982</v>
       </c>
       <c r="D133" s="9" t="s">
-        <v>2299</v>
+        <v>2321</v>
       </c>
       <c r="E133" s="22"/>
       <c r="F133" s="121" t="s">
-        <v>2300</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="134" ht="22.5" customHeight="1">
@@ -19817,11 +19883,11 @@
         <v>1676</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>2301</v>
+        <v>2323</v>
       </c>
       <c r="E134" s="21"/>
       <c r="F134" s="120" t="s">
-        <v>2302</v>
+        <v>2324</v>
       </c>
     </row>
     <row r="135" ht="22.5" customHeight="1">
@@ -19835,11 +19901,11 @@
         <v>1676</v>
       </c>
       <c r="D135" s="9" t="s">
-        <v>2303</v>
+        <v>2325</v>
       </c>
       <c r="E135" s="22"/>
       <c r="F135" s="121" t="s">
-        <v>2304</v>
+        <v>2326</v>
       </c>
     </row>
     <row r="136" ht="22.5" customHeight="1">
@@ -19850,14 +19916,14 @@
         <v>161</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>1971</v>
+        <v>1982</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>2305</v>
+        <v>2327</v>
       </c>
       <c r="E136" s="21"/>
       <c r="F136" s="120" t="s">
-        <v>2306</v>
+        <v>2328</v>
       </c>
     </row>
     <row r="137" ht="22.5" customHeight="1">
@@ -19868,14 +19934,14 @@
         <v>161</v>
       </c>
       <c r="C137" s="9" t="s">
-        <v>2216</v>
+        <v>2238</v>
       </c>
       <c r="D137" s="9" t="s">
-        <v>2307</v>
+        <v>2329</v>
       </c>
       <c r="E137" s="22"/>
       <c r="F137" s="121" t="s">
-        <v>2308</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="138" ht="22.5" customHeight="1">
@@ -19886,14 +19952,14 @@
         <v>162</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>2309</v>
+        <v>2331</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>2310</v>
+        <v>2332</v>
       </c>
       <c r="E138" s="21"/>
       <c r="F138" s="120" t="s">
-        <v>2311</v>
+        <v>2333</v>
       </c>
     </row>
     <row r="139" ht="22.5" customHeight="1">
@@ -19904,14 +19970,14 @@
         <v>163</v>
       </c>
       <c r="C139" s="9" t="s">
-        <v>2216</v>
+        <v>2238</v>
       </c>
       <c r="D139" s="9" t="s">
-        <v>2312</v>
+        <v>2334</v>
       </c>
       <c r="E139" s="22"/>
       <c r="F139" s="121" t="s">
-        <v>2313</v>
+        <v>2335</v>
       </c>
     </row>
     <row r="140" ht="22.5" customHeight="1">
@@ -19922,14 +19988,14 @@
         <v>164</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>1971</v>
+        <v>1982</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>2314</v>
+        <v>2336</v>
       </c>
       <c r="E140" s="21"/>
       <c r="F140" s="120" t="s">
-        <v>2315</v>
+        <v>2337</v>
       </c>
     </row>
     <row r="141" ht="22.5" customHeight="1">
@@ -19943,11 +20009,11 @@
         <v>1676</v>
       </c>
       <c r="D141" s="9" t="s">
-        <v>2316</v>
+        <v>2338</v>
       </c>
       <c r="E141" s="22"/>
       <c r="F141" s="121" t="s">
-        <v>2317</v>
+        <v>2339</v>
       </c>
     </row>
     <row r="142" ht="22.5" customHeight="1">
@@ -19958,14 +20024,14 @@
         <v>165</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>1971</v>
+        <v>1982</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>2318</v>
+        <v>2340</v>
       </c>
       <c r="E142" s="21"/>
       <c r="F142" s="120" t="s">
-        <v>2319</v>
+        <v>2341</v>
       </c>
     </row>
     <row r="143" ht="22.5" customHeight="1">
@@ -19976,14 +20042,14 @@
         <v>165</v>
       </c>
       <c r="C143" s="9" t="s">
-        <v>2216</v>
+        <v>2238</v>
       </c>
       <c r="D143" s="9" t="s">
-        <v>2320</v>
+        <v>2342</v>
       </c>
       <c r="E143" s="22"/>
       <c r="F143" s="121" t="s">
-        <v>2321</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="144" ht="22.5" customHeight="1">
@@ -19991,17 +20057,17 @@
         <v>17</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>2322</v>
+        <v>2344</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>1971</v>
+        <v>1982</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>2323</v>
+        <v>2345</v>
       </c>
       <c r="E144" s="21"/>
       <c r="F144" s="120" t="s">
-        <v>2324</v>
+        <v>2346</v>
       </c>
     </row>
     <row r="145" ht="22.5" customHeight="1">
@@ -20015,11 +20081,11 @@
         <v>1676</v>
       </c>
       <c r="D145" s="9" t="s">
-        <v>2325</v>
+        <v>2347</v>
       </c>
       <c r="E145" s="22"/>
       <c r="F145" s="121" t="s">
-        <v>2326</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="146" ht="22.5" customHeight="1">
@@ -20030,14 +20096,14 @@
         <v>168</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>2260</v>
+        <v>2282</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>2327</v>
+        <v>2349</v>
       </c>
       <c r="E146" s="21"/>
       <c r="F146" s="120" t="s">
-        <v>2328</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="147" ht="22.5" customHeight="1">
@@ -20048,14 +20114,14 @@
         <v>169</v>
       </c>
       <c r="C147" s="9" t="s">
-        <v>2216</v>
+        <v>2238</v>
       </c>
       <c r="D147" s="9" t="s">
-        <v>2329</v>
+        <v>2351</v>
       </c>
       <c r="E147" s="22"/>
       <c r="F147" s="121" t="s">
-        <v>2330</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="148" ht="22.5" customHeight="1">
@@ -20066,14 +20132,14 @@
         <v>169</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>2267</v>
+        <v>2289</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>2331</v>
+        <v>2353</v>
       </c>
       <c r="E148" s="21"/>
       <c r="F148" s="120" t="s">
-        <v>2332</v>
+        <v>2354</v>
       </c>
     </row>
     <row r="149" ht="22.5" customHeight="1">
@@ -20087,11 +20153,11 @@
         <v>1676</v>
       </c>
       <c r="D149" s="9" t="s">
-        <v>2333</v>
+        <v>2355</v>
       </c>
       <c r="E149" s="22"/>
       <c r="F149" s="121" t="s">
-        <v>2334</v>
+        <v>2356</v>
       </c>
     </row>
     <row r="150" ht="22.5" customHeight="1">
@@ -20102,14 +20168,14 @@
         <v>170</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>2335</v>
+        <v>2357</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>2336</v>
+        <v>2358</v>
       </c>
       <c r="E150" s="21"/>
       <c r="F150" s="120" t="s">
-        <v>2337</v>
+        <v>2359</v>
       </c>
     </row>
     <row r="151" ht="22.5" customHeight="1">
@@ -20123,11 +20189,11 @@
         <v>1676</v>
       </c>
       <c r="D151" s="9" t="s">
-        <v>2338</v>
+        <v>2360</v>
       </c>
       <c r="E151" s="22"/>
       <c r="F151" s="121" t="s">
-        <v>2339</v>
+        <v>2361</v>
       </c>
     </row>
     <row r="152" ht="22.5" customHeight="1">
@@ -20138,14 +20204,14 @@
         <v>171</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>2216</v>
+        <v>2238</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>2340</v>
+        <v>2362</v>
       </c>
       <c r="E152" s="21"/>
       <c r="F152" s="120" t="s">
-        <v>2341</v>
+        <v>2363</v>
       </c>
     </row>
     <row r="153" ht="22.5" customHeight="1">
@@ -20159,11 +20225,11 @@
         <v>1676</v>
       </c>
       <c r="D153" s="9" t="s">
-        <v>2342</v>
+        <v>2364</v>
       </c>
       <c r="E153" s="22"/>
       <c r="F153" s="121" t="s">
-        <v>2343</v>
+        <v>2365</v>
       </c>
     </row>
     <row r="154" ht="22.5" customHeight="1">
@@ -20174,14 +20240,14 @@
         <v>172</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>2046</v>
+        <v>2068</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>2344</v>
+        <v>2366</v>
       </c>
       <c r="E154" s="21"/>
       <c r="F154" s="120" t="s">
-        <v>2345</v>
+        <v>2367</v>
       </c>
     </row>
     <row r="155" ht="22.5" customHeight="1">
@@ -20192,14 +20258,14 @@
         <v>173</v>
       </c>
       <c r="C155" s="9" t="s">
-        <v>1971</v>
+        <v>1982</v>
       </c>
       <c r="D155" s="9" t="s">
-        <v>2346</v>
+        <v>2368</v>
       </c>
       <c r="E155" s="22"/>
       <c r="F155" s="121" t="s">
-        <v>2347</v>
+        <v>2369</v>
       </c>
     </row>
     <row r="156" ht="22.5" customHeight="1">
@@ -20213,11 +20279,11 @@
         <v>1676</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>2348</v>
+        <v>2370</v>
       </c>
       <c r="E156" s="21"/>
       <c r="F156" s="120" t="s">
-        <v>2349</v>
+        <v>2371</v>
       </c>
     </row>
     <row r="157" ht="22.5" customHeight="1">
@@ -20228,14 +20294,14 @@
         <v>174</v>
       </c>
       <c r="C157" s="9" t="s">
-        <v>1971</v>
+        <v>1982</v>
       </c>
       <c r="D157" s="9" t="s">
-        <v>2350</v>
+        <v>2372</v>
       </c>
       <c r="E157" s="22"/>
       <c r="F157" s="121" t="s">
-        <v>2351</v>
+        <v>2373</v>
       </c>
     </row>
     <row r="158" ht="22.5" customHeight="1">
@@ -20249,11 +20315,11 @@
         <v>1676</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>2352</v>
+        <v>2374</v>
       </c>
       <c r="E158" s="21"/>
       <c r="F158" s="120" t="s">
-        <v>2353</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="159" ht="22.5" customHeight="1">
@@ -20264,14 +20330,14 @@
         <v>176</v>
       </c>
       <c r="C159" s="9" t="s">
-        <v>2216</v>
+        <v>2238</v>
       </c>
       <c r="D159" s="9" t="s">
-        <v>2354</v>
+        <v>2376</v>
       </c>
       <c r="E159" s="22"/>
       <c r="F159" s="121" t="s">
-        <v>2355</v>
+        <v>2377</v>
       </c>
     </row>
     <row r="160" ht="22.5" customHeight="1">
@@ -20282,14 +20348,14 @@
         <v>177</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>1971</v>
+        <v>1982</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>2356</v>
+        <v>2378</v>
       </c>
       <c r="E160" s="21"/>
       <c r="F160" s="120" t="s">
-        <v>2357</v>
+        <v>2379</v>
       </c>
     </row>
     <row r="161" ht="22.5" customHeight="1">
@@ -20303,11 +20369,11 @@
         <v>1676</v>
       </c>
       <c r="D161" s="9" t="s">
-        <v>2358</v>
+        <v>2380</v>
       </c>
       <c r="E161" s="22"/>
       <c r="F161" s="121" t="s">
-        <v>2334</v>
+        <v>2356</v>
       </c>
     </row>
     <row r="162" ht="22.5" customHeight="1">
@@ -20318,14 +20384,14 @@
         <v>179</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>1971</v>
+        <v>1982</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>2359</v>
+        <v>2381</v>
       </c>
       <c r="E162" s="21"/>
       <c r="F162" s="120" t="s">
-        <v>2360</v>
+        <v>2382</v>
       </c>
     </row>
     <row r="163" ht="22.5" customHeight="1">
@@ -20336,14 +20402,14 @@
         <v>179</v>
       </c>
       <c r="C163" s="9" t="s">
-        <v>2216</v>
+        <v>2238</v>
       </c>
       <c r="D163" s="9" t="s">
-        <v>2361</v>
+        <v>2383</v>
       </c>
       <c r="E163" s="22"/>
       <c r="F163" s="121" t="s">
-        <v>2362</v>
+        <v>2384</v>
       </c>
     </row>
     <row r="164" ht="22.5" customHeight="1">
@@ -20354,14 +20420,14 @@
         <v>180</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>1971</v>
+        <v>1982</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>2363</v>
+        <v>2385</v>
       </c>
       <c r="E164" s="21"/>
       <c r="F164" s="120" t="s">
-        <v>2364</v>
+        <v>2386</v>
       </c>
     </row>
     <row r="165" ht="22.5" customHeight="1">
@@ -20372,10 +20438,10 @@
         <v>180</v>
       </c>
       <c r="C165" s="9" t="s">
-        <v>2365</v>
+        <v>2387</v>
       </c>
       <c r="D165" s="9" t="s">
-        <v>2366</v>
+        <v>2388</v>
       </c>
       <c r="E165" s="22"/>
       <c r="F165" s="121" t="s">
@@ -20390,14 +20456,14 @@
         <v>181</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>1971</v>
+        <v>1982</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>2367</v>
+        <v>2389</v>
       </c>
       <c r="E166" s="21"/>
       <c r="F166" s="120" t="s">
-        <v>2368</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="167" ht="22.5" customHeight="1">
@@ -20411,11 +20477,11 @@
         <v>1676</v>
       </c>
       <c r="D167" s="9" t="s">
-        <v>2369</v>
+        <v>2391</v>
       </c>
       <c r="E167" s="22"/>
       <c r="F167" s="121" t="s">
-        <v>2370</v>
+        <v>2392</v>
       </c>
     </row>
     <row r="168" ht="22.5" customHeight="1">
@@ -20426,14 +20492,14 @@
         <v>182</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>1971</v>
+        <v>1982</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>2371</v>
+        <v>2393</v>
       </c>
       <c r="E168" s="21"/>
       <c r="F168" s="120" t="s">
-        <v>2372</v>
+        <v>2394</v>
       </c>
     </row>
     <row r="169" ht="22.5" customHeight="1">
@@ -20444,14 +20510,14 @@
         <v>182</v>
       </c>
       <c r="C169" s="9" t="s">
-        <v>2216</v>
+        <v>2238</v>
       </c>
       <c r="D169" s="9" t="s">
-        <v>2373</v>
+        <v>2395</v>
       </c>
       <c r="E169" s="22"/>
       <c r="F169" s="121" t="s">
-        <v>2374</v>
+        <v>2396</v>
       </c>
     </row>
     <row r="170" ht="22.5" customHeight="1">
@@ -20465,11 +20531,11 @@
         <v>1676</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>2375</v>
+        <v>2397</v>
       </c>
       <c r="E170" s="21"/>
       <c r="F170" s="120" t="s">
-        <v>2376</v>
+        <v>2398</v>
       </c>
     </row>
     <row r="171" ht="22.5" customHeight="1">
@@ -20480,14 +20546,14 @@
         <v>184</v>
       </c>
       <c r="C171" s="9" t="s">
-        <v>1971</v>
+        <v>1982</v>
       </c>
       <c r="D171" s="9" t="s">
-        <v>2377</v>
+        <v>2399</v>
       </c>
       <c r="E171" s="22"/>
       <c r="F171" s="121" t="s">
-        <v>2378</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="172" ht="22.5" customHeight="1">
@@ -20501,11 +20567,11 @@
         <v>1676</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>2379</v>
+        <v>2401</v>
       </c>
       <c r="E172" s="21"/>
       <c r="F172" s="120" t="s">
-        <v>2380</v>
+        <v>2402</v>
       </c>
     </row>
     <row r="173" ht="22.5" customHeight="1">
@@ -20519,11 +20585,11 @@
         <v>1676</v>
       </c>
       <c r="D173" s="9" t="s">
-        <v>2381</v>
+        <v>2403</v>
       </c>
       <c r="E173" s="22"/>
       <c r="F173" s="121" t="s">
-        <v>2382</v>
+        <v>2404</v>
       </c>
     </row>
     <row r="174" ht="22.5" customHeight="1">
@@ -20534,14 +20600,14 @@
         <v>185</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>2216</v>
+        <v>2238</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>2383</v>
+        <v>2405</v>
       </c>
       <c r="E174" s="21"/>
       <c r="F174" s="120" t="s">
-        <v>2384</v>
+        <v>2406</v>
       </c>
     </row>
     <row r="175" ht="22.5" customHeight="1">
@@ -20552,14 +20618,14 @@
         <v>186</v>
       </c>
       <c r="C175" s="9" t="s">
-        <v>1971</v>
+        <v>1982</v>
       </c>
       <c r="D175" s="9" t="s">
-        <v>2385</v>
+        <v>2407</v>
       </c>
       <c r="E175" s="22"/>
       <c r="F175" s="121" t="s">
-        <v>2386</v>
+        <v>2408</v>
       </c>
     </row>
     <row r="176" ht="22.5" customHeight="1">
@@ -20570,14 +20636,14 @@
         <v>186</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>2274</v>
+        <v>2296</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>2387</v>
+        <v>2409</v>
       </c>
       <c r="E176" s="21"/>
       <c r="F176" s="120" t="s">
-        <v>2388</v>
+        <v>2410</v>
       </c>
     </row>
     <row r="177" ht="22.5" customHeight="1">
@@ -20591,11 +20657,11 @@
         <v>1676</v>
       </c>
       <c r="D177" s="9" t="s">
-        <v>2389</v>
+        <v>2411</v>
       </c>
       <c r="E177" s="22"/>
       <c r="F177" s="121" t="s">
-        <v>2242</v>
+        <v>2264</v>
       </c>
     </row>
     <row r="178" ht="22.5" customHeight="1">
@@ -20606,14 +20672,14 @@
         <v>188</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>2216</v>
+        <v>2238</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>2390</v>
+        <v>2412</v>
       </c>
       <c r="E178" s="21"/>
       <c r="F178" s="120" t="s">
-        <v>2244</v>
+        <v>2266</v>
       </c>
     </row>
     <row r="179" ht="22.5" customHeight="1">
@@ -20624,10 +20690,10 @@
         <v>193</v>
       </c>
       <c r="C179" s="9" t="s">
-        <v>2391</v>
+        <v>2413</v>
       </c>
       <c r="D179" s="9" t="s">
-        <v>2392</v>
+        <v>2414</v>
       </c>
       <c r="E179" s="22"/>
       <c r="F179" s="131"/>
@@ -20640,14 +20706,14 @@
         <v>196</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>2391</v>
+        <v>2413</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>2393</v>
+        <v>2415</v>
       </c>
       <c r="E180" s="21"/>
       <c r="F180" s="120" t="s">
-        <v>2394</v>
+        <v>2416</v>
       </c>
     </row>
     <row r="181" ht="22.5" customHeight="1">
@@ -20658,14 +20724,14 @@
         <v>198</v>
       </c>
       <c r="C181" s="9" t="s">
-        <v>2391</v>
+        <v>2413</v>
       </c>
       <c r="D181" s="9" t="s">
-        <v>2395</v>
+        <v>2417</v>
       </c>
       <c r="E181" s="22"/>
       <c r="F181" s="121" t="s">
-        <v>2396</v>
+        <v>2418</v>
       </c>
     </row>
     <row r="182" ht="22.5" customHeight="1">
@@ -20676,14 +20742,14 @@
         <v>199</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>2391</v>
+        <v>2413</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>2397</v>
+        <v>2419</v>
       </c>
       <c r="E182" s="21"/>
       <c r="F182" s="120" t="s">
-        <v>2398</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="183" ht="22.5" customHeight="1">
@@ -20697,11 +20763,11 @@
         <v>1671</v>
       </c>
       <c r="D183" s="9" t="s">
-        <v>2399</v>
+        <v>2421</v>
       </c>
       <c r="E183" s="22"/>
       <c r="F183" s="121" t="s">
-        <v>2400</v>
+        <v>2422</v>
       </c>
     </row>
     <row r="184" ht="22.5" customHeight="1">
@@ -20712,14 +20778,14 @@
         <v>202</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>2391</v>
+        <v>2413</v>
       </c>
       <c r="D184" s="3" t="s">
-        <v>2401</v>
+        <v>2423</v>
       </c>
       <c r="E184" s="21"/>
       <c r="F184" s="120" t="s">
-        <v>2402</v>
+        <v>2424</v>
       </c>
     </row>
     <row r="185" ht="22.5" customHeight="1">
@@ -20730,14 +20796,14 @@
         <v>203</v>
       </c>
       <c r="C185" s="9" t="s">
-        <v>2391</v>
+        <v>2413</v>
       </c>
       <c r="D185" s="9" t="s">
-        <v>2403</v>
+        <v>2425</v>
       </c>
       <c r="E185" s="22"/>
       <c r="F185" s="121" t="s">
-        <v>2404</v>
+        <v>2426</v>
       </c>
     </row>
     <row r="186" ht="22.5" customHeight="1">
@@ -20748,14 +20814,14 @@
         <v>204</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>2405</v>
+        <v>2427</v>
       </c>
       <c r="D186" s="3" t="s">
-        <v>2406</v>
+        <v>2428</v>
       </c>
       <c r="E186" s="21"/>
       <c r="F186" s="120" t="s">
-        <v>2407</v>
+        <v>2429</v>
       </c>
     </row>
     <row r="187" ht="22.5" customHeight="1">
@@ -20766,14 +20832,14 @@
         <v>205</v>
       </c>
       <c r="C187" s="9" t="s">
-        <v>2391</v>
+        <v>2413</v>
       </c>
       <c r="D187" s="9" t="s">
-        <v>2408</v>
+        <v>2430</v>
       </c>
       <c r="E187" s="22"/>
       <c r="F187" s="121" t="s">
-        <v>2409</v>
+        <v>2431</v>
       </c>
     </row>
     <row r="188" ht="22.5" customHeight="1">
@@ -20784,14 +20850,14 @@
         <v>205</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>2410</v>
+        <v>2432</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>2411</v>
+        <v>2433</v>
       </c>
       <c r="E188" s="21"/>
       <c r="F188" s="120" t="s">
-        <v>2412</v>
+        <v>2434</v>
       </c>
     </row>
     <row r="189" ht="22.5" customHeight="1">
@@ -20802,14 +20868,14 @@
         <v>208</v>
       </c>
       <c r="C189" s="9" t="s">
-        <v>2410</v>
+        <v>2432</v>
       </c>
       <c r="D189" s="9" t="s">
-        <v>2413</v>
+        <v>2435</v>
       </c>
       <c r="E189" s="22"/>
       <c r="F189" s="59" t="s">
-        <v>2414</v>
+        <v>2436</v>
       </c>
     </row>
     <row r="190" ht="22.5" customHeight="1">
@@ -20820,14 +20886,14 @@
         <v>209</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>2391</v>
+        <v>2413</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>2415</v>
+        <v>2437</v>
       </c>
       <c r="E190" s="21"/>
       <c r="F190" s="120" t="s">
-        <v>2416</v>
+        <v>2438</v>
       </c>
     </row>
     <row r="191" ht="22.5" customHeight="1">
@@ -20838,14 +20904,14 @@
         <v>210</v>
       </c>
       <c r="C191" s="9" t="s">
-        <v>2391</v>
+        <v>2413</v>
       </c>
       <c r="D191" s="9" t="s">
-        <v>2417</v>
+        <v>2439</v>
       </c>
       <c r="E191" s="22"/>
       <c r="F191" s="121" t="s">
-        <v>2418</v>
+        <v>2440</v>
       </c>
     </row>
     <row r="192" ht="22.5" customHeight="1">
@@ -20859,11 +20925,11 @@
         <v>1671</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>2419</v>
+        <v>2441</v>
       </c>
       <c r="E192" s="21"/>
       <c r="F192" s="120" t="s">
-        <v>2420</v>
+        <v>2442</v>
       </c>
     </row>
     <row r="193" ht="22.5" customHeight="1">
@@ -20874,14 +20940,14 @@
         <v>210</v>
       </c>
       <c r="C193" s="9" t="s">
-        <v>2410</v>
+        <v>2432</v>
       </c>
       <c r="D193" s="9" t="s">
-        <v>2421</v>
+        <v>2443</v>
       </c>
       <c r="E193" s="22"/>
       <c r="F193" s="121" t="s">
-        <v>2422</v>
+        <v>2444</v>
       </c>
     </row>
     <row r="194" ht="22.5" customHeight="1">
@@ -20892,14 +20958,14 @@
         <v>210</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>2423</v>
+        <v>2445</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>2424</v>
+        <v>2446</v>
       </c>
       <c r="E194" s="21"/>
       <c r="F194" s="120" t="s">
-        <v>2425</v>
+        <v>2447</v>
       </c>
     </row>
     <row r="195" ht="22.5" customHeight="1">
@@ -20910,14 +20976,14 @@
         <v>103</v>
       </c>
       <c r="C195" s="9" t="s">
-        <v>2391</v>
+        <v>2413</v>
       </c>
       <c r="D195" s="9" t="s">
-        <v>2426</v>
+        <v>2448</v>
       </c>
       <c r="E195" s="22"/>
       <c r="F195" s="121" t="s">
-        <v>2427</v>
+        <v>2449</v>
       </c>
     </row>
     <row r="196" ht="22.5" customHeight="1">
@@ -20928,14 +20994,14 @@
         <v>212</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>2391</v>
+        <v>2413</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>2428</v>
+        <v>2450</v>
       </c>
       <c r="E196" s="21"/>
       <c r="F196" s="120" t="s">
-        <v>2429</v>
+        <v>2451</v>
       </c>
     </row>
     <row r="197" ht="22.5" customHeight="1">
@@ -20946,14 +21012,14 @@
         <v>213</v>
       </c>
       <c r="C197" s="9" t="s">
-        <v>2391</v>
+        <v>2413</v>
       </c>
       <c r="D197" s="9" t="s">
-        <v>2430</v>
+        <v>2452</v>
       </c>
       <c r="E197" s="22"/>
       <c r="F197" s="121" t="s">
-        <v>2431</v>
+        <v>2453</v>
       </c>
     </row>
     <row r="198" ht="22.5" customHeight="1">
@@ -20964,14 +21030,14 @@
         <v>215</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>2432</v>
+        <v>2454</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>2433</v>
+        <v>2455</v>
       </c>
       <c r="E198" s="21"/>
       <c r="F198" s="120" t="s">
-        <v>2434</v>
+        <v>2456</v>
       </c>
     </row>
     <row r="199" ht="22.5" customHeight="1">
@@ -20982,14 +21048,14 @@
         <v>219</v>
       </c>
       <c r="C199" s="9" t="s">
-        <v>2391</v>
+        <v>2413</v>
       </c>
       <c r="D199" s="9" t="s">
-        <v>2435</v>
+        <v>2457</v>
       </c>
       <c r="E199" s="22"/>
       <c r="F199" s="121" t="s">
-        <v>2436</v>
+        <v>2458</v>
       </c>
     </row>
     <row r="200" ht="22.5" customHeight="1">
@@ -21000,14 +21066,14 @@
         <v>220</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>2432</v>
+        <v>2454</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>2437</v>
+        <v>2459</v>
       </c>
       <c r="E200" s="21"/>
       <c r="F200" s="120" t="s">
-        <v>2438</v>
+        <v>2460</v>
       </c>
     </row>
     <row r="201" ht="22.5" customHeight="1">
@@ -21018,14 +21084,14 @@
         <v>220</v>
       </c>
       <c r="C201" s="9" t="s">
-        <v>2410</v>
+        <v>2432</v>
       </c>
       <c r="D201" s="9" t="s">
-        <v>2439</v>
+        <v>2461</v>
       </c>
       <c r="E201" s="22"/>
       <c r="F201" s="121" t="s">
-        <v>2440</v>
+        <v>2462</v>
       </c>
     </row>
     <row r="202" ht="22.5" customHeight="1">
@@ -21039,11 +21105,11 @@
         <v>1676</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>2441</v>
+        <v>2463</v>
       </c>
       <c r="E202" s="21"/>
       <c r="F202" s="120" t="s">
-        <v>2440</v>
+        <v>2462</v>
       </c>
     </row>
     <row r="203" ht="22.5" customHeight="1">
@@ -21057,11 +21123,11 @@
         <v>1671</v>
       </c>
       <c r="D203" s="9" t="s">
-        <v>2442</v>
+        <v>2464</v>
       </c>
       <c r="E203" s="22"/>
       <c r="F203" s="121" t="s">
-        <v>2443</v>
+        <v>2465</v>
       </c>
     </row>
     <row r="204" ht="22.5" customHeight="1">
@@ -21072,14 +21138,14 @@
         <v>222</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>2391</v>
+        <v>2413</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>2444</v>
+        <v>2466</v>
       </c>
       <c r="E204" s="21"/>
       <c r="F204" s="120" t="s">
-        <v>2445</v>
+        <v>2467</v>
       </c>
     </row>
     <row r="205" ht="22.5" customHeight="1">
@@ -21090,14 +21156,14 @@
         <v>222</v>
       </c>
       <c r="C205" s="9" t="s">
-        <v>2405</v>
+        <v>2427</v>
       </c>
       <c r="D205" s="9" t="s">
-        <v>2446</v>
+        <v>2468</v>
       </c>
       <c r="E205" s="22"/>
       <c r="F205" s="121" t="s">
-        <v>2447</v>
+        <v>2469</v>
       </c>
     </row>
     <row r="206" ht="22.5" customHeight="1">
@@ -21108,14 +21174,14 @@
         <v>222</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>2448</v>
+        <v>2470</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>2449</v>
+        <v>2471</v>
       </c>
       <c r="E206" s="21"/>
       <c r="F206" s="120" t="s">
-        <v>2450</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="207" ht="22.5" customHeight="1">
@@ -21129,11 +21195,11 @@
         <v>1671</v>
       </c>
       <c r="D207" s="9" t="s">
-        <v>2451</v>
+        <v>2473</v>
       </c>
       <c r="E207" s="22"/>
       <c r="F207" s="121" t="s">
-        <v>2452</v>
+        <v>2474</v>
       </c>
     </row>
     <row r="208" ht="22.5" customHeight="1">
@@ -21147,11 +21213,11 @@
         <v>1671</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>2453</v>
+        <v>2475</v>
       </c>
       <c r="E208" s="21"/>
       <c r="F208" s="120" t="s">
-        <v>2454</v>
+        <v>2476</v>
       </c>
     </row>
     <row r="209" ht="22.5" customHeight="1">
@@ -21162,14 +21228,14 @@
         <v>228</v>
       </c>
       <c r="C209" s="9" t="s">
-        <v>2391</v>
+        <v>2413</v>
       </c>
       <c r="D209" s="9" t="s">
-        <v>2455</v>
+        <v>2477</v>
       </c>
       <c r="E209" s="22"/>
       <c r="F209" s="121" t="s">
-        <v>2456</v>
+        <v>2478</v>
       </c>
     </row>
     <row r="210" ht="22.5" customHeight="1">
@@ -21180,14 +21246,14 @@
         <v>228</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>2405</v>
+        <v>2427</v>
       </c>
       <c r="D210" s="3" t="s">
-        <v>2457</v>
+        <v>2479</v>
       </c>
       <c r="E210" s="21"/>
       <c r="F210" s="120" t="s">
-        <v>2458</v>
+        <v>2480</v>
       </c>
     </row>
     <row r="211" ht="22.5" customHeight="1">
@@ -21198,14 +21264,14 @@
         <v>229</v>
       </c>
       <c r="C211" s="9" t="s">
-        <v>2410</v>
+        <v>2432</v>
       </c>
       <c r="D211" s="9" t="s">
-        <v>2459</v>
+        <v>2481</v>
       </c>
       <c r="E211" s="22"/>
       <c r="F211" s="121" t="s">
-        <v>2460</v>
+        <v>2482</v>
       </c>
     </row>
     <row r="212" ht="22.5" customHeight="1">
@@ -21216,10 +21282,10 @@
         <v>230</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>2461</v>
+        <v>2483</v>
       </c>
       <c r="D212" s="3" t="s">
-        <v>2461</v>
+        <v>2483</v>
       </c>
       <c r="E212" s="21"/>
       <c r="F212" s="132"/>
@@ -21232,14 +21298,14 @@
         <v>232</v>
       </c>
       <c r="C213" s="9" t="s">
-        <v>2391</v>
+        <v>2413</v>
       </c>
       <c r="D213" s="9" t="s">
-        <v>2462</v>
+        <v>2484</v>
       </c>
       <c r="E213" s="22"/>
       <c r="F213" s="121" t="s">
-        <v>2463</v>
+        <v>2485</v>
       </c>
     </row>
     <row r="214" ht="22.5" customHeight="1">
@@ -21250,14 +21316,14 @@
         <v>232</v>
       </c>
       <c r="C214" s="3" t="s">
-        <v>2410</v>
+        <v>2432</v>
       </c>
       <c r="D214" s="3" t="s">
-        <v>2464</v>
+        <v>2486</v>
       </c>
       <c r="E214" s="21"/>
       <c r="F214" s="120" t="s">
-        <v>2465</v>
+        <v>2487</v>
       </c>
     </row>
     <row r="215" ht="22.5" customHeight="1">
@@ -21268,14 +21334,14 @@
         <v>232</v>
       </c>
       <c r="C215" s="9" t="s">
-        <v>2410</v>
+        <v>2432</v>
       </c>
       <c r="D215" s="9" t="s">
-        <v>2466</v>
+        <v>2488</v>
       </c>
       <c r="E215" s="22"/>
       <c r="F215" s="121" t="s">
-        <v>2467</v>
+        <v>2489</v>
       </c>
     </row>
     <row r="216" ht="22.5" customHeight="1">
@@ -21286,14 +21352,14 @@
         <v>232</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>2468</v>
+        <v>2490</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>2469</v>
+        <v>2491</v>
       </c>
       <c r="E216" s="21"/>
       <c r="F216" s="120" t="s">
-        <v>2470</v>
+        <v>2492</v>
       </c>
     </row>
     <row r="217" ht="22.5" customHeight="1">
@@ -21304,14 +21370,14 @@
         <v>234</v>
       </c>
       <c r="C217" s="9" t="s">
-        <v>2391</v>
+        <v>2413</v>
       </c>
       <c r="D217" s="9" t="s">
-        <v>2471</v>
+        <v>2493</v>
       </c>
       <c r="E217" s="22"/>
       <c r="F217" s="121" t="s">
-        <v>2472</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="218" ht="22.5" customHeight="1">
@@ -21322,10 +21388,10 @@
         <v>235</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>2461</v>
+        <v>2483</v>
       </c>
       <c r="D218" s="3" t="s">
-        <v>2461</v>
+        <v>2483</v>
       </c>
       <c r="E218" s="21"/>
       <c r="F218" s="132"/>
@@ -21341,11 +21407,11 @@
         <v>1671</v>
       </c>
       <c r="D219" s="9" t="s">
-        <v>2473</v>
+        <v>2495</v>
       </c>
       <c r="E219" s="22"/>
       <c r="F219" s="59" t="s">
-        <v>2474</v>
+        <v>2496</v>
       </c>
     </row>
     <row r="220" ht="22.5" customHeight="1">
@@ -21359,11 +21425,11 @@
         <v>1671</v>
       </c>
       <c r="D220" s="36" t="s">
-        <v>2475</v>
+        <v>2497</v>
       </c>
       <c r="E220" s="37"/>
       <c r="F220" s="125" t="s">
-        <v>2476</v>
+        <v>2498</v>
       </c>
     </row>
   </sheetData>
@@ -21394,7 +21460,7 @@
         <v>264</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2477</v>
+        <v>2499</v>
       </c>
     </row>
     <row r="2" ht="22.5" customHeight="1">
@@ -21405,7 +21471,7 @@
         <v>261</v>
       </c>
       <c r="C2" s="57" t="s">
-        <v>2478</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1">
@@ -21416,7 +21482,7 @@
         <v>261</v>
       </c>
       <c r="C3" s="59" t="s">
-        <v>2479</v>
+        <v>2501</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
@@ -21427,7 +21493,7 @@
         <v>261</v>
       </c>
       <c r="C4" s="57" t="s">
-        <v>2480</v>
+        <v>2502</v>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1">
@@ -21438,7 +21504,7 @@
         <v>261</v>
       </c>
       <c r="C5" s="59" t="s">
-        <v>2023</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1">
@@ -21449,7 +21515,7 @@
         <v>261</v>
       </c>
       <c r="C6" s="133" t="s">
-        <v>2481</v>
+        <v>2503</v>
       </c>
     </row>
   </sheetData>
